--- a/outputs/SA_curtailment.xlsx
+++ b/outputs/SA_curtailment.xlsx
@@ -638,7 +638,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="5" t="n">
-        <v>0.256</v>
+        <v>0.2756</v>
       </c>
       <c r="K2" s="5" t="inlineStr"/>
       <c r="L2" s="5" t="inlineStr"/>
@@ -805,10 +805,10 @@
       </c>
       <c r="I5" s="2" t="inlineStr"/>
       <c r="J5" s="5" t="n">
-        <v>0.1726</v>
+        <v>0.1844</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>0.1928</v>
+        <v>0.2168</v>
       </c>
       <c r="L5" s="5" t="inlineStr"/>
       <c r="M5" s="5" t="inlineStr"/>
@@ -870,7 +870,7 @@
         <v>132</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>0.3235</v>
+        <v>0.3552</v>
       </c>
       <c r="K6" s="5" t="inlineStr"/>
       <c r="L6" s="5" t="n">
@@ -953,10 +953,10 @@
         <v>132</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>0.2766</v>
+        <v>0.2949</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>0.302</v>
+        <v>0.3494</v>
       </c>
       <c r="L7" s="5" t="n">
         <v>0.501077617843089</v>
@@ -1148,10 +1148,10 @@
         <v>66</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>0.2415</v>
+        <v>0.2554</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>0.2987</v>
+        <v>0.3269</v>
       </c>
       <c r="L10" s="5" t="n">
         <v>0.511388342191138</v>
@@ -1217,7 +1217,7 @@
         <v>3.3</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>0.2007</v>
+        <v>0.2156</v>
       </c>
       <c r="K11" s="5" t="inlineStr"/>
       <c r="L11" s="5" t="n">
@@ -1381,10 +1381,10 @@
         <v>33</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>0.3012</v>
+        <v>0.3249</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>0.2557</v>
+        <v>0.2807</v>
       </c>
       <c r="L13" s="5" t="n">
         <v>0.510590381447813</v>
@@ -1466,10 +1466,10 @@
         <v>3.3</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>0.2462</v>
+        <v>0.2753</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>0.3446</v>
+        <v>0.3888</v>
       </c>
       <c r="L14" s="5" t="n">
         <v>0.65425629128861</v>
@@ -1551,10 +1551,10 @@
         <v>3.3</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>0.2411</v>
+        <v>0.2707</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>0.3571</v>
+        <v>0.3988</v>
       </c>
       <c r="L15" s="5" t="n">
         <v>0.65425629128861</v>
@@ -1636,10 +1636,10 @@
         <v>3.3</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>0.1273</v>
+        <v>0.148</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>0.2429</v>
+        <v>0.286</v>
       </c>
       <c r="L16" s="5" t="n">
         <v>0.65425629128861</v>
@@ -1721,10 +1721,10 @@
         <v>3.3</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>0.2031</v>
+        <v>0.2332</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>0.3023</v>
+        <v>0.3481</v>
       </c>
       <c r="L17" s="5" t="n">
         <v>0.65425629128861</v>
@@ -1806,7 +1806,7 @@
         <v>11</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>0.2284</v>
+        <v>0.2613</v>
       </c>
       <c r="K18" s="5" t="inlineStr"/>
       <c r="L18" s="5" t="n">
@@ -1889,10 +1889,10 @@
         <v>275</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>0.3589</v>
+        <v>0.4012</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>0.4077</v>
+        <v>0.4797</v>
       </c>
       <c r="L19" s="5" t="n">
         <v>0.501077617843089</v>
@@ -1974,10 +1974,10 @@
         <v>132</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>0.2973</v>
+        <v>0.3167</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>0.3825</v>
+        <v>0.4573</v>
       </c>
       <c r="L20" s="5" t="n">
         <v>0.511370986967519</v>
@@ -2043,10 +2043,10 @@
         <v>132</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>0.3511</v>
+        <v>0.384</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>0.4088</v>
+        <v>0.5138</v>
       </c>
       <c r="L21" s="5" t="n">
         <v>0.511370986967519</v>
@@ -2106,10 +2106,10 @@
       </c>
       <c r="I22" s="2" t="inlineStr"/>
       <c r="J22" s="5" t="n">
-        <v>0.254</v>
+        <v>0.2612</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>0.2722</v>
+        <v>0.2954</v>
       </c>
       <c r="L22" s="5" t="inlineStr"/>
       <c r="M22" s="5" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
       </c>
       <c r="I23" s="2" t="inlineStr"/>
       <c r="J23" s="5" t="n">
-        <v>0.0515</v>
+        <v>0.0518</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>0.0373</v>
+        <v>0.0381</v>
       </c>
       <c r="L23" s="5" t="inlineStr"/>
       <c r="M23" s="5" t="inlineStr"/>
@@ -2227,7 +2227,7 @@
         <v>0.0062</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>0.0175</v>
+        <v>0.0178</v>
       </c>
       <c r="L24" s="5" t="inlineStr"/>
       <c r="M24" s="5" t="inlineStr"/>
@@ -2283,10 +2283,10 @@
       </c>
       <c r="I25" s="2" t="inlineStr"/>
       <c r="J25" s="5" t="n">
-        <v>0.176</v>
+        <v>0.1796</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>0.09</v>
+        <v>0.094</v>
       </c>
       <c r="L25" s="5" t="inlineStr"/>
       <c r="M25" s="5" t="inlineStr"/>
@@ -2343,7 +2343,7 @@
       <c r="I26" s="2" t="inlineStr"/>
       <c r="J26" s="5" t="inlineStr"/>
       <c r="K26" s="5" t="n">
-        <v>0.2684</v>
+        <v>0.2785</v>
       </c>
       <c r="L26" s="5" t="inlineStr"/>
       <c r="M26" s="5" t="inlineStr"/>
@@ -2399,10 +2399,10 @@
       </c>
       <c r="I27" s="2" t="inlineStr"/>
       <c r="J27" s="5" t="n">
-        <v>0.1169</v>
+        <v>0.1209</v>
       </c>
       <c r="K27" s="5" t="n">
-        <v>0.1842</v>
+        <v>0.1935</v>
       </c>
       <c r="L27" s="5" t="inlineStr"/>
       <c r="M27" s="5" t="inlineStr"/>
@@ -2458,10 +2458,10 @@
       </c>
       <c r="I28" s="2" t="inlineStr"/>
       <c r="J28" s="5" t="n">
-        <v>0.1053</v>
+        <v>0.1083</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>0.1829</v>
+        <v>0.1916</v>
       </c>
       <c r="L28" s="5" t="inlineStr"/>
       <c r="M28" s="5" t="inlineStr"/>
@@ -2517,7 +2517,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="5" t="n">
-        <v>0.0033</v>
+        <v>0.0034</v>
       </c>
       <c r="K29" s="5" t="n">
         <v>0.0016</v>
@@ -2635,7 +2635,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="5" t="n">
-        <v>0.0027</v>
+        <v>0.0028</v>
       </c>
       <c r="K31" s="5" t="n">
         <v>0.0015</v>
@@ -2694,10 +2694,10 @@
       </c>
       <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="5" t="n">
-        <v>0.1941</v>
+        <v>0.2</v>
       </c>
       <c r="K32" s="5" t="n">
-        <v>0.2447</v>
+        <v>0.2497</v>
       </c>
       <c r="L32" s="5" t="inlineStr"/>
       <c r="M32" s="5" t="inlineStr"/>
@@ -2753,10 +2753,10 @@
       </c>
       <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="5" t="n">
-        <v>0.2514</v>
+        <v>0.2652</v>
       </c>
       <c r="K33" s="5" t="n">
-        <v>0.2681</v>
+        <v>0.2733</v>
       </c>
       <c r="L33" s="5" t="inlineStr"/>
       <c r="M33" s="5" t="inlineStr"/>
@@ -2812,10 +2812,10 @@
       </c>
       <c r="I34" s="2" t="inlineStr"/>
       <c r="J34" s="5" t="n">
-        <v>0.2535</v>
+        <v>0.2637</v>
       </c>
       <c r="K34" s="5" t="n">
-        <v>0.2928</v>
+        <v>0.3006</v>
       </c>
       <c r="L34" s="5" t="inlineStr"/>
       <c r="M34" s="5" t="inlineStr"/>
@@ -2871,10 +2871,10 @@
       </c>
       <c r="I35" s="2" t="inlineStr"/>
       <c r="J35" s="5" t="n">
-        <v>0.1438</v>
+        <v>0.1458</v>
       </c>
       <c r="K35" s="5" t="n">
-        <v>0.1687</v>
+        <v>0.1783</v>
       </c>
       <c r="L35" s="5" t="inlineStr"/>
       <c r="M35" s="5" t="inlineStr"/>
@@ -2930,10 +2930,10 @@
       </c>
       <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="5" t="n">
-        <v>0.1628</v>
+        <v>0.1653</v>
       </c>
       <c r="K36" s="5" t="n">
-        <v>0.1911</v>
+        <v>0.1995</v>
       </c>
       <c r="L36" s="5" t="inlineStr"/>
       <c r="M36" s="5" t="inlineStr"/>
@@ -2989,10 +2989,10 @@
       </c>
       <c r="I37" s="2" t="inlineStr"/>
       <c r="J37" s="5" t="n">
-        <v>0.287</v>
+        <v>0.3052</v>
       </c>
       <c r="K37" s="5" t="n">
-        <v>0.1473</v>
+        <v>0.1511</v>
       </c>
       <c r="L37" s="5" t="inlineStr"/>
       <c r="M37" s="5" t="inlineStr"/>
@@ -3048,10 +3048,10 @@
       </c>
       <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="5" t="n">
-        <v>0.1193</v>
+        <v>0.1223</v>
       </c>
       <c r="K38" s="5" t="n">
-        <v>0.1648</v>
+        <v>0.1729</v>
       </c>
       <c r="L38" s="5" t="inlineStr"/>
       <c r="M38" s="5" t="inlineStr"/>
@@ -3107,10 +3107,10 @@
       </c>
       <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="5" t="n">
-        <v>0.1943</v>
+        <v>0.1999</v>
       </c>
       <c r="K39" s="5" t="n">
-        <v>0.2082</v>
+        <v>0.2153</v>
       </c>
       <c r="L39" s="5" t="inlineStr"/>
       <c r="M39" s="5" t="inlineStr"/>
@@ -3169,7 +3169,7 @@
         <v>0.0037</v>
       </c>
       <c r="K40" s="5" t="n">
-        <v>0.0026</v>
+        <v>0.0022</v>
       </c>
       <c r="L40" s="5" t="inlineStr"/>
       <c r="M40" s="5" t="inlineStr"/>
@@ -3225,10 +3225,10 @@
       </c>
       <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="5" t="n">
-        <v>0.0026</v>
+        <v>0.0027</v>
       </c>
       <c r="K41" s="5" t="n">
-        <v>0.0028</v>
+        <v>0.0027</v>
       </c>
       <c r="L41" s="5" t="inlineStr"/>
       <c r="M41" s="5" t="inlineStr"/>
@@ -3284,10 +3284,10 @@
       </c>
       <c r="I42" s="2" t="inlineStr"/>
       <c r="J42" s="5" t="n">
-        <v>0.1825</v>
+        <v>0.1863</v>
       </c>
       <c r="K42" s="5" t="n">
-        <v>0.2632</v>
+        <v>0.2696</v>
       </c>
       <c r="L42" s="5" t="inlineStr"/>
       <c r="M42" s="5" t="inlineStr"/>
@@ -3402,10 +3402,10 @@
       </c>
       <c r="I44" s="2" t="inlineStr"/>
       <c r="J44" s="5" t="n">
-        <v>0.0847</v>
+        <v>0.0906</v>
       </c>
       <c r="K44" s="5" t="n">
-        <v>0.1771</v>
+        <v>0.1905</v>
       </c>
       <c r="L44" s="5" t="inlineStr"/>
       <c r="M44" s="5" t="inlineStr"/>
@@ -3461,10 +3461,10 @@
       </c>
       <c r="I45" s="2" t="inlineStr"/>
       <c r="J45" s="5" t="n">
-        <v>0.0203</v>
+        <v>0.0206</v>
       </c>
       <c r="K45" s="5" t="n">
-        <v>0.0122</v>
+        <v>0.0121</v>
       </c>
       <c r="L45" s="5" t="inlineStr"/>
       <c r="M45" s="5" t="inlineStr"/>
@@ -3520,10 +3520,10 @@
       </c>
       <c r="I46" s="2" t="inlineStr"/>
       <c r="J46" s="5" t="n">
-        <v>0.1598</v>
+        <v>0.1686</v>
       </c>
       <c r="K46" s="5" t="n">
-        <v>0.1908</v>
+        <v>0.2013</v>
       </c>
       <c r="L46" s="5" t="inlineStr"/>
       <c r="M46" s="5" t="inlineStr"/>
@@ -3579,10 +3579,10 @@
       </c>
       <c r="I47" s="2" t="inlineStr"/>
       <c r="J47" s="5" t="n">
-        <v>0.0426</v>
+        <v>0.0432</v>
       </c>
       <c r="K47" s="5" t="n">
-        <v>0.0328</v>
+        <v>0.0341</v>
       </c>
       <c r="L47" s="5" t="inlineStr"/>
       <c r="M47" s="5" t="inlineStr"/>
@@ -3769,7 +3769,7 @@
         <v>1.0033</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>0.256</v>
+        <v>0.2756</v>
       </c>
       <c r="F2" s="5" t="inlineStr"/>
       <c r="G2" s="5" t="inlineStr"/>
@@ -3951,10 +3951,10 @@
         <v>1.0002</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.1726</v>
+        <v>0.1844</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.1928</v>
+        <v>0.2168</v>
       </c>
       <c r="G5" s="5" t="inlineStr"/>
       <c r="H5" s="5" t="inlineStr"/>
@@ -4015,7 +4015,7 @@
         <v>0.9703000000000001</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0.3235</v>
+        <v>0.3552</v>
       </c>
       <c r="F6" s="5" t="inlineStr"/>
       <c r="G6" s="5" t="n">
@@ -4097,10 +4097,10 @@
         <v>0.9703000000000001</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>0.2766</v>
+        <v>0.2949</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.302</v>
+        <v>0.3494</v>
       </c>
       <c r="G7" s="5" t="n">
         <v>0.501077617843089</v>
@@ -4301,10 +4301,10 @@
         <v>1.0022</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>0.2415</v>
+        <v>0.2554</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>0.2987</v>
+        <v>0.3269</v>
       </c>
       <c r="G10" s="5" t="n">
         <v>0.511388342191138</v>
@@ -4369,7 +4369,7 @@
         <v>1.0134</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0.2007</v>
+        <v>0.2156</v>
       </c>
       <c r="F11" s="5" t="inlineStr"/>
       <c r="G11" s="5" t="n">
@@ -4531,10 +4531,10 @@
         <v>0.9959</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>0.3012</v>
+        <v>0.3249</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.2557</v>
+        <v>0.2807</v>
       </c>
       <c r="G13" s="5" t="n">
         <v>0.510590381447813</v>
@@ -4615,10 +4615,10 @@
         <v>0.9540999999999999</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>0.2462</v>
+        <v>0.2753</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>0.3446</v>
+        <v>0.3888</v>
       </c>
       <c r="G14" s="5" t="n">
         <v>0.65425629128861</v>
@@ -4699,10 +4699,10 @@
         <v>0.9664</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>0.2411</v>
+        <v>0.2707</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>0.3571</v>
+        <v>0.3988</v>
       </c>
       <c r="G15" s="5" t="n">
         <v>0.65425629128861</v>
@@ -4783,10 +4783,10 @@
         <v>0.9741</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>0.1273</v>
+        <v>0.148</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>0.2429</v>
+        <v>0.286</v>
       </c>
       <c r="G16" s="5" t="n">
         <v>0.65425629128861</v>
@@ -4867,10 +4867,10 @@
         <v>0.9772999999999999</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>0.2031</v>
+        <v>0.2332</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>0.3023</v>
+        <v>0.3481</v>
       </c>
       <c r="G17" s="5" t="n">
         <v>0.65425629128861</v>
@@ -4951,7 +4951,7 @@
         <v>1.011</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>0.2284</v>
+        <v>0.2613</v>
       </c>
       <c r="F18" s="5" t="inlineStr"/>
       <c r="G18" s="5" t="n">
@@ -5033,10 +5033,10 @@
         <v>0.9709</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>0.3589</v>
+        <v>0.4012</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>0.4077</v>
+        <v>0.4797</v>
       </c>
       <c r="G19" s="5" t="n">
         <v>0.501077617843089</v>
@@ -5117,10 +5117,10 @@
         <v>0.9968</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>0.2973</v>
+        <v>0.3167</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>0.3825</v>
+        <v>0.4573</v>
       </c>
       <c r="G20" s="5" t="n">
         <v>0.511370986967519</v>
@@ -5185,10 +5185,10 @@
         <v>0.9978</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>0.3511</v>
+        <v>0.384</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>0.4088</v>
+        <v>0.5138</v>
       </c>
       <c r="G21" s="5" t="n">
         <v>0.511370986967519</v>
@@ -5253,10 +5253,10 @@
         <v>0.9527</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>0.254</v>
+        <v>0.2612</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>0.2722</v>
+        <v>0.2954</v>
       </c>
       <c r="G22" s="5" t="inlineStr"/>
       <c r="H22" s="5" t="inlineStr"/>
@@ -5317,10 +5317,10 @@
         <v>0.9417</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>0.0515</v>
+        <v>0.0518</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>0.0373</v>
+        <v>0.0381</v>
       </c>
       <c r="G23" s="5" t="inlineStr"/>
       <c r="H23" s="5" t="inlineStr"/>
@@ -5384,7 +5384,7 @@
         <v>0.0062</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>0.0175</v>
+        <v>0.0178</v>
       </c>
       <c r="G24" s="5" t="inlineStr"/>
       <c r="H24" s="5" t="inlineStr"/>
@@ -5445,10 +5445,10 @@
         <v>0.9687</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>0.176</v>
+        <v>0.1796</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>0.09</v>
+        <v>0.094</v>
       </c>
       <c r="G25" s="5" t="inlineStr"/>
       <c r="H25" s="5" t="inlineStr"/>
@@ -5510,7 +5510,7 @@
       </c>
       <c r="E26" s="5" t="inlineStr"/>
       <c r="F26" s="5" t="n">
-        <v>0.2684</v>
+        <v>0.2785</v>
       </c>
       <c r="G26" s="5" t="inlineStr"/>
       <c r="H26" s="5" t="inlineStr"/>
@@ -5571,10 +5571,10 @@
         <v>0.9628</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>0.1169</v>
+        <v>0.1209</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>0.1842</v>
+        <v>0.1935</v>
       </c>
       <c r="G27" s="5" t="inlineStr"/>
       <c r="H27" s="5" t="inlineStr"/>
@@ -5635,10 +5635,10 @@
         <v>0.9606</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>0.1053</v>
+        <v>0.1083</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>0.1829</v>
+        <v>0.1916</v>
       </c>
       <c r="G28" s="5" t="inlineStr"/>
       <c r="H28" s="5" t="inlineStr"/>
@@ -5699,7 +5699,7 @@
         <v>0.9533</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>0.0033</v>
+        <v>0.0034</v>
       </c>
       <c r="F29" s="5" t="n">
         <v>0.0016</v>
@@ -5827,7 +5827,7 @@
         <v>0.9533</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>0.0027</v>
+        <v>0.0028</v>
       </c>
       <c r="F31" s="5" t="n">
         <v>0.0015</v>
@@ -5891,10 +5891,10 @@
         <v>0.9468</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>0.1941</v>
+        <v>0.2</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>0.2447</v>
+        <v>0.2497</v>
       </c>
       <c r="G32" s="5" t="inlineStr"/>
       <c r="H32" s="5" t="inlineStr"/>
@@ -5955,10 +5955,10 @@
         <v>0.9468</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>0.2514</v>
+        <v>0.2652</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>0.2681</v>
+        <v>0.2733</v>
       </c>
       <c r="G33" s="5" t="inlineStr"/>
       <c r="H33" s="5" t="inlineStr"/>
@@ -6019,10 +6019,10 @@
         <v>0.9468</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>0.2535</v>
+        <v>0.2637</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>0.2928</v>
+        <v>0.3006</v>
       </c>
       <c r="G34" s="5" t="inlineStr"/>
       <c r="H34" s="5" t="inlineStr"/>
@@ -6083,10 +6083,10 @@
         <v>0.9661</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>0.1438</v>
+        <v>0.1458</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>0.1687</v>
+        <v>0.1783</v>
       </c>
       <c r="G35" s="5" t="inlineStr"/>
       <c r="H35" s="5" t="inlineStr"/>
@@ -6147,10 +6147,10 @@
         <v>0.9661</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>0.1628</v>
+        <v>0.1653</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>0.1911</v>
+        <v>0.1995</v>
       </c>
       <c r="G36" s="5" t="inlineStr"/>
       <c r="H36" s="5" t="inlineStr"/>
@@ -6211,10 +6211,10 @@
         <v>0.9387</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>0.287</v>
+        <v>0.3052</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>0.1473</v>
+        <v>0.1511</v>
       </c>
       <c r="G37" s="5" t="inlineStr"/>
       <c r="H37" s="5" t="inlineStr"/>
@@ -6275,10 +6275,10 @@
         <v>0.9572000000000001</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>0.1193</v>
+        <v>0.1223</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>0.1648</v>
+        <v>0.1729</v>
       </c>
       <c r="G38" s="5" t="inlineStr"/>
       <c r="H38" s="5" t="inlineStr"/>
@@ -6339,10 +6339,10 @@
         <v>0.9709</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>0.1943</v>
+        <v>0.1999</v>
       </c>
       <c r="F39" s="5" t="n">
-        <v>0.2082</v>
+        <v>0.2153</v>
       </c>
       <c r="G39" s="5" t="inlineStr"/>
       <c r="H39" s="5" t="inlineStr"/>
@@ -6406,7 +6406,7 @@
         <v>0.0037</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>0.0026</v>
+        <v>0.0022</v>
       </c>
       <c r="G40" s="5" t="inlineStr"/>
       <c r="H40" s="5" t="inlineStr"/>
@@ -6467,10 +6467,10 @@
         <v>0.9699</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>0.0026</v>
+        <v>0.0027</v>
       </c>
       <c r="F41" s="5" t="n">
-        <v>0.0028</v>
+        <v>0.0027</v>
       </c>
       <c r="G41" s="5" t="inlineStr"/>
       <c r="H41" s="5" t="inlineStr"/>
@@ -6531,10 +6531,10 @@
         <v>0.9132</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>0.1825</v>
+        <v>0.1863</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>0.2632</v>
+        <v>0.2696</v>
       </c>
       <c r="G42" s="5" t="inlineStr"/>
       <c r="H42" s="5" t="inlineStr"/>
@@ -6659,10 +6659,10 @@
         <v>0.9572000000000001</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>0.0847</v>
+        <v>0.0906</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>0.1771</v>
+        <v>0.1905</v>
       </c>
       <c r="G44" s="5" t="inlineStr"/>
       <c r="H44" s="5" t="inlineStr"/>
@@ -6723,10 +6723,10 @@
         <v>0.9611</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>0.0203</v>
+        <v>0.0206</v>
       </c>
       <c r="F45" s="5" t="n">
-        <v>0.0122</v>
+        <v>0.0121</v>
       </c>
       <c r="G45" s="5" t="inlineStr"/>
       <c r="H45" s="5" t="inlineStr"/>
@@ -6787,10 +6787,10 @@
         <v>0.8476</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>0.1598</v>
+        <v>0.1686</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>0.1908</v>
+        <v>0.2013</v>
       </c>
       <c r="G46" s="5" t="inlineStr"/>
       <c r="H46" s="5" t="inlineStr"/>
@@ -6851,10 +6851,10 @@
         <v>0.9592000000000001</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>0.0426</v>
+        <v>0.0432</v>
       </c>
       <c r="F47" s="5" t="n">
-        <v>0.0328</v>
+        <v>0.0341</v>
       </c>
       <c r="G47" s="5" t="inlineStr"/>
       <c r="H47" s="5" t="inlineStr"/>

--- a/outputs/SA_curtailment.xlsx
+++ b/outputs/SA_curtailment.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W47"/>
+  <dimension ref="A1:Y47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -465,10 +465,10 @@
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="5" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="6" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
@@ -482,6 +482,8 @@
     <col width="12" customWidth="1" min="21" max="21"/>
     <col width="12" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="24" max="24"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -517,85 +519,95 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>REZ Source</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>State</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>MW</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>kV</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Actual FY24-25</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Actual FY25-26</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>ELI Near Term</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>ELI Med Term</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ELI Source</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>FY25-26</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>FY26-27</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Curt FY1</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Curt FY2</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Curt FY3</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Curt Avg</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Offl FY1</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Offl FY2</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Offl FY3</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Offl Avg</t>
         </is>
@@ -618,45 +630,39 @@
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr"/>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr"/>
+      <c r="F2" s="3" t="inlineStr"/>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>SA</t>
         </is>
       </c>
-      <c r="H2" s="4" t="n">
+      <c r="I2" s="4" t="n">
         <v>24.75</v>
       </c>
-      <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="5" t="n">
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="5" t="n">
         <v>0.2756</v>
       </c>
-      <c r="K2" s="5" t="inlineStr"/>
       <c r="L2" s="5" t="inlineStr"/>
       <c r="M2" s="5" t="inlineStr"/>
-      <c r="N2" s="5" t="n">
+      <c r="N2" s="5" t="inlineStr"/>
+      <c r="O2" s="2" t="inlineStr"/>
+      <c r="P2" s="5" t="n">
         <v>1.0037</v>
       </c>
-      <c r="O2" s="5" t="n">
+      <c r="Q2" s="5" t="n">
         <v>1.0033</v>
       </c>
-      <c r="P2" s="6" t="inlineStr"/>
-      <c r="Q2" s="6" t="inlineStr"/>
       <c r="R2" s="6" t="inlineStr"/>
       <c r="S2" s="6" t="inlineStr"/>
       <c r="T2" s="6" t="inlineStr"/>
       <c r="U2" s="6" t="inlineStr"/>
       <c r="V2" s="6" t="inlineStr"/>
       <c r="W2" s="6" t="inlineStr"/>
+      <c r="X2" s="6" t="inlineStr"/>
+      <c r="Y2" s="6" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -675,43 +681,37 @@
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr"/>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>SA</t>
         </is>
       </c>
-      <c r="H3" s="4" t="n">
+      <c r="I3" s="4" t="n">
         <v>0.2</v>
       </c>
-      <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="5" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="5" t="inlineStr"/>
       <c r="L3" s="5" t="inlineStr"/>
       <c r="M3" s="5" t="inlineStr"/>
-      <c r="N3" s="5" t="n">
+      <c r="N3" s="5" t="inlineStr"/>
+      <c r="O3" s="2" t="inlineStr"/>
+      <c r="P3" s="5" t="n">
         <v>1.0037</v>
       </c>
-      <c r="O3" s="5" t="n">
+      <c r="Q3" s="5" t="n">
         <v>1.0033</v>
       </c>
-      <c r="P3" s="6" t="inlineStr"/>
-      <c r="Q3" s="6" t="inlineStr"/>
       <c r="R3" s="6" t="inlineStr"/>
       <c r="S3" s="6" t="inlineStr"/>
       <c r="T3" s="6" t="inlineStr"/>
       <c r="U3" s="6" t="inlineStr"/>
       <c r="V3" s="6" t="inlineStr"/>
       <c r="W3" s="6" t="inlineStr"/>
+      <c r="X3" s="6" t="inlineStr"/>
+      <c r="Y3" s="6" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -730,43 +730,37 @@
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr"/>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr"/>
+      <c r="F4" s="3" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>SA</t>
         </is>
       </c>
-      <c r="H4" s="4" t="n">
+      <c r="I4" s="4" t="n">
         <v>0.02</v>
       </c>
-      <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="5" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="5" t="inlineStr"/>
       <c r="L4" s="5" t="inlineStr"/>
       <c r="M4" s="5" t="inlineStr"/>
-      <c r="N4" s="5" t="n">
+      <c r="N4" s="5" t="inlineStr"/>
+      <c r="O4" s="2" t="inlineStr"/>
+      <c r="P4" s="5" t="n">
         <v>1.0037</v>
       </c>
-      <c r="O4" s="5" t="n">
+      <c r="Q4" s="5" t="n">
         <v>1.0033</v>
       </c>
-      <c r="P4" s="6" t="inlineStr"/>
-      <c r="Q4" s="6" t="inlineStr"/>
       <c r="R4" s="6" t="inlineStr"/>
       <c r="S4" s="6" t="inlineStr"/>
       <c r="T4" s="6" t="inlineStr"/>
       <c r="U4" s="6" t="inlineStr"/>
       <c r="V4" s="6" t="inlineStr"/>
       <c r="W4" s="6" t="inlineStr"/>
+      <c r="X4" s="6" t="inlineStr"/>
+      <c r="Y4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -785,47 +779,41 @@
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr"/>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="3" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>SA</t>
         </is>
       </c>
-      <c r="H5" s="4" t="n">
+      <c r="I5" s="4" t="n">
         <v>8.25</v>
       </c>
-      <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="5" t="n">
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="5" t="n">
         <v>0.1844</v>
       </c>
-      <c r="K5" s="5" t="n">
+      <c r="L5" s="5" t="n">
         <v>0.2168</v>
       </c>
-      <c r="L5" s="5" t="inlineStr"/>
       <c r="M5" s="5" t="inlineStr"/>
-      <c r="N5" s="5" t="n">
+      <c r="N5" s="5" t="inlineStr"/>
+      <c r="O5" s="2" t="inlineStr"/>
+      <c r="P5" s="5" t="n">
         <v>0.9999</v>
       </c>
-      <c r="O5" s="5" t="n">
+      <c r="Q5" s="5" t="n">
         <v>1.0002</v>
       </c>
-      <c r="P5" s="6" t="inlineStr"/>
-      <c r="Q5" s="6" t="inlineStr"/>
       <c r="R5" s="6" t="inlineStr"/>
       <c r="S5" s="6" t="inlineStr"/>
       <c r="T5" s="6" t="inlineStr"/>
       <c r="U5" s="6" t="inlineStr"/>
       <c r="V5" s="6" t="inlineStr"/>
       <c r="W5" s="6" t="inlineStr"/>
+      <c r="X5" s="6" t="inlineStr"/>
+      <c r="Y5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -860,37 +848,41 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
           <t>SA</t>
         </is>
       </c>
-      <c r="H6" s="4" t="n">
+      <c r="I6" s="4" t="n">
         <v>135</v>
       </c>
-      <c r="I6" s="2" t="n">
+      <c r="J6" s="2" t="n">
         <v>132</v>
       </c>
-      <c r="J6" s="5" t="n">
+      <c r="K6" s="5" t="n">
         <v>0.3552</v>
       </c>
-      <c r="K6" s="5" t="inlineStr"/>
-      <c r="L6" s="5" t="n">
+      <c r="L6" s="5" t="inlineStr"/>
+      <c r="M6" s="5" t="n">
         <v>0.501077617843089</v>
       </c>
-      <c r="M6" s="5" t="n">
+      <c r="N6" s="5" t="n">
         <v>0.212860651220515</v>
       </c>
-      <c r="N6" s="5" t="n">
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>per-DUID</t>
+        </is>
+      </c>
+      <c r="P6" s="5" t="n">
         <v>0.9725</v>
       </c>
-      <c r="O6" s="5" t="n">
+      <c r="Q6" s="5" t="n">
         <v>0.9703000000000001</v>
       </c>
-      <c r="P6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" s="6" t="n">
         <v>0</v>
       </c>
@@ -898,15 +890,21 @@
         <v>0</v>
       </c>
       <c r="T6" s="6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="U6" s="6" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="V6" s="6" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="W6" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="X6" s="6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="Y6" s="6" t="n">
         <v>0.07333333333333335</v>
       </c>
     </row>
@@ -943,39 +941,43 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
           <t>SA</t>
         </is>
       </c>
-      <c r="H7" s="4" t="n">
+      <c r="I7" s="4" t="n">
         <v>135</v>
       </c>
-      <c r="I7" s="2" t="n">
+      <c r="J7" s="2" t="n">
         <v>132</v>
       </c>
-      <c r="J7" s="5" t="n">
+      <c r="K7" s="5" t="n">
         <v>0.2949</v>
       </c>
-      <c r="K7" s="5" t="n">
+      <c r="L7" s="5" t="n">
         <v>0.3494</v>
       </c>
-      <c r="L7" s="5" t="n">
+      <c r="M7" s="5" t="n">
         <v>0.501077617843089</v>
       </c>
-      <c r="M7" s="5" t="n">
+      <c r="N7" s="5" t="n">
         <v>0.212860651220515</v>
       </c>
-      <c r="N7" s="5" t="n">
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>per-DUID</t>
+        </is>
+      </c>
+      <c r="P7" s="5" t="n">
         <v>0.9725</v>
       </c>
-      <c r="O7" s="5" t="n">
+      <c r="Q7" s="5" t="n">
         <v>0.9703000000000001</v>
       </c>
-      <c r="P7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" s="6" t="n">
         <v>0</v>
       </c>
@@ -983,15 +985,21 @@
         <v>0</v>
       </c>
       <c r="T7" s="6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="U7" s="6" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="V7" s="6" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="W7" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="X7" s="6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="Y7" s="6" t="n">
         <v>0.07333333333333335</v>
       </c>
     </row>
@@ -1012,43 +1020,37 @@
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr"/>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr"/>
+      <c r="F8" s="3" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>SA</t>
         </is>
       </c>
-      <c r="H8" s="4" t="n">
+      <c r="I8" s="4" t="n">
         <v>2.75</v>
       </c>
-      <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="5" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="5" t="inlineStr"/>
       <c r="L8" s="5" t="inlineStr"/>
       <c r="M8" s="5" t="inlineStr"/>
-      <c r="N8" s="5" t="n">
+      <c r="N8" s="5" t="inlineStr"/>
+      <c r="O8" s="2" t="inlineStr"/>
+      <c r="P8" s="5" t="n">
         <v>1.0037</v>
       </c>
-      <c r="O8" s="5" t="n">
+      <c r="Q8" s="5" t="n">
         <v>1.0033</v>
       </c>
-      <c r="P8" s="6" t="inlineStr"/>
-      <c r="Q8" s="6" t="inlineStr"/>
       <c r="R8" s="6" t="inlineStr"/>
       <c r="S8" s="6" t="inlineStr"/>
       <c r="T8" s="6" t="inlineStr"/>
       <c r="U8" s="6" t="inlineStr"/>
       <c r="V8" s="6" t="inlineStr"/>
       <c r="W8" s="6" t="inlineStr"/>
+      <c r="X8" s="6" t="inlineStr"/>
+      <c r="Y8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1067,43 +1069,37 @@
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr"/>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>SA</t>
         </is>
       </c>
-      <c r="H9" s="4" t="n">
+      <c r="I9" s="4" t="n">
         <v>1.08</v>
       </c>
-      <c r="I9" s="2" t="inlineStr"/>
-      <c r="J9" s="5" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="5" t="inlineStr"/>
       <c r="L9" s="5" t="inlineStr"/>
       <c r="M9" s="5" t="inlineStr"/>
-      <c r="N9" s="5" t="n">
+      <c r="N9" s="5" t="inlineStr"/>
+      <c r="O9" s="2" t="inlineStr"/>
+      <c r="P9" s="5" t="n">
         <v>1.0037</v>
       </c>
-      <c r="O9" s="5" t="n">
+      <c r="Q9" s="5" t="n">
         <v>1.0033</v>
       </c>
-      <c r="P9" s="6" t="inlineStr"/>
-      <c r="Q9" s="6" t="inlineStr"/>
       <c r="R9" s="6" t="inlineStr"/>
       <c r="S9" s="6" t="inlineStr"/>
       <c r="T9" s="6" t="inlineStr"/>
       <c r="U9" s="6" t="inlineStr"/>
       <c r="V9" s="6" t="inlineStr"/>
       <c r="W9" s="6" t="inlineStr"/>
+      <c r="X9" s="6" t="inlineStr"/>
+      <c r="Y9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1138,41 +1134,51 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
           <t>SA</t>
         </is>
       </c>
-      <c r="H10" s="4" t="n">
+      <c r="I10" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="I10" s="2" t="n">
+      <c r="J10" s="2" t="n">
         <v>66</v>
       </c>
-      <c r="J10" s="5" t="n">
+      <c r="K10" s="5" t="n">
         <v>0.2554</v>
       </c>
-      <c r="K10" s="5" t="n">
+      <c r="L10" s="5" t="n">
         <v>0.3269</v>
       </c>
-      <c r="L10" s="5" t="n">
+      <c r="M10" s="5" t="n">
         <v>0.511388342191138</v>
       </c>
-      <c r="M10" s="5" t="n">
+      <c r="N10" s="5" t="n">
         <v>0.22265637813532</v>
       </c>
-      <c r="N10" s="5" t="n">
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>per-DUID</t>
+        </is>
+      </c>
+      <c r="P10" s="5" t="n">
         <v>1.0024</v>
       </c>
-      <c r="O10" s="5" t="n">
+      <c r="Q10" s="5" t="n">
         <v>1.0022</v>
       </c>
-      <c r="P10" s="6" t="inlineStr"/>
-      <c r="Q10" s="6" t="inlineStr"/>
       <c r="R10" s="6" t="inlineStr"/>
       <c r="S10" s="6" t="inlineStr"/>
       <c r="T10" s="6" t="inlineStr"/>
       <c r="U10" s="6" t="inlineStr"/>
       <c r="V10" s="6" t="inlineStr"/>
       <c r="W10" s="6" t="inlineStr"/>
+      <c r="X10" s="6" t="inlineStr"/>
+      <c r="Y10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1207,37 +1213,41 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
           <t>SA</t>
         </is>
       </c>
-      <c r="H11" s="4" t="n">
+      <c r="I11" s="4" t="n">
         <v>16.5</v>
       </c>
-      <c r="I11" s="2" t="n">
+      <c r="J11" s="2" t="n">
         <v>3.3</v>
       </c>
-      <c r="J11" s="5" t="n">
+      <c r="K11" s="5" t="n">
         <v>0.2156</v>
       </c>
-      <c r="K11" s="5" t="inlineStr"/>
-      <c r="L11" s="5" t="n">
+      <c r="L11" s="5" t="inlineStr"/>
+      <c r="M11" s="5" t="n">
         <v>0.510590381447813</v>
       </c>
-      <c r="M11" s="5" t="n">
+      <c r="N11" s="5" t="n">
         <v>0.225784053085401</v>
       </c>
-      <c r="N11" s="5" t="n">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>per-DUID</t>
+        </is>
+      </c>
+      <c r="P11" s="5" t="n">
         <v>1.0257</v>
       </c>
-      <c r="O11" s="5" t="n">
+      <c r="Q11" s="5" t="n">
         <v>1.0134</v>
       </c>
-      <c r="P11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" s="6" t="n">
         <v>0</v>
       </c>
@@ -1254,6 +1264,12 @@
         <v>0</v>
       </c>
       <c r="W11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1290,35 +1306,39 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
           <t>SA</t>
         </is>
       </c>
-      <c r="H12" s="4" t="n">
+      <c r="I12" s="4" t="n">
         <v>16.5</v>
       </c>
-      <c r="I12" s="2" t="n">
+      <c r="J12" s="2" t="n">
         <v>3.3</v>
       </c>
-      <c r="J12" s="5" t="inlineStr"/>
       <c r="K12" s="5" t="inlineStr"/>
-      <c r="L12" s="5" t="n">
+      <c r="L12" s="5" t="inlineStr"/>
+      <c r="M12" s="5" t="n">
         <v>0.510590381447813</v>
       </c>
-      <c r="M12" s="5" t="n">
+      <c r="N12" s="5" t="n">
         <v>0.225784053085401</v>
       </c>
-      <c r="N12" s="5" t="n">
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>per-DUID</t>
+        </is>
+      </c>
+      <c r="P12" s="5" t="n">
         <v>1.0252</v>
       </c>
-      <c r="O12" s="5" t="n">
+      <c r="Q12" s="5" t="n">
         <v>1.0137</v>
       </c>
-      <c r="P12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" s="6" t="n">
         <v>0</v>
       </c>
@@ -1335,6 +1355,12 @@
         <v>0</v>
       </c>
       <c r="W12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1371,39 +1397,43 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
           <t>SA</t>
         </is>
       </c>
-      <c r="H13" s="4" t="n">
+      <c r="I13" s="4" t="n">
         <v>29.99</v>
       </c>
-      <c r="I13" s="2" t="n">
+      <c r="J13" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="J13" s="5" t="n">
+      <c r="K13" s="5" t="n">
         <v>0.3249</v>
       </c>
-      <c r="K13" s="5" t="n">
+      <c r="L13" s="5" t="n">
         <v>0.2807</v>
       </c>
-      <c r="L13" s="5" t="n">
+      <c r="M13" s="5" t="n">
         <v>0.510590381447813</v>
       </c>
-      <c r="M13" s="5" t="n">
+      <c r="N13" s="5" t="n">
         <v>0.225784053085401</v>
       </c>
-      <c r="N13" s="5" t="n">
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>per-DUID</t>
+        </is>
+      </c>
+      <c r="P13" s="5" t="n">
         <v>0.9932</v>
       </c>
-      <c r="O13" s="5" t="n">
+      <c r="Q13" s="5" t="n">
         <v>0.9959</v>
       </c>
-      <c r="P13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="R13" s="6" t="n">
         <v>0</v>
       </c>
@@ -1411,10 +1441,10 @@
         <v>0</v>
       </c>
       <c r="T13" s="6" t="n">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="U13" s="6" t="n">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="V13" s="6" t="n">
         <v>0.16</v>
@@ -1422,6 +1452,12 @@
       <c r="W13" s="6" t="n">
         <v>0.16</v>
       </c>
+      <c r="X13" s="6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Y13" s="6" t="n">
+        <v>0.16</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1456,39 +1492,43 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
           <t>SA</t>
         </is>
       </c>
-      <c r="H14" s="4" t="n">
+      <c r="I14" s="4" t="n">
         <v>5.5</v>
       </c>
-      <c r="I14" s="2" t="n">
+      <c r="J14" s="2" t="n">
         <v>3.3</v>
       </c>
-      <c r="J14" s="5" t="n">
+      <c r="K14" s="5" t="n">
         <v>0.2753</v>
       </c>
-      <c r="K14" s="5" t="n">
+      <c r="L14" s="5" t="n">
         <v>0.3888</v>
       </c>
-      <c r="L14" s="5" t="n">
+      <c r="M14" s="5" t="n">
         <v>0.65425629128861</v>
       </c>
-      <c r="M14" s="5" t="n">
+      <c r="N14" s="5" t="n">
         <v>0.512670422089759</v>
       </c>
-      <c r="N14" s="5" t="n">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>per-DUID</t>
+        </is>
+      </c>
+      <c r="P14" s="5" t="n">
         <v>1.0146</v>
       </c>
-      <c r="O14" s="5" t="n">
+      <c r="Q14" s="5" t="n">
         <v>0.9540999999999999</v>
       </c>
-      <c r="P14" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" s="6" t="n">
         <v>0</v>
       </c>
@@ -1496,10 +1536,10 @@
         <v>0</v>
       </c>
       <c r="T14" s="6" t="n">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="U14" s="6" t="n">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="V14" s="6" t="n">
         <v>0.16</v>
@@ -1507,6 +1547,12 @@
       <c r="W14" s="6" t="n">
         <v>0.16</v>
       </c>
+      <c r="X14" s="6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Y14" s="6" t="n">
+        <v>0.16</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1541,39 +1587,43 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
           <t>SA</t>
         </is>
       </c>
-      <c r="H15" s="4" t="n">
+      <c r="I15" s="4" t="n">
         <v>5.5</v>
       </c>
-      <c r="I15" s="2" t="n">
+      <c r="J15" s="2" t="n">
         <v>3.3</v>
       </c>
-      <c r="J15" s="5" t="n">
+      <c r="K15" s="5" t="n">
         <v>0.2707</v>
       </c>
-      <c r="K15" s="5" t="n">
+      <c r="L15" s="5" t="n">
         <v>0.3988</v>
       </c>
-      <c r="L15" s="5" t="n">
+      <c r="M15" s="5" t="n">
         <v>0.65425629128861</v>
       </c>
-      <c r="M15" s="5" t="n">
+      <c r="N15" s="5" t="n">
         <v>0.512670422089759</v>
       </c>
-      <c r="N15" s="5" t="n">
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>per-DUID</t>
+        </is>
+      </c>
+      <c r="P15" s="5" t="n">
         <v>1.003</v>
       </c>
-      <c r="O15" s="5" t="n">
+      <c r="Q15" s="5" t="n">
         <v>0.9664</v>
       </c>
-      <c r="P15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" s="6" t="n">
         <v>0</v>
       </c>
@@ -1581,10 +1631,10 @@
         <v>0</v>
       </c>
       <c r="T15" s="6" t="n">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="U15" s="6" t="n">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="V15" s="6" t="n">
         <v>0.16</v>
@@ -1592,6 +1642,12 @@
       <c r="W15" s="6" t="n">
         <v>0.16</v>
       </c>
+      <c r="X15" s="6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Y15" s="6" t="n">
+        <v>0.16</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1626,39 +1682,43 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
           <t>SA</t>
         </is>
       </c>
-      <c r="H16" s="4" t="n">
+      <c r="I16" s="4" t="n">
         <v>7.5</v>
       </c>
-      <c r="I16" s="2" t="n">
+      <c r="J16" s="2" t="n">
         <v>3.3</v>
       </c>
-      <c r="J16" s="5" t="n">
+      <c r="K16" s="5" t="n">
         <v>0.148</v>
       </c>
-      <c r="K16" s="5" t="n">
+      <c r="L16" s="5" t="n">
         <v>0.286</v>
       </c>
-      <c r="L16" s="5" t="n">
+      <c r="M16" s="5" t="n">
         <v>0.65425629128861</v>
       </c>
-      <c r="M16" s="5" t="n">
+      <c r="N16" s="5" t="n">
         <v>0.512670422089759</v>
       </c>
-      <c r="N16" s="5" t="n">
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>per-DUID</t>
+        </is>
+      </c>
+      <c r="P16" s="5" t="n">
         <v>0.9897</v>
       </c>
-      <c r="O16" s="5" t="n">
+      <c r="Q16" s="5" t="n">
         <v>0.9741</v>
       </c>
-      <c r="P16" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" s="6" t="n">
         <v>0</v>
       </c>
@@ -1666,10 +1726,10 @@
         <v>0</v>
       </c>
       <c r="T16" s="6" t="n">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="U16" s="6" t="n">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="V16" s="6" t="n">
         <v>0.16</v>
@@ -1677,6 +1737,12 @@
       <c r="W16" s="6" t="n">
         <v>0.16</v>
       </c>
+      <c r="X16" s="6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Y16" s="6" t="n">
+        <v>0.16</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1711,39 +1777,43 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
           <t>SA</t>
         </is>
       </c>
-      <c r="H17" s="4" t="n">
+      <c r="I17" s="4" t="n">
         <v>5.5</v>
       </c>
-      <c r="I17" s="2" t="n">
+      <c r="J17" s="2" t="n">
         <v>3.3</v>
       </c>
-      <c r="J17" s="5" t="n">
+      <c r="K17" s="5" t="n">
         <v>0.2332</v>
       </c>
-      <c r="K17" s="5" t="n">
+      <c r="L17" s="5" t="n">
         <v>0.3481</v>
       </c>
-      <c r="L17" s="5" t="n">
+      <c r="M17" s="5" t="n">
         <v>0.65425629128861</v>
       </c>
-      <c r="M17" s="5" t="n">
+      <c r="N17" s="5" t="n">
         <v>0.512670422089759</v>
       </c>
-      <c r="N17" s="5" t="n">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>per-DUID</t>
+        </is>
+      </c>
+      <c r="P17" s="5" t="n">
         <v>0.9837</v>
       </c>
-      <c r="O17" s="5" t="n">
+      <c r="Q17" s="5" t="n">
         <v>0.9772999999999999</v>
       </c>
-      <c r="P17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" s="6" t="n">
         <v>0</v>
       </c>
@@ -1751,10 +1821,10 @@
         <v>0</v>
       </c>
       <c r="T17" s="6" t="n">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="U17" s="6" t="n">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="V17" s="6" t="n">
         <v>0.16</v>
@@ -1762,6 +1832,12 @@
       <c r="W17" s="6" t="n">
         <v>0.16</v>
       </c>
+      <c r="X17" s="6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Y17" s="6" t="n">
+        <v>0.16</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1796,37 +1872,41 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
           <t>SA</t>
         </is>
       </c>
-      <c r="H18" s="4" t="n">
+      <c r="I18" s="4" t="n">
         <v>13.75</v>
       </c>
-      <c r="I18" s="2" t="n">
+      <c r="J18" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="J18" s="5" t="n">
+      <c r="K18" s="5" t="n">
         <v>0.2613</v>
       </c>
-      <c r="K18" s="5" t="inlineStr"/>
-      <c r="L18" s="5" t="n">
+      <c r="L18" s="5" t="inlineStr"/>
+      <c r="M18" s="5" t="n">
         <v>0.510590381447813</v>
       </c>
-      <c r="M18" s="5" t="n">
+      <c r="N18" s="5" t="n">
         <v>0.225784053085401</v>
       </c>
-      <c r="N18" s="5" t="n">
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>per-DUID</t>
+        </is>
+      </c>
+      <c r="P18" s="5" t="n">
         <v>1.0127</v>
       </c>
-      <c r="O18" s="5" t="n">
+      <c r="Q18" s="5" t="n">
         <v>1.011</v>
       </c>
-      <c r="P18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" s="6" t="n">
         <v>0</v>
       </c>
@@ -1843,6 +1923,12 @@
         <v>0</v>
       </c>
       <c r="W18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1879,39 +1965,43 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
           <t>SA</t>
         </is>
       </c>
-      <c r="H19" s="4" t="n">
+      <c r="I19" s="4" t="n">
         <v>79.2</v>
       </c>
-      <c r="I19" s="2" t="n">
+      <c r="J19" s="2" t="n">
         <v>275</v>
       </c>
-      <c r="J19" s="5" t="n">
+      <c r="K19" s="5" t="n">
         <v>0.4012</v>
       </c>
-      <c r="K19" s="5" t="n">
+      <c r="L19" s="5" t="n">
         <v>0.4797</v>
       </c>
-      <c r="L19" s="5" t="n">
+      <c r="M19" s="5" t="n">
         <v>0.501077617843089</v>
       </c>
-      <c r="M19" s="5" t="n">
+      <c r="N19" s="5" t="n">
         <v>0.212860651220515</v>
       </c>
-      <c r="N19" s="5" t="n">
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>per-DUID</t>
+        </is>
+      </c>
+      <c r="P19" s="5" t="n">
         <v>0.9735</v>
       </c>
-      <c r="O19" s="5" t="n">
+      <c r="Q19" s="5" t="n">
         <v>0.9709</v>
       </c>
-      <c r="P19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="R19" s="6" t="n">
         <v>0</v>
       </c>
@@ -1919,15 +2009,21 @@
         <v>0</v>
       </c>
       <c r="T19" s="6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="U19" s="6" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="V19" s="6" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="W19" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="X19" s="6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="Y19" s="6" t="n">
         <v>0.07333333333333335</v>
       </c>
     </row>
@@ -1964,41 +2060,51 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
           <t>SA</t>
         </is>
       </c>
-      <c r="H20" s="4" t="n">
+      <c r="I20" s="4" t="n">
         <v>105</v>
       </c>
-      <c r="I20" s="2" t="n">
+      <c r="J20" s="2" t="n">
         <v>132</v>
       </c>
-      <c r="J20" s="5" t="n">
+      <c r="K20" s="5" t="n">
         <v>0.3167</v>
       </c>
-      <c r="K20" s="5" t="n">
+      <c r="L20" s="5" t="n">
         <v>0.4573</v>
       </c>
-      <c r="L20" s="5" t="n">
+      <c r="M20" s="5" t="n">
         <v>0.511370986967519</v>
       </c>
-      <c r="M20" s="5" t="n">
+      <c r="N20" s="5" t="n">
         <v>0.22945882760626</v>
       </c>
-      <c r="N20" s="5" t="n">
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>per-DUID</t>
+        </is>
+      </c>
+      <c r="P20" s="5" t="n">
         <v>0.9945000000000001</v>
       </c>
-      <c r="O20" s="5" t="n">
+      <c r="Q20" s="5" t="n">
         <v>0.9968</v>
       </c>
-      <c r="P20" s="6" t="inlineStr"/>
-      <c r="Q20" s="6" t="inlineStr"/>
       <c r="R20" s="6" t="inlineStr"/>
       <c r="S20" s="6" t="inlineStr"/>
       <c r="T20" s="6" t="inlineStr"/>
       <c r="U20" s="6" t="inlineStr"/>
       <c r="V20" s="6" t="inlineStr"/>
       <c r="W20" s="6" t="inlineStr"/>
+      <c r="X20" s="6" t="inlineStr"/>
+      <c r="Y20" s="6" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -2033,41 +2139,51 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
           <t>SA</t>
         </is>
       </c>
-      <c r="H21" s="4" t="n">
+      <c r="I21" s="4" t="n">
         <v>108</v>
       </c>
-      <c r="I21" s="2" t="n">
+      <c r="J21" s="2" t="n">
         <v>132</v>
       </c>
-      <c r="J21" s="5" t="n">
+      <c r="K21" s="5" t="n">
         <v>0.384</v>
       </c>
-      <c r="K21" s="5" t="n">
+      <c r="L21" s="5" t="n">
         <v>0.5138</v>
       </c>
-      <c r="L21" s="5" t="n">
+      <c r="M21" s="5" t="n">
         <v>0.511370986967519</v>
       </c>
-      <c r="M21" s="5" t="n">
+      <c r="N21" s="5" t="n">
         <v>0.22945882760626</v>
       </c>
-      <c r="N21" s="5" t="n">
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>per-DUID</t>
+        </is>
+      </c>
+      <c r="P21" s="5" t="n">
         <v>0.9952</v>
       </c>
-      <c r="O21" s="5" t="n">
+      <c r="Q21" s="5" t="n">
         <v>0.9978</v>
       </c>
-      <c r="P21" s="6" t="inlineStr"/>
-      <c r="Q21" s="6" t="inlineStr"/>
       <c r="R21" s="6" t="inlineStr"/>
       <c r="S21" s="6" t="inlineStr"/>
       <c r="T21" s="6" t="inlineStr"/>
       <c r="U21" s="6" t="inlineStr"/>
       <c r="V21" s="6" t="inlineStr"/>
       <c r="W21" s="6" t="inlineStr"/>
+      <c r="X21" s="6" t="inlineStr"/>
+      <c r="Y21" s="6" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -2086,47 +2202,41 @@
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr"/>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr"/>
+      <c r="F22" s="3" t="inlineStr"/>
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>SA</t>
         </is>
       </c>
-      <c r="H22" s="4" t="n">
+      <c r="I22" s="4" t="n">
         <v>46</v>
       </c>
-      <c r="I22" s="2" t="inlineStr"/>
-      <c r="J22" s="5" t="n">
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="5" t="n">
         <v>0.2612</v>
       </c>
-      <c r="K22" s="5" t="n">
+      <c r="L22" s="5" t="n">
         <v>0.2954</v>
       </c>
-      <c r="L22" s="5" t="inlineStr"/>
       <c r="M22" s="5" t="inlineStr"/>
-      <c r="N22" s="5" t="n">
+      <c r="N22" s="5" t="inlineStr"/>
+      <c r="O22" s="2" t="inlineStr"/>
+      <c r="P22" s="5" t="n">
         <v>0.9333</v>
       </c>
-      <c r="O22" s="5" t="n">
+      <c r="Q22" s="5" t="n">
         <v>0.9527</v>
       </c>
-      <c r="P22" s="6" t="inlineStr"/>
-      <c r="Q22" s="6" t="inlineStr"/>
       <c r="R22" s="6" t="inlineStr"/>
       <c r="S22" s="6" t="inlineStr"/>
       <c r="T22" s="6" t="inlineStr"/>
       <c r="U22" s="6" t="inlineStr"/>
       <c r="V22" s="6" t="inlineStr"/>
       <c r="W22" s="6" t="inlineStr"/>
+      <c r="X22" s="6" t="inlineStr"/>
+      <c r="Y22" s="6" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -2145,47 +2255,41 @@
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr"/>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr"/>
+      <c r="F23" s="3" t="inlineStr"/>
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>SA</t>
         </is>
       </c>
-      <c r="H23" s="4" t="n">
+      <c r="I23" s="4" t="n">
         <v>66</v>
       </c>
-      <c r="I23" s="2" t="inlineStr"/>
-      <c r="J23" s="5" t="n">
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="5" t="n">
         <v>0.0518</v>
       </c>
-      <c r="K23" s="5" t="n">
+      <c r="L23" s="5" t="n">
         <v>0.0381</v>
       </c>
-      <c r="L23" s="5" t="inlineStr"/>
       <c r="M23" s="5" t="inlineStr"/>
-      <c r="N23" s="5" t="n">
+      <c r="N23" s="5" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr"/>
+      <c r="P23" s="5" t="n">
         <v>0.9467</v>
       </c>
-      <c r="O23" s="5" t="n">
+      <c r="Q23" s="5" t="n">
         <v>0.9417</v>
       </c>
-      <c r="P23" s="6" t="inlineStr"/>
-      <c r="Q23" s="6" t="inlineStr"/>
       <c r="R23" s="6" t="inlineStr"/>
       <c r="S23" s="6" t="inlineStr"/>
       <c r="T23" s="6" t="inlineStr"/>
       <c r="U23" s="6" t="inlineStr"/>
       <c r="V23" s="6" t="inlineStr"/>
       <c r="W23" s="6" t="inlineStr"/>
+      <c r="X23" s="6" t="inlineStr"/>
+      <c r="Y23" s="6" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -2204,47 +2308,41 @@
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr"/>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr"/>
+      <c r="F24" s="3" t="inlineStr"/>
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>SA</t>
         </is>
       </c>
-      <c r="H24" s="4" t="n">
+      <c r="I24" s="4" t="n">
         <v>57</v>
       </c>
-      <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" s="5" t="n">
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="5" t="n">
         <v>0.0062</v>
       </c>
-      <c r="K24" s="5" t="n">
+      <c r="L24" s="5" t="n">
         <v>0.0178</v>
       </c>
-      <c r="L24" s="5" t="inlineStr"/>
       <c r="M24" s="5" t="inlineStr"/>
-      <c r="N24" s="5" t="n">
+      <c r="N24" s="5" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr"/>
+      <c r="P24" s="5" t="n">
         <v>0.9604</v>
       </c>
-      <c r="O24" s="5" t="n">
+      <c r="Q24" s="5" t="n">
         <v>0.9614</v>
       </c>
-      <c r="P24" s="6" t="inlineStr"/>
-      <c r="Q24" s="6" t="inlineStr"/>
       <c r="R24" s="6" t="inlineStr"/>
       <c r="S24" s="6" t="inlineStr"/>
       <c r="T24" s="6" t="inlineStr"/>
       <c r="U24" s="6" t="inlineStr"/>
       <c r="V24" s="6" t="inlineStr"/>
       <c r="W24" s="6" t="inlineStr"/>
+      <c r="X24" s="6" t="inlineStr"/>
+      <c r="Y24" s="6" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -2263,47 +2361,41 @@
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr"/>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr"/>
+      <c r="F25" s="3" t="inlineStr"/>
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>SA</t>
         </is>
       </c>
-      <c r="H25" s="4" t="n">
+      <c r="I25" s="4" t="n">
         <v>209</v>
       </c>
-      <c r="I25" s="2" t="inlineStr"/>
-      <c r="J25" s="5" t="n">
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="5" t="n">
         <v>0.1796</v>
       </c>
-      <c r="K25" s="5" t="n">
+      <c r="L25" s="5" t="n">
         <v>0.094</v>
       </c>
-      <c r="L25" s="5" t="inlineStr"/>
       <c r="M25" s="5" t="inlineStr"/>
-      <c r="N25" s="5" t="n">
+      <c r="N25" s="5" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr"/>
+      <c r="P25" s="5" t="n">
         <v>0.9697</v>
       </c>
-      <c r="O25" s="5" t="n">
+      <c r="Q25" s="5" t="n">
         <v>0.9687</v>
       </c>
-      <c r="P25" s="6" t="inlineStr"/>
-      <c r="Q25" s="6" t="inlineStr"/>
       <c r="R25" s="6" t="inlineStr"/>
       <c r="S25" s="6" t="inlineStr"/>
       <c r="T25" s="6" t="inlineStr"/>
       <c r="U25" s="6" t="inlineStr"/>
       <c r="V25" s="6" t="inlineStr"/>
       <c r="W25" s="6" t="inlineStr"/>
+      <c r="X25" s="6" t="inlineStr"/>
+      <c r="Y25" s="6" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -2322,45 +2414,39 @@
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr"/>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr"/>
+      <c r="F26" s="3" t="inlineStr"/>
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>SA</t>
         </is>
       </c>
-      <c r="H26" s="4" t="n">
+      <c r="I26" s="4" t="n">
         <v>203</v>
       </c>
-      <c r="I26" s="2" t="inlineStr"/>
-      <c r="J26" s="5" t="inlineStr"/>
-      <c r="K26" s="5" t="n">
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="5" t="inlineStr"/>
+      <c r="L26" s="5" t="n">
         <v>0.2785</v>
       </c>
-      <c r="L26" s="5" t="inlineStr"/>
       <c r="M26" s="5" t="inlineStr"/>
-      <c r="N26" s="5" t="n">
+      <c r="N26" s="5" t="inlineStr"/>
+      <c r="O26" s="2" t="inlineStr"/>
+      <c r="P26" s="5" t="n">
         <v>0.9689</v>
       </c>
-      <c r="O26" s="5" t="n">
+      <c r="Q26" s="5" t="n">
         <v>0.9687</v>
       </c>
-      <c r="P26" s="6" t="inlineStr"/>
-      <c r="Q26" s="6" t="inlineStr"/>
       <c r="R26" s="6" t="inlineStr"/>
       <c r="S26" s="6" t="inlineStr"/>
       <c r="T26" s="6" t="inlineStr"/>
       <c r="U26" s="6" t="inlineStr"/>
       <c r="V26" s="6" t="inlineStr"/>
       <c r="W26" s="6" t="inlineStr"/>
+      <c r="X26" s="6" t="inlineStr"/>
+      <c r="Y26" s="6" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -2379,47 +2465,41 @@
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr"/>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr"/>
+      <c r="F27" s="3" t="inlineStr"/>
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>SA</t>
         </is>
       </c>
-      <c r="H27" s="4" t="n">
+      <c r="I27" s="4" t="n">
         <v>94.5</v>
       </c>
-      <c r="I27" s="2" t="inlineStr"/>
-      <c r="J27" s="5" t="n">
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="5" t="n">
         <v>0.1209</v>
       </c>
-      <c r="K27" s="5" t="n">
+      <c r="L27" s="5" t="n">
         <v>0.1935</v>
       </c>
-      <c r="L27" s="5" t="inlineStr"/>
       <c r="M27" s="5" t="inlineStr"/>
-      <c r="N27" s="5" t="n">
+      <c r="N27" s="5" t="inlineStr"/>
+      <c r="O27" s="2" t="inlineStr"/>
+      <c r="P27" s="5" t="n">
         <v>0.9663</v>
       </c>
-      <c r="O27" s="5" t="n">
+      <c r="Q27" s="5" t="n">
         <v>0.9628</v>
       </c>
-      <c r="P27" s="6" t="inlineStr"/>
-      <c r="Q27" s="6" t="inlineStr"/>
       <c r="R27" s="6" t="inlineStr"/>
       <c r="S27" s="6" t="inlineStr"/>
       <c r="T27" s="6" t="inlineStr"/>
       <c r="U27" s="6" t="inlineStr"/>
       <c r="V27" s="6" t="inlineStr"/>
       <c r="W27" s="6" t="inlineStr"/>
+      <c r="X27" s="6" t="inlineStr"/>
+      <c r="Y27" s="6" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2438,47 +2518,41 @@
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr"/>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr"/>
+      <c r="F28" s="3" t="inlineStr"/>
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>SA</t>
         </is>
       </c>
-      <c r="H28" s="4" t="n">
+      <c r="I28" s="4" t="n">
         <v>71.40000000000001</v>
       </c>
-      <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" s="5" t="n">
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="5" t="n">
         <v>0.1083</v>
       </c>
-      <c r="K28" s="5" t="n">
+      <c r="L28" s="5" t="n">
         <v>0.1916</v>
       </c>
-      <c r="L28" s="5" t="inlineStr"/>
       <c r="M28" s="5" t="inlineStr"/>
-      <c r="N28" s="5" t="n">
+      <c r="N28" s="5" t="inlineStr"/>
+      <c r="O28" s="2" t="inlineStr"/>
+      <c r="P28" s="5" t="n">
         <v>0.9608</v>
       </c>
-      <c r="O28" s="5" t="n">
+      <c r="Q28" s="5" t="n">
         <v>0.9606</v>
       </c>
-      <c r="P28" s="6" t="inlineStr"/>
-      <c r="Q28" s="6" t="inlineStr"/>
       <c r="R28" s="6" t="inlineStr"/>
       <c r="S28" s="6" t="inlineStr"/>
       <c r="T28" s="6" t="inlineStr"/>
       <c r="U28" s="6" t="inlineStr"/>
       <c r="V28" s="6" t="inlineStr"/>
       <c r="W28" s="6" t="inlineStr"/>
+      <c r="X28" s="6" t="inlineStr"/>
+      <c r="Y28" s="6" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -2497,47 +2571,41 @@
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr"/>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr"/>
+      <c r="F29" s="3" t="inlineStr"/>
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>SA</t>
         </is>
       </c>
-      <c r="H29" s="4" t="n">
+      <c r="I29" s="4" t="n">
         <v>102.4</v>
       </c>
-      <c r="I29" s="2" t="inlineStr"/>
-      <c r="J29" s="5" t="n">
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="5" t="n">
         <v>0.0034</v>
       </c>
-      <c r="K29" s="5" t="n">
+      <c r="L29" s="5" t="n">
         <v>0.0016</v>
       </c>
-      <c r="L29" s="5" t="inlineStr"/>
       <c r="M29" s="5" t="inlineStr"/>
-      <c r="N29" s="5" t="n">
+      <c r="N29" s="5" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr"/>
+      <c r="P29" s="5" t="n">
         <v>0.956</v>
       </c>
-      <c r="O29" s="5" t="n">
+      <c r="Q29" s="5" t="n">
         <v>0.9533</v>
       </c>
-      <c r="P29" s="6" t="inlineStr"/>
-      <c r="Q29" s="6" t="inlineStr"/>
       <c r="R29" s="6" t="inlineStr"/>
       <c r="S29" s="6" t="inlineStr"/>
       <c r="T29" s="6" t="inlineStr"/>
       <c r="U29" s="6" t="inlineStr"/>
       <c r="V29" s="6" t="inlineStr"/>
       <c r="W29" s="6" t="inlineStr"/>
+      <c r="X29" s="6" t="inlineStr"/>
+      <c r="Y29" s="6" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2556,47 +2624,41 @@
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr"/>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F30" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr"/>
+      <c r="F30" s="3" t="inlineStr"/>
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>SA</t>
         </is>
       </c>
-      <c r="H30" s="4" t="n">
+      <c r="I30" s="4" t="n">
         <v>102.4</v>
       </c>
-      <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" s="5" t="n">
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="5" t="n">
         <v>0.0038</v>
       </c>
-      <c r="K30" s="5" t="n">
+      <c r="L30" s="5" t="n">
         <v>0.0011</v>
       </c>
-      <c r="L30" s="5" t="inlineStr"/>
       <c r="M30" s="5" t="inlineStr"/>
-      <c r="N30" s="5" t="n">
+      <c r="N30" s="5" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr"/>
+      <c r="P30" s="5" t="n">
         <v>0.956</v>
       </c>
-      <c r="O30" s="5" t="n">
+      <c r="Q30" s="5" t="n">
         <v>0.9533</v>
       </c>
-      <c r="P30" s="6" t="inlineStr"/>
-      <c r="Q30" s="6" t="inlineStr"/>
       <c r="R30" s="6" t="inlineStr"/>
       <c r="S30" s="6" t="inlineStr"/>
       <c r="T30" s="6" t="inlineStr"/>
       <c r="U30" s="6" t="inlineStr"/>
       <c r="V30" s="6" t="inlineStr"/>
       <c r="W30" s="6" t="inlineStr"/>
+      <c r="X30" s="6" t="inlineStr"/>
+      <c r="Y30" s="6" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -2615,47 +2677,41 @@
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr"/>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr"/>
+      <c r="F31" s="3" t="inlineStr"/>
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>SA</t>
         </is>
       </c>
-      <c r="H31" s="4" t="n">
+      <c r="I31" s="4" t="n">
         <v>112</v>
       </c>
-      <c r="I31" s="2" t="inlineStr"/>
-      <c r="J31" s="5" t="n">
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="5" t="n">
         <v>0.0028</v>
       </c>
-      <c r="K31" s="5" t="n">
+      <c r="L31" s="5" t="n">
         <v>0.0015</v>
       </c>
-      <c r="L31" s="5" t="inlineStr"/>
       <c r="M31" s="5" t="inlineStr"/>
-      <c r="N31" s="5" t="n">
+      <c r="N31" s="5" t="inlineStr"/>
+      <c r="O31" s="2" t="inlineStr"/>
+      <c r="P31" s="5" t="n">
         <v>0.956</v>
       </c>
-      <c r="O31" s="5" t="n">
+      <c r="Q31" s="5" t="n">
         <v>0.9533</v>
       </c>
-      <c r="P31" s="6" t="inlineStr"/>
-      <c r="Q31" s="6" t="inlineStr"/>
       <c r="R31" s="6" t="inlineStr"/>
       <c r="S31" s="6" t="inlineStr"/>
       <c r="T31" s="6" t="inlineStr"/>
       <c r="U31" s="6" t="inlineStr"/>
       <c r="V31" s="6" t="inlineStr"/>
       <c r="W31" s="6" t="inlineStr"/>
+      <c r="X31" s="6" t="inlineStr"/>
+      <c r="Y31" s="6" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2674,47 +2730,41 @@
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr"/>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr"/>
+      <c r="F32" s="3" t="inlineStr"/>
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>SA</t>
         </is>
       </c>
-      <c r="H32" s="4" t="n">
+      <c r="I32" s="4" t="n">
         <v>159</v>
       </c>
-      <c r="I32" s="2" t="inlineStr"/>
-      <c r="J32" s="5" t="n">
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="5" t="n">
         <v>0.2</v>
       </c>
-      <c r="K32" s="5" t="n">
+      <c r="L32" s="5" t="n">
         <v>0.2497</v>
       </c>
-      <c r="L32" s="5" t="inlineStr"/>
       <c r="M32" s="5" t="inlineStr"/>
-      <c r="N32" s="5" t="n">
+      <c r="N32" s="5" t="inlineStr"/>
+      <c r="O32" s="2" t="inlineStr"/>
+      <c r="P32" s="5" t="n">
         <v>0.9297</v>
       </c>
-      <c r="O32" s="5" t="n">
+      <c r="Q32" s="5" t="n">
         <v>0.9468</v>
       </c>
-      <c r="P32" s="6" t="inlineStr"/>
-      <c r="Q32" s="6" t="inlineStr"/>
       <c r="R32" s="6" t="inlineStr"/>
       <c r="S32" s="6" t="inlineStr"/>
       <c r="T32" s="6" t="inlineStr"/>
       <c r="U32" s="6" t="inlineStr"/>
       <c r="V32" s="6" t="inlineStr"/>
       <c r="W32" s="6" t="inlineStr"/>
+      <c r="X32" s="6" t="inlineStr"/>
+      <c r="Y32" s="6" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -2733,47 +2783,41 @@
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr"/>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr"/>
+      <c r="F33" s="3" t="inlineStr"/>
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>SA</t>
         </is>
       </c>
-      <c r="H33" s="4" t="n">
+      <c r="I33" s="4" t="n">
         <v>39</v>
       </c>
-      <c r="I33" s="2" t="inlineStr"/>
-      <c r="J33" s="5" t="n">
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="5" t="n">
         <v>0.2652</v>
       </c>
-      <c r="K33" s="5" t="n">
+      <c r="L33" s="5" t="n">
         <v>0.2733</v>
       </c>
-      <c r="L33" s="5" t="inlineStr"/>
       <c r="M33" s="5" t="inlineStr"/>
-      <c r="N33" s="5" t="n">
+      <c r="N33" s="5" t="inlineStr"/>
+      <c r="O33" s="2" t="inlineStr"/>
+      <c r="P33" s="5" t="n">
         <v>0.9297</v>
       </c>
-      <c r="O33" s="5" t="n">
+      <c r="Q33" s="5" t="n">
         <v>0.9468</v>
       </c>
-      <c r="P33" s="6" t="inlineStr"/>
-      <c r="Q33" s="6" t="inlineStr"/>
       <c r="R33" s="6" t="inlineStr"/>
       <c r="S33" s="6" t="inlineStr"/>
       <c r="T33" s="6" t="inlineStr"/>
       <c r="U33" s="6" t="inlineStr"/>
       <c r="V33" s="6" t="inlineStr"/>
       <c r="W33" s="6" t="inlineStr"/>
+      <c r="X33" s="6" t="inlineStr"/>
+      <c r="Y33" s="6" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -2792,47 +2836,41 @@
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr"/>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F34" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr"/>
+      <c r="F34" s="3" t="inlineStr"/>
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>SA</t>
         </is>
       </c>
-      <c r="H34" s="4" t="n">
+      <c r="I34" s="4" t="n">
         <v>80.5</v>
       </c>
-      <c r="I34" s="2" t="inlineStr"/>
-      <c r="J34" s="5" t="n">
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="5" t="n">
         <v>0.2637</v>
       </c>
-      <c r="K34" s="5" t="n">
+      <c r="L34" s="5" t="n">
         <v>0.3006</v>
       </c>
-      <c r="L34" s="5" t="inlineStr"/>
       <c r="M34" s="5" t="inlineStr"/>
-      <c r="N34" s="5" t="n">
+      <c r="N34" s="5" t="inlineStr"/>
+      <c r="O34" s="2" t="inlineStr"/>
+      <c r="P34" s="5" t="n">
         <v>0.9297</v>
       </c>
-      <c r="O34" s="5" t="n">
+      <c r="Q34" s="5" t="n">
         <v>0.9468</v>
       </c>
-      <c r="P34" s="6" t="inlineStr"/>
-      <c r="Q34" s="6" t="inlineStr"/>
       <c r="R34" s="6" t="inlineStr"/>
       <c r="S34" s="6" t="inlineStr"/>
       <c r="T34" s="6" t="inlineStr"/>
       <c r="U34" s="6" t="inlineStr"/>
       <c r="V34" s="6" t="inlineStr"/>
       <c r="W34" s="6" t="inlineStr"/>
+      <c r="X34" s="6" t="inlineStr"/>
+      <c r="Y34" s="6" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -2851,47 +2889,41 @@
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr"/>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr"/>
+      <c r="F35" s="3" t="inlineStr"/>
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>SA</t>
         </is>
       </c>
-      <c r="H35" s="4" t="n">
+      <c r="I35" s="4" t="n">
         <v>126</v>
       </c>
-      <c r="I35" s="2" t="inlineStr"/>
-      <c r="J35" s="5" t="n">
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="5" t="n">
         <v>0.1458</v>
       </c>
-      <c r="K35" s="5" t="n">
+      <c r="L35" s="5" t="n">
         <v>0.1783</v>
       </c>
-      <c r="L35" s="5" t="inlineStr"/>
       <c r="M35" s="5" t="inlineStr"/>
-      <c r="N35" s="5" t="n">
+      <c r="N35" s="5" t="inlineStr"/>
+      <c r="O35" s="2" t="inlineStr"/>
+      <c r="P35" s="5" t="n">
         <v>0.9689</v>
       </c>
-      <c r="O35" s="5" t="n">
+      <c r="Q35" s="5" t="n">
         <v>0.9661</v>
       </c>
-      <c r="P35" s="6" t="inlineStr"/>
-      <c r="Q35" s="6" t="inlineStr"/>
       <c r="R35" s="6" t="inlineStr"/>
       <c r="S35" s="6" t="inlineStr"/>
       <c r="T35" s="6" t="inlineStr"/>
       <c r="U35" s="6" t="inlineStr"/>
       <c r="V35" s="6" t="inlineStr"/>
       <c r="W35" s="6" t="inlineStr"/>
+      <c r="X35" s="6" t="inlineStr"/>
+      <c r="Y35" s="6" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -2910,47 +2942,41 @@
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr"/>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F36" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr"/>
+      <c r="F36" s="3" t="inlineStr"/>
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>SA</t>
         </is>
       </c>
-      <c r="H36" s="4" t="n">
+      <c r="I36" s="4" t="n">
         <v>86</v>
       </c>
-      <c r="I36" s="2" t="inlineStr"/>
-      <c r="J36" s="5" t="n">
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="5" t="n">
         <v>0.1653</v>
       </c>
-      <c r="K36" s="5" t="n">
+      <c r="L36" s="5" t="n">
         <v>0.1995</v>
       </c>
-      <c r="L36" s="5" t="inlineStr"/>
       <c r="M36" s="5" t="inlineStr"/>
-      <c r="N36" s="5" t="n">
+      <c r="N36" s="5" t="inlineStr"/>
+      <c r="O36" s="2" t="inlineStr"/>
+      <c r="P36" s="5" t="n">
         <v>0.9689</v>
       </c>
-      <c r="O36" s="5" t="n">
+      <c r="Q36" s="5" t="n">
         <v>0.9661</v>
       </c>
-      <c r="P36" s="6" t="inlineStr"/>
-      <c r="Q36" s="6" t="inlineStr"/>
       <c r="R36" s="6" t="inlineStr"/>
       <c r="S36" s="6" t="inlineStr"/>
       <c r="T36" s="6" t="inlineStr"/>
       <c r="U36" s="6" t="inlineStr"/>
       <c r="V36" s="6" t="inlineStr"/>
       <c r="W36" s="6" t="inlineStr"/>
+      <c r="X36" s="6" t="inlineStr"/>
+      <c r="Y36" s="6" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -2969,47 +2995,41 @@
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr"/>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F37" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr"/>
+      <c r="F37" s="3" t="inlineStr"/>
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>SA</t>
         </is>
       </c>
-      <c r="H37" s="4" t="n">
+      <c r="I37" s="4" t="n">
         <v>70</v>
       </c>
-      <c r="I37" s="2" t="inlineStr"/>
-      <c r="J37" s="5" t="n">
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="5" t="n">
         <v>0.3052</v>
       </c>
-      <c r="K37" s="5" t="n">
+      <c r="L37" s="5" t="n">
         <v>0.1511</v>
       </c>
-      <c r="L37" s="5" t="inlineStr"/>
       <c r="M37" s="5" t="inlineStr"/>
-      <c r="N37" s="5" t="n">
+      <c r="N37" s="5" t="inlineStr"/>
+      <c r="O37" s="2" t="inlineStr"/>
+      <c r="P37" s="5" t="n">
         <v>0.9403</v>
       </c>
-      <c r="O37" s="5" t="n">
+      <c r="Q37" s="5" t="n">
         <v>0.9387</v>
       </c>
-      <c r="P37" s="6" t="inlineStr"/>
-      <c r="Q37" s="6" t="inlineStr"/>
       <c r="R37" s="6" t="inlineStr"/>
       <c r="S37" s="6" t="inlineStr"/>
       <c r="T37" s="6" t="inlineStr"/>
       <c r="U37" s="6" t="inlineStr"/>
       <c r="V37" s="6" t="inlineStr"/>
       <c r="W37" s="6" t="inlineStr"/>
+      <c r="X37" s="6" t="inlineStr"/>
+      <c r="Y37" s="6" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -3028,47 +3048,41 @@
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr"/>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F38" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr"/>
+      <c r="F38" s="3" t="inlineStr"/>
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>SA</t>
         </is>
       </c>
-      <c r="H38" s="4" t="n">
+      <c r="I38" s="4" t="n">
         <v>132.3</v>
       </c>
-      <c r="I38" s="2" t="inlineStr"/>
-      <c r="J38" s="5" t="n">
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="5" t="n">
         <v>0.1223</v>
       </c>
-      <c r="K38" s="5" t="n">
+      <c r="L38" s="5" t="n">
         <v>0.1729</v>
       </c>
-      <c r="L38" s="5" t="inlineStr"/>
       <c r="M38" s="5" t="inlineStr"/>
-      <c r="N38" s="5" t="n">
+      <c r="N38" s="5" t="inlineStr"/>
+      <c r="O38" s="2" t="inlineStr"/>
+      <c r="P38" s="5" t="n">
         <v>0.9579</v>
       </c>
-      <c r="O38" s="5" t="n">
+      <c r="Q38" s="5" t="n">
         <v>0.9572000000000001</v>
       </c>
-      <c r="P38" s="6" t="inlineStr"/>
-      <c r="Q38" s="6" t="inlineStr"/>
       <c r="R38" s="6" t="inlineStr"/>
       <c r="S38" s="6" t="inlineStr"/>
       <c r="T38" s="6" t="inlineStr"/>
       <c r="U38" s="6" t="inlineStr"/>
       <c r="V38" s="6" t="inlineStr"/>
       <c r="W38" s="6" t="inlineStr"/>
+      <c r="X38" s="6" t="inlineStr"/>
+      <c r="Y38" s="6" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -3087,47 +3101,41 @@
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr"/>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr"/>
+      <c r="F39" s="3" t="inlineStr"/>
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>SA</t>
         </is>
       </c>
-      <c r="H39" s="4" t="n">
+      <c r="I39" s="4" t="n">
         <v>210</v>
       </c>
-      <c r="I39" s="2" t="inlineStr"/>
-      <c r="J39" s="5" t="n">
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="5" t="n">
         <v>0.1999</v>
       </c>
-      <c r="K39" s="5" t="n">
+      <c r="L39" s="5" t="n">
         <v>0.2153</v>
       </c>
-      <c r="L39" s="5" t="inlineStr"/>
       <c r="M39" s="5" t="inlineStr"/>
-      <c r="N39" s="5" t="n">
+      <c r="N39" s="5" t="inlineStr"/>
+      <c r="O39" s="2" t="inlineStr"/>
+      <c r="P39" s="5" t="n">
         <v>0.9735</v>
       </c>
-      <c r="O39" s="5" t="n">
+      <c r="Q39" s="5" t="n">
         <v>0.9709</v>
       </c>
-      <c r="P39" s="6" t="inlineStr"/>
-      <c r="Q39" s="6" t="inlineStr"/>
       <c r="R39" s="6" t="inlineStr"/>
       <c r="S39" s="6" t="inlineStr"/>
       <c r="T39" s="6" t="inlineStr"/>
       <c r="U39" s="6" t="inlineStr"/>
       <c r="V39" s="6" t="inlineStr"/>
       <c r="W39" s="6" t="inlineStr"/>
+      <c r="X39" s="6" t="inlineStr"/>
+      <c r="Y39" s="6" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -3146,47 +3154,41 @@
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr"/>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F40" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr"/>
+      <c r="F40" s="3" t="inlineStr"/>
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>SA</t>
         </is>
       </c>
-      <c r="H40" s="4" t="n">
+      <c r="I40" s="4" t="n">
         <v>126</v>
       </c>
-      <c r="I40" s="2" t="inlineStr"/>
-      <c r="J40" s="5" t="n">
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="5" t="n">
         <v>0.0037</v>
       </c>
-      <c r="K40" s="5" t="n">
+      <c r="L40" s="5" t="n">
         <v>0.0022</v>
       </c>
-      <c r="L40" s="5" t="inlineStr"/>
       <c r="M40" s="5" t="inlineStr"/>
-      <c r="N40" s="5" t="n">
+      <c r="N40" s="5" t="inlineStr"/>
+      <c r="O40" s="2" t="inlineStr"/>
+      <c r="P40" s="5" t="n">
         <v>0.9695</v>
       </c>
-      <c r="O40" s="5" t="n">
+      <c r="Q40" s="5" t="n">
         <v>0.9699</v>
       </c>
-      <c r="P40" s="6" t="inlineStr"/>
-      <c r="Q40" s="6" t="inlineStr"/>
       <c r="R40" s="6" t="inlineStr"/>
       <c r="S40" s="6" t="inlineStr"/>
       <c r="T40" s="6" t="inlineStr"/>
       <c r="U40" s="6" t="inlineStr"/>
       <c r="V40" s="6" t="inlineStr"/>
       <c r="W40" s="6" t="inlineStr"/>
+      <c r="X40" s="6" t="inlineStr"/>
+      <c r="Y40" s="6" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -3205,47 +3207,41 @@
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr"/>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F41" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr"/>
+      <c r="F41" s="3" t="inlineStr"/>
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>SA</t>
         </is>
       </c>
-      <c r="H41" s="4" t="n">
+      <c r="I41" s="4" t="n">
         <v>144</v>
       </c>
-      <c r="I41" s="2" t="inlineStr"/>
-      <c r="J41" s="5" t="n">
-        <v>0.0027</v>
-      </c>
+      <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="5" t="n">
         <v>0.0027</v>
       </c>
-      <c r="L41" s="5" t="inlineStr"/>
+      <c r="L41" s="5" t="n">
+        <v>0.0027</v>
+      </c>
       <c r="M41" s="5" t="inlineStr"/>
-      <c r="N41" s="5" t="n">
+      <c r="N41" s="5" t="inlineStr"/>
+      <c r="O41" s="2" t="inlineStr"/>
+      <c r="P41" s="5" t="n">
         <v>0.9695</v>
       </c>
-      <c r="O41" s="5" t="n">
+      <c r="Q41" s="5" t="n">
         <v>0.9699</v>
       </c>
-      <c r="P41" s="6" t="inlineStr"/>
-      <c r="Q41" s="6" t="inlineStr"/>
       <c r="R41" s="6" t="inlineStr"/>
       <c r="S41" s="6" t="inlineStr"/>
       <c r="T41" s="6" t="inlineStr"/>
       <c r="U41" s="6" t="inlineStr"/>
       <c r="V41" s="6" t="inlineStr"/>
       <c r="W41" s="6" t="inlineStr"/>
+      <c r="X41" s="6" t="inlineStr"/>
+      <c r="Y41" s="6" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -3264,47 +3260,41 @@
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr"/>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F42" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr"/>
+      <c r="F42" s="3" t="inlineStr"/>
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>SA</t>
         </is>
       </c>
-      <c r="H42" s="4" t="n">
+      <c r="I42" s="4" t="n">
         <v>99</v>
       </c>
-      <c r="I42" s="2" t="inlineStr"/>
-      <c r="J42" s="5" t="n">
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="5" t="n">
         <v>0.1863</v>
       </c>
-      <c r="K42" s="5" t="n">
+      <c r="L42" s="5" t="n">
         <v>0.2696</v>
       </c>
-      <c r="L42" s="5" t="inlineStr"/>
       <c r="M42" s="5" t="inlineStr"/>
-      <c r="N42" s="5" t="n">
+      <c r="N42" s="5" t="inlineStr"/>
+      <c r="O42" s="2" t="inlineStr"/>
+      <c r="P42" s="5" t="n">
         <v>0.9157</v>
       </c>
-      <c r="O42" s="5" t="n">
+      <c r="Q42" s="5" t="n">
         <v>0.9132</v>
       </c>
-      <c r="P42" s="6" t="inlineStr"/>
-      <c r="Q42" s="6" t="inlineStr"/>
       <c r="R42" s="6" t="inlineStr"/>
       <c r="S42" s="6" t="inlineStr"/>
       <c r="T42" s="6" t="inlineStr"/>
       <c r="U42" s="6" t="inlineStr"/>
       <c r="V42" s="6" t="inlineStr"/>
       <c r="W42" s="6" t="inlineStr"/>
+      <c r="X42" s="6" t="inlineStr"/>
+      <c r="Y42" s="6" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -3323,47 +3313,41 @@
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr"/>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F43" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr"/>
+      <c r="F43" s="3" t="inlineStr"/>
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>SA</t>
         </is>
       </c>
-      <c r="H43" s="4" t="n">
+      <c r="I43" s="4" t="n">
         <v>34.5</v>
       </c>
-      <c r="I43" s="2" t="inlineStr"/>
-      <c r="J43" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="L43" s="5" t="inlineStr"/>
+      <c r="L43" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="M43" s="5" t="inlineStr"/>
-      <c r="N43" s="5" t="n">
+      <c r="N43" s="5" t="inlineStr"/>
+      <c r="O43" s="2" t="inlineStr"/>
+      <c r="P43" s="5" t="n">
         <v>1.0037</v>
       </c>
-      <c r="O43" s="5" t="n">
+      <c r="Q43" s="5" t="n">
         <v>1.0033</v>
       </c>
-      <c r="P43" s="6" t="inlineStr"/>
-      <c r="Q43" s="6" t="inlineStr"/>
       <c r="R43" s="6" t="inlineStr"/>
       <c r="S43" s="6" t="inlineStr"/>
       <c r="T43" s="6" t="inlineStr"/>
       <c r="U43" s="6" t="inlineStr"/>
       <c r="V43" s="6" t="inlineStr"/>
       <c r="W43" s="6" t="inlineStr"/>
+      <c r="X43" s="6" t="inlineStr"/>
+      <c r="Y43" s="6" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -3382,47 +3366,41 @@
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr"/>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F44" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr"/>
+      <c r="F44" s="3" t="inlineStr"/>
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>SA</t>
         </is>
       </c>
-      <c r="H44" s="4" t="n">
+      <c r="I44" s="4" t="n">
         <v>52.5</v>
       </c>
-      <c r="I44" s="2" t="inlineStr"/>
-      <c r="J44" s="5" t="n">
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="5" t="n">
         <v>0.0906</v>
       </c>
-      <c r="K44" s="5" t="n">
+      <c r="L44" s="5" t="n">
         <v>0.1905</v>
       </c>
-      <c r="L44" s="5" t="inlineStr"/>
       <c r="M44" s="5" t="inlineStr"/>
-      <c r="N44" s="5" t="n">
+      <c r="N44" s="5" t="inlineStr"/>
+      <c r="O44" s="2" t="inlineStr"/>
+      <c r="P44" s="5" t="n">
         <v>0.9579</v>
       </c>
-      <c r="O44" s="5" t="n">
+      <c r="Q44" s="5" t="n">
         <v>0.9572000000000001</v>
       </c>
-      <c r="P44" s="6" t="inlineStr"/>
-      <c r="Q44" s="6" t="inlineStr"/>
       <c r="R44" s="6" t="inlineStr"/>
       <c r="S44" s="6" t="inlineStr"/>
       <c r="T44" s="6" t="inlineStr"/>
       <c r="U44" s="6" t="inlineStr"/>
       <c r="V44" s="6" t="inlineStr"/>
       <c r="W44" s="6" t="inlineStr"/>
+      <c r="X44" s="6" t="inlineStr"/>
+      <c r="Y44" s="6" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -3441,47 +3419,41 @@
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr"/>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F45" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr"/>
+      <c r="F45" s="3" t="inlineStr"/>
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>SA</t>
         </is>
       </c>
-      <c r="H45" s="4" t="n">
+      <c r="I45" s="4" t="n">
         <v>130.8</v>
       </c>
-      <c r="I45" s="2" t="inlineStr"/>
-      <c r="J45" s="5" t="n">
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="5" t="n">
         <v>0.0206</v>
       </c>
-      <c r="K45" s="5" t="n">
+      <c r="L45" s="5" t="n">
         <v>0.0121</v>
       </c>
-      <c r="L45" s="5" t="inlineStr"/>
       <c r="M45" s="5" t="inlineStr"/>
-      <c r="N45" s="5" t="n">
+      <c r="N45" s="5" t="inlineStr"/>
+      <c r="O45" s="2" t="inlineStr"/>
+      <c r="P45" s="5" t="n">
         <v>0.9624</v>
       </c>
-      <c r="O45" s="5" t="n">
+      <c r="Q45" s="5" t="n">
         <v>0.9611</v>
       </c>
-      <c r="P45" s="6" t="inlineStr"/>
-      <c r="Q45" s="6" t="inlineStr"/>
       <c r="R45" s="6" t="inlineStr"/>
       <c r="S45" s="6" t="inlineStr"/>
       <c r="T45" s="6" t="inlineStr"/>
       <c r="U45" s="6" t="inlineStr"/>
       <c r="V45" s="6" t="inlineStr"/>
       <c r="W45" s="6" t="inlineStr"/>
+      <c r="X45" s="6" t="inlineStr"/>
+      <c r="Y45" s="6" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -3500,47 +3472,41 @@
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr"/>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F46" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr"/>
+      <c r="F46" s="3" t="inlineStr"/>
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>SA</t>
         </is>
       </c>
-      <c r="H46" s="4" t="n">
+      <c r="I46" s="4" t="n">
         <v>90.75</v>
       </c>
-      <c r="I46" s="2" t="inlineStr"/>
-      <c r="J46" s="5" t="n">
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="5" t="n">
         <v>0.1686</v>
       </c>
-      <c r="K46" s="5" t="n">
+      <c r="L46" s="5" t="n">
         <v>0.2013</v>
       </c>
-      <c r="L46" s="5" t="inlineStr"/>
       <c r="M46" s="5" t="inlineStr"/>
-      <c r="N46" s="5" t="n">
+      <c r="N46" s="5" t="inlineStr"/>
+      <c r="O46" s="2" t="inlineStr"/>
+      <c r="P46" s="5" t="n">
         <v>0.8456</v>
       </c>
-      <c r="O46" s="5" t="n">
+      <c r="Q46" s="5" t="n">
         <v>0.8476</v>
       </c>
-      <c r="P46" s="6" t="inlineStr"/>
-      <c r="Q46" s="6" t="inlineStr"/>
       <c r="R46" s="6" t="inlineStr"/>
       <c r="S46" s="6" t="inlineStr"/>
       <c r="T46" s="6" t="inlineStr"/>
       <c r="U46" s="6" t="inlineStr"/>
       <c r="V46" s="6" t="inlineStr"/>
       <c r="W46" s="6" t="inlineStr"/>
+      <c r="X46" s="6" t="inlineStr"/>
+      <c r="Y46" s="6" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -3559,47 +3525,41 @@
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr"/>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F47" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr"/>
+      <c r="F47" s="3" t="inlineStr"/>
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>SA</t>
         </is>
       </c>
-      <c r="H47" s="4" t="n">
+      <c r="I47" s="4" t="n">
         <v>122</v>
       </c>
-      <c r="I47" s="2" t="inlineStr"/>
-      <c r="J47" s="5" t="n">
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="5" t="n">
         <v>0.0432</v>
       </c>
-      <c r="K47" s="5" t="n">
+      <c r="L47" s="5" t="n">
         <v>0.0341</v>
       </c>
-      <c r="L47" s="5" t="inlineStr"/>
       <c r="M47" s="5" t="inlineStr"/>
-      <c r="N47" s="5" t="n">
+      <c r="N47" s="5" t="inlineStr"/>
+      <c r="O47" s="2" t="inlineStr"/>
+      <c r="P47" s="5" t="n">
         <v>0.9601</v>
       </c>
-      <c r="O47" s="5" t="n">
+      <c r="Q47" s="5" t="n">
         <v>0.9592000000000001</v>
       </c>
-      <c r="P47" s="6" t="inlineStr"/>
-      <c r="Q47" s="6" t="inlineStr"/>
       <c r="R47" s="6" t="inlineStr"/>
       <c r="S47" s="6" t="inlineStr"/>
       <c r="T47" s="6" t="inlineStr"/>
       <c r="U47" s="6" t="inlineStr"/>
       <c r="V47" s="6" t="inlineStr"/>
       <c r="W47" s="6" t="inlineStr"/>
+      <c r="X47" s="6" t="inlineStr"/>
+      <c r="Y47" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3775,42 +3735,18 @@
       <c r="G2" s="5" t="inlineStr"/>
       <c r="H2" s="5" t="inlineStr"/>
       <c r="I2" s="5" t="inlineStr"/>
-      <c r="J2" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J2" s="5" t="inlineStr"/>
       <c r="K2" s="5" t="inlineStr"/>
-      <c r="L2" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L2" s="5" t="inlineStr"/>
       <c r="M2" s="5" t="inlineStr"/>
-      <c r="N2" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N2" s="5" t="inlineStr"/>
       <c r="O2" s="5" t="inlineStr"/>
       <c r="P2" s="5" t="inlineStr"/>
-      <c r="Q2" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q2" s="5" t="inlineStr"/>
       <c r="R2" s="5" t="inlineStr"/>
-      <c r="S2" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S2" s="5" t="inlineStr"/>
       <c r="T2" s="5" t="inlineStr"/>
-      <c r="U2" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U2" s="5" t="inlineStr"/>
       <c r="V2" s="5" t="inlineStr"/>
     </row>
     <row r="3">
@@ -3835,42 +3771,18 @@
       <c r="G3" s="5" t="inlineStr"/>
       <c r="H3" s="5" t="inlineStr"/>
       <c r="I3" s="5" t="inlineStr"/>
-      <c r="J3" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J3" s="5" t="inlineStr"/>
       <c r="K3" s="5" t="inlineStr"/>
-      <c r="L3" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L3" s="5" t="inlineStr"/>
       <c r="M3" s="5" t="inlineStr"/>
-      <c r="N3" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N3" s="5" t="inlineStr"/>
       <c r="O3" s="5" t="inlineStr"/>
       <c r="P3" s="5" t="inlineStr"/>
-      <c r="Q3" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q3" s="5" t="inlineStr"/>
       <c r="R3" s="5" t="inlineStr"/>
-      <c r="S3" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S3" s="5" t="inlineStr"/>
       <c r="T3" s="5" t="inlineStr"/>
-      <c r="U3" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U3" s="5" t="inlineStr"/>
       <c r="V3" s="5" t="inlineStr"/>
     </row>
     <row r="4">
@@ -3895,42 +3807,18 @@
       <c r="G4" s="5" t="inlineStr"/>
       <c r="H4" s="5" t="inlineStr"/>
       <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J4" s="5" t="inlineStr"/>
       <c r="K4" s="5" t="inlineStr"/>
-      <c r="L4" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L4" s="5" t="inlineStr"/>
       <c r="M4" s="5" t="inlineStr"/>
-      <c r="N4" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N4" s="5" t="inlineStr"/>
       <c r="O4" s="5" t="inlineStr"/>
       <c r="P4" s="5" t="inlineStr"/>
-      <c r="Q4" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q4" s="5" t="inlineStr"/>
       <c r="R4" s="5" t="inlineStr"/>
-      <c r="S4" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S4" s="5" t="inlineStr"/>
       <c r="T4" s="5" t="inlineStr"/>
-      <c r="U4" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U4" s="5" t="inlineStr"/>
       <c r="V4" s="5" t="inlineStr"/>
     </row>
     <row r="5">
@@ -3959,42 +3847,18 @@
       <c r="G5" s="5" t="inlineStr"/>
       <c r="H5" s="5" t="inlineStr"/>
       <c r="I5" s="5" t="inlineStr"/>
-      <c r="J5" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J5" s="5" t="inlineStr"/>
       <c r="K5" s="5" t="inlineStr"/>
-      <c r="L5" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L5" s="5" t="inlineStr"/>
       <c r="M5" s="5" t="inlineStr"/>
-      <c r="N5" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N5" s="5" t="inlineStr"/>
       <c r="O5" s="5" t="inlineStr"/>
       <c r="P5" s="5" t="inlineStr"/>
-      <c r="Q5" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q5" s="5" t="inlineStr"/>
       <c r="R5" s="5" t="inlineStr"/>
-      <c r="S5" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S5" s="5" t="inlineStr"/>
       <c r="T5" s="5" t="inlineStr"/>
-      <c r="U5" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U5" s="5" t="inlineStr"/>
       <c r="V5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
@@ -4185,42 +4049,18 @@
       <c r="G8" s="5" t="inlineStr"/>
       <c r="H8" s="5" t="inlineStr"/>
       <c r="I8" s="5" t="inlineStr"/>
-      <c r="J8" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J8" s="5" t="inlineStr"/>
       <c r="K8" s="5" t="inlineStr"/>
-      <c r="L8" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L8" s="5" t="inlineStr"/>
       <c r="M8" s="5" t="inlineStr"/>
-      <c r="N8" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N8" s="5" t="inlineStr"/>
       <c r="O8" s="5" t="inlineStr"/>
       <c r="P8" s="5" t="inlineStr"/>
-      <c r="Q8" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q8" s="5" t="inlineStr"/>
       <c r="R8" s="5" t="inlineStr"/>
-      <c r="S8" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S8" s="5" t="inlineStr"/>
       <c r="T8" s="5" t="inlineStr"/>
-      <c r="U8" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U8" s="5" t="inlineStr"/>
       <c r="V8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
@@ -4245,42 +4085,18 @@
       <c r="G9" s="5" t="inlineStr"/>
       <c r="H9" s="5" t="inlineStr"/>
       <c r="I9" s="5" t="inlineStr"/>
-      <c r="J9" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J9" s="5" t="inlineStr"/>
       <c r="K9" s="5" t="inlineStr"/>
-      <c r="L9" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L9" s="5" t="inlineStr"/>
       <c r="M9" s="5" t="inlineStr"/>
-      <c r="N9" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N9" s="5" t="inlineStr"/>
       <c r="O9" s="5" t="inlineStr"/>
       <c r="P9" s="5" t="inlineStr"/>
-      <c r="Q9" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q9" s="5" t="inlineStr"/>
       <c r="R9" s="5" t="inlineStr"/>
-      <c r="S9" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S9" s="5" t="inlineStr"/>
       <c r="T9" s="5" t="inlineStr"/>
-      <c r="U9" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U9" s="5" t="inlineStr"/>
       <c r="V9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
@@ -5261,42 +5077,18 @@
       <c r="G22" s="5" t="inlineStr"/>
       <c r="H22" s="5" t="inlineStr"/>
       <c r="I22" s="5" t="inlineStr"/>
-      <c r="J22" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J22" s="5" t="inlineStr"/>
       <c r="K22" s="5" t="inlineStr"/>
-      <c r="L22" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L22" s="5" t="inlineStr"/>
       <c r="M22" s="5" t="inlineStr"/>
-      <c r="N22" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N22" s="5" t="inlineStr"/>
       <c r="O22" s="5" t="inlineStr"/>
       <c r="P22" s="5" t="inlineStr"/>
-      <c r="Q22" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q22" s="5" t="inlineStr"/>
       <c r="R22" s="5" t="inlineStr"/>
-      <c r="S22" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S22" s="5" t="inlineStr"/>
       <c r="T22" s="5" t="inlineStr"/>
-      <c r="U22" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U22" s="5" t="inlineStr"/>
       <c r="V22" s="5" t="inlineStr"/>
     </row>
     <row r="23">
@@ -5325,42 +5117,18 @@
       <c r="G23" s="5" t="inlineStr"/>
       <c r="H23" s="5" t="inlineStr"/>
       <c r="I23" s="5" t="inlineStr"/>
-      <c r="J23" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J23" s="5" t="inlineStr"/>
       <c r="K23" s="5" t="inlineStr"/>
-      <c r="L23" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L23" s="5" t="inlineStr"/>
       <c r="M23" s="5" t="inlineStr"/>
-      <c r="N23" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N23" s="5" t="inlineStr"/>
       <c r="O23" s="5" t="inlineStr"/>
       <c r="P23" s="5" t="inlineStr"/>
-      <c r="Q23" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q23" s="5" t="inlineStr"/>
       <c r="R23" s="5" t="inlineStr"/>
-      <c r="S23" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S23" s="5" t="inlineStr"/>
       <c r="T23" s="5" t="inlineStr"/>
-      <c r="U23" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U23" s="5" t="inlineStr"/>
       <c r="V23" s="5" t="inlineStr"/>
     </row>
     <row r="24">
@@ -5389,42 +5157,18 @@
       <c r="G24" s="5" t="inlineStr"/>
       <c r="H24" s="5" t="inlineStr"/>
       <c r="I24" s="5" t="inlineStr"/>
-      <c r="J24" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J24" s="5" t="inlineStr"/>
       <c r="K24" s="5" t="inlineStr"/>
-      <c r="L24" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L24" s="5" t="inlineStr"/>
       <c r="M24" s="5" t="inlineStr"/>
-      <c r="N24" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N24" s="5" t="inlineStr"/>
       <c r="O24" s="5" t="inlineStr"/>
       <c r="P24" s="5" t="inlineStr"/>
-      <c r="Q24" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q24" s="5" t="inlineStr"/>
       <c r="R24" s="5" t="inlineStr"/>
-      <c r="S24" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S24" s="5" t="inlineStr"/>
       <c r="T24" s="5" t="inlineStr"/>
-      <c r="U24" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U24" s="5" t="inlineStr"/>
       <c r="V24" s="5" t="inlineStr"/>
     </row>
     <row r="25">
@@ -5453,42 +5197,18 @@
       <c r="G25" s="5" t="inlineStr"/>
       <c r="H25" s="5" t="inlineStr"/>
       <c r="I25" s="5" t="inlineStr"/>
-      <c r="J25" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J25" s="5" t="inlineStr"/>
       <c r="K25" s="5" t="inlineStr"/>
-      <c r="L25" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L25" s="5" t="inlineStr"/>
       <c r="M25" s="5" t="inlineStr"/>
-      <c r="N25" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N25" s="5" t="inlineStr"/>
       <c r="O25" s="5" t="inlineStr"/>
       <c r="P25" s="5" t="inlineStr"/>
-      <c r="Q25" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q25" s="5" t="inlineStr"/>
       <c r="R25" s="5" t="inlineStr"/>
-      <c r="S25" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S25" s="5" t="inlineStr"/>
       <c r="T25" s="5" t="inlineStr"/>
-      <c r="U25" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U25" s="5" t="inlineStr"/>
       <c r="V25" s="5" t="inlineStr"/>
     </row>
     <row r="26">
@@ -5515,42 +5235,18 @@
       <c r="G26" s="5" t="inlineStr"/>
       <c r="H26" s="5" t="inlineStr"/>
       <c r="I26" s="5" t="inlineStr"/>
-      <c r="J26" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J26" s="5" t="inlineStr"/>
       <c r="K26" s="5" t="inlineStr"/>
-      <c r="L26" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L26" s="5" t="inlineStr"/>
       <c r="M26" s="5" t="inlineStr"/>
-      <c r="N26" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N26" s="5" t="inlineStr"/>
       <c r="O26" s="5" t="inlineStr"/>
       <c r="P26" s="5" t="inlineStr"/>
-      <c r="Q26" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q26" s="5" t="inlineStr"/>
       <c r="R26" s="5" t="inlineStr"/>
-      <c r="S26" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S26" s="5" t="inlineStr"/>
       <c r="T26" s="5" t="inlineStr"/>
-      <c r="U26" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U26" s="5" t="inlineStr"/>
       <c r="V26" s="5" t="inlineStr"/>
     </row>
     <row r="27">
@@ -5579,42 +5275,18 @@
       <c r="G27" s="5" t="inlineStr"/>
       <c r="H27" s="5" t="inlineStr"/>
       <c r="I27" s="5" t="inlineStr"/>
-      <c r="J27" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J27" s="5" t="inlineStr"/>
       <c r="K27" s="5" t="inlineStr"/>
-      <c r="L27" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L27" s="5" t="inlineStr"/>
       <c r="M27" s="5" t="inlineStr"/>
-      <c r="N27" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N27" s="5" t="inlineStr"/>
       <c r="O27" s="5" t="inlineStr"/>
       <c r="P27" s="5" t="inlineStr"/>
-      <c r="Q27" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q27" s="5" t="inlineStr"/>
       <c r="R27" s="5" t="inlineStr"/>
-      <c r="S27" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S27" s="5" t="inlineStr"/>
       <c r="T27" s="5" t="inlineStr"/>
-      <c r="U27" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U27" s="5" t="inlineStr"/>
       <c r="V27" s="5" t="inlineStr"/>
     </row>
     <row r="28">
@@ -5643,42 +5315,18 @@
       <c r="G28" s="5" t="inlineStr"/>
       <c r="H28" s="5" t="inlineStr"/>
       <c r="I28" s="5" t="inlineStr"/>
-      <c r="J28" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J28" s="5" t="inlineStr"/>
       <c r="K28" s="5" t="inlineStr"/>
-      <c r="L28" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L28" s="5" t="inlineStr"/>
       <c r="M28" s="5" t="inlineStr"/>
-      <c r="N28" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N28" s="5" t="inlineStr"/>
       <c r="O28" s="5" t="inlineStr"/>
       <c r="P28" s="5" t="inlineStr"/>
-      <c r="Q28" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q28" s="5" t="inlineStr"/>
       <c r="R28" s="5" t="inlineStr"/>
-      <c r="S28" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S28" s="5" t="inlineStr"/>
       <c r="T28" s="5" t="inlineStr"/>
-      <c r="U28" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U28" s="5" t="inlineStr"/>
       <c r="V28" s="5" t="inlineStr"/>
     </row>
     <row r="29">
@@ -5707,42 +5355,18 @@
       <c r="G29" s="5" t="inlineStr"/>
       <c r="H29" s="5" t="inlineStr"/>
       <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J29" s="5" t="inlineStr"/>
       <c r="K29" s="5" t="inlineStr"/>
-      <c r="L29" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L29" s="5" t="inlineStr"/>
       <c r="M29" s="5" t="inlineStr"/>
-      <c r="N29" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N29" s="5" t="inlineStr"/>
       <c r="O29" s="5" t="inlineStr"/>
       <c r="P29" s="5" t="inlineStr"/>
-      <c r="Q29" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q29" s="5" t="inlineStr"/>
       <c r="R29" s="5" t="inlineStr"/>
-      <c r="S29" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S29" s="5" t="inlineStr"/>
       <c r="T29" s="5" t="inlineStr"/>
-      <c r="U29" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U29" s="5" t="inlineStr"/>
       <c r="V29" s="5" t="inlineStr"/>
     </row>
     <row r="30">
@@ -5771,42 +5395,18 @@
       <c r="G30" s="5" t="inlineStr"/>
       <c r="H30" s="5" t="inlineStr"/>
       <c r="I30" s="5" t="inlineStr"/>
-      <c r="J30" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J30" s="5" t="inlineStr"/>
       <c r="K30" s="5" t="inlineStr"/>
-      <c r="L30" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L30" s="5" t="inlineStr"/>
       <c r="M30" s="5" t="inlineStr"/>
-      <c r="N30" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N30" s="5" t="inlineStr"/>
       <c r="O30" s="5" t="inlineStr"/>
       <c r="P30" s="5" t="inlineStr"/>
-      <c r="Q30" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q30" s="5" t="inlineStr"/>
       <c r="R30" s="5" t="inlineStr"/>
-      <c r="S30" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S30" s="5" t="inlineStr"/>
       <c r="T30" s="5" t="inlineStr"/>
-      <c r="U30" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U30" s="5" t="inlineStr"/>
       <c r="V30" s="5" t="inlineStr"/>
     </row>
     <row r="31">
@@ -5835,42 +5435,18 @@
       <c r="G31" s="5" t="inlineStr"/>
       <c r="H31" s="5" t="inlineStr"/>
       <c r="I31" s="5" t="inlineStr"/>
-      <c r="J31" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J31" s="5" t="inlineStr"/>
       <c r="K31" s="5" t="inlineStr"/>
-      <c r="L31" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L31" s="5" t="inlineStr"/>
       <c r="M31" s="5" t="inlineStr"/>
-      <c r="N31" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N31" s="5" t="inlineStr"/>
       <c r="O31" s="5" t="inlineStr"/>
       <c r="P31" s="5" t="inlineStr"/>
-      <c r="Q31" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q31" s="5" t="inlineStr"/>
       <c r="R31" s="5" t="inlineStr"/>
-      <c r="S31" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S31" s="5" t="inlineStr"/>
       <c r="T31" s="5" t="inlineStr"/>
-      <c r="U31" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U31" s="5" t="inlineStr"/>
       <c r="V31" s="5" t="inlineStr"/>
     </row>
     <row r="32">
@@ -5899,42 +5475,18 @@
       <c r="G32" s="5" t="inlineStr"/>
       <c r="H32" s="5" t="inlineStr"/>
       <c r="I32" s="5" t="inlineStr"/>
-      <c r="J32" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J32" s="5" t="inlineStr"/>
       <c r="K32" s="5" t="inlineStr"/>
-      <c r="L32" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L32" s="5" t="inlineStr"/>
       <c r="M32" s="5" t="inlineStr"/>
-      <c r="N32" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N32" s="5" t="inlineStr"/>
       <c r="O32" s="5" t="inlineStr"/>
       <c r="P32" s="5" t="inlineStr"/>
-      <c r="Q32" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q32" s="5" t="inlineStr"/>
       <c r="R32" s="5" t="inlineStr"/>
-      <c r="S32" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S32" s="5" t="inlineStr"/>
       <c r="T32" s="5" t="inlineStr"/>
-      <c r="U32" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U32" s="5" t="inlineStr"/>
       <c r="V32" s="5" t="inlineStr"/>
     </row>
     <row r="33">
@@ -5963,42 +5515,18 @@
       <c r="G33" s="5" t="inlineStr"/>
       <c r="H33" s="5" t="inlineStr"/>
       <c r="I33" s="5" t="inlineStr"/>
-      <c r="J33" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J33" s="5" t="inlineStr"/>
       <c r="K33" s="5" t="inlineStr"/>
-      <c r="L33" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L33" s="5" t="inlineStr"/>
       <c r="M33" s="5" t="inlineStr"/>
-      <c r="N33" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N33" s="5" t="inlineStr"/>
       <c r="O33" s="5" t="inlineStr"/>
       <c r="P33" s="5" t="inlineStr"/>
-      <c r="Q33" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q33" s="5" t="inlineStr"/>
       <c r="R33" s="5" t="inlineStr"/>
-      <c r="S33" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S33" s="5" t="inlineStr"/>
       <c r="T33" s="5" t="inlineStr"/>
-      <c r="U33" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U33" s="5" t="inlineStr"/>
       <c r="V33" s="5" t="inlineStr"/>
     </row>
     <row r="34">
@@ -6027,42 +5555,18 @@
       <c r="G34" s="5" t="inlineStr"/>
       <c r="H34" s="5" t="inlineStr"/>
       <c r="I34" s="5" t="inlineStr"/>
-      <c r="J34" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J34" s="5" t="inlineStr"/>
       <c r="K34" s="5" t="inlineStr"/>
-      <c r="L34" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L34" s="5" t="inlineStr"/>
       <c r="M34" s="5" t="inlineStr"/>
-      <c r="N34" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N34" s="5" t="inlineStr"/>
       <c r="O34" s="5" t="inlineStr"/>
       <c r="P34" s="5" t="inlineStr"/>
-      <c r="Q34" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q34" s="5" t="inlineStr"/>
       <c r="R34" s="5" t="inlineStr"/>
-      <c r="S34" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S34" s="5" t="inlineStr"/>
       <c r="T34" s="5" t="inlineStr"/>
-      <c r="U34" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U34" s="5" t="inlineStr"/>
       <c r="V34" s="5" t="inlineStr"/>
     </row>
     <row r="35">
@@ -6091,42 +5595,18 @@
       <c r="G35" s="5" t="inlineStr"/>
       <c r="H35" s="5" t="inlineStr"/>
       <c r="I35" s="5" t="inlineStr"/>
-      <c r="J35" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J35" s="5" t="inlineStr"/>
       <c r="K35" s="5" t="inlineStr"/>
-      <c r="L35" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L35" s="5" t="inlineStr"/>
       <c r="M35" s="5" t="inlineStr"/>
-      <c r="N35" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N35" s="5" t="inlineStr"/>
       <c r="O35" s="5" t="inlineStr"/>
       <c r="P35" s="5" t="inlineStr"/>
-      <c r="Q35" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q35" s="5" t="inlineStr"/>
       <c r="R35" s="5" t="inlineStr"/>
-      <c r="S35" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S35" s="5" t="inlineStr"/>
       <c r="T35" s="5" t="inlineStr"/>
-      <c r="U35" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U35" s="5" t="inlineStr"/>
       <c r="V35" s="5" t="inlineStr"/>
     </row>
     <row r="36">
@@ -6155,42 +5635,18 @@
       <c r="G36" s="5" t="inlineStr"/>
       <c r="H36" s="5" t="inlineStr"/>
       <c r="I36" s="5" t="inlineStr"/>
-      <c r="J36" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J36" s="5" t="inlineStr"/>
       <c r="K36" s="5" t="inlineStr"/>
-      <c r="L36" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L36" s="5" t="inlineStr"/>
       <c r="M36" s="5" t="inlineStr"/>
-      <c r="N36" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N36" s="5" t="inlineStr"/>
       <c r="O36" s="5" t="inlineStr"/>
       <c r="P36" s="5" t="inlineStr"/>
-      <c r="Q36" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q36" s="5" t="inlineStr"/>
       <c r="R36" s="5" t="inlineStr"/>
-      <c r="S36" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S36" s="5" t="inlineStr"/>
       <c r="T36" s="5" t="inlineStr"/>
-      <c r="U36" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U36" s="5" t="inlineStr"/>
       <c r="V36" s="5" t="inlineStr"/>
     </row>
     <row r="37">
@@ -6219,42 +5675,18 @@
       <c r="G37" s="5" t="inlineStr"/>
       <c r="H37" s="5" t="inlineStr"/>
       <c r="I37" s="5" t="inlineStr"/>
-      <c r="J37" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J37" s="5" t="inlineStr"/>
       <c r="K37" s="5" t="inlineStr"/>
-      <c r="L37" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L37" s="5" t="inlineStr"/>
       <c r="M37" s="5" t="inlineStr"/>
-      <c r="N37" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N37" s="5" t="inlineStr"/>
       <c r="O37" s="5" t="inlineStr"/>
       <c r="P37" s="5" t="inlineStr"/>
-      <c r="Q37" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q37" s="5" t="inlineStr"/>
       <c r="R37" s="5" t="inlineStr"/>
-      <c r="S37" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S37" s="5" t="inlineStr"/>
       <c r="T37" s="5" t="inlineStr"/>
-      <c r="U37" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U37" s="5" t="inlineStr"/>
       <c r="V37" s="5" t="inlineStr"/>
     </row>
     <row r="38">
@@ -6283,42 +5715,18 @@
       <c r="G38" s="5" t="inlineStr"/>
       <c r="H38" s="5" t="inlineStr"/>
       <c r="I38" s="5" t="inlineStr"/>
-      <c r="J38" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J38" s="5" t="inlineStr"/>
       <c r="K38" s="5" t="inlineStr"/>
-      <c r="L38" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L38" s="5" t="inlineStr"/>
       <c r="M38" s="5" t="inlineStr"/>
-      <c r="N38" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N38" s="5" t="inlineStr"/>
       <c r="O38" s="5" t="inlineStr"/>
       <c r="P38" s="5" t="inlineStr"/>
-      <c r="Q38" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q38" s="5" t="inlineStr"/>
       <c r="R38" s="5" t="inlineStr"/>
-      <c r="S38" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S38" s="5" t="inlineStr"/>
       <c r="T38" s="5" t="inlineStr"/>
-      <c r="U38" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U38" s="5" t="inlineStr"/>
       <c r="V38" s="5" t="inlineStr"/>
     </row>
     <row r="39">
@@ -6347,42 +5755,18 @@
       <c r="G39" s="5" t="inlineStr"/>
       <c r="H39" s="5" t="inlineStr"/>
       <c r="I39" s="5" t="inlineStr"/>
-      <c r="J39" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J39" s="5" t="inlineStr"/>
       <c r="K39" s="5" t="inlineStr"/>
-      <c r="L39" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L39" s="5" t="inlineStr"/>
       <c r="M39" s="5" t="inlineStr"/>
-      <c r="N39" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N39" s="5" t="inlineStr"/>
       <c r="O39" s="5" t="inlineStr"/>
       <c r="P39" s="5" t="inlineStr"/>
-      <c r="Q39" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q39" s="5" t="inlineStr"/>
       <c r="R39" s="5" t="inlineStr"/>
-      <c r="S39" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S39" s="5" t="inlineStr"/>
       <c r="T39" s="5" t="inlineStr"/>
-      <c r="U39" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U39" s="5" t="inlineStr"/>
       <c r="V39" s="5" t="inlineStr"/>
     </row>
     <row r="40">
@@ -6411,42 +5795,18 @@
       <c r="G40" s="5" t="inlineStr"/>
       <c r="H40" s="5" t="inlineStr"/>
       <c r="I40" s="5" t="inlineStr"/>
-      <c r="J40" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J40" s="5" t="inlineStr"/>
       <c r="K40" s="5" t="inlineStr"/>
-      <c r="L40" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L40" s="5" t="inlineStr"/>
       <c r="M40" s="5" t="inlineStr"/>
-      <c r="N40" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N40" s="5" t="inlineStr"/>
       <c r="O40" s="5" t="inlineStr"/>
       <c r="P40" s="5" t="inlineStr"/>
-      <c r="Q40" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q40" s="5" t="inlineStr"/>
       <c r="R40" s="5" t="inlineStr"/>
-      <c r="S40" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S40" s="5" t="inlineStr"/>
       <c r="T40" s="5" t="inlineStr"/>
-      <c r="U40" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U40" s="5" t="inlineStr"/>
       <c r="V40" s="5" t="inlineStr"/>
     </row>
     <row r="41">
@@ -6475,42 +5835,18 @@
       <c r="G41" s="5" t="inlineStr"/>
       <c r="H41" s="5" t="inlineStr"/>
       <c r="I41" s="5" t="inlineStr"/>
-      <c r="J41" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J41" s="5" t="inlineStr"/>
       <c r="K41" s="5" t="inlineStr"/>
-      <c r="L41" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L41" s="5" t="inlineStr"/>
       <c r="M41" s="5" t="inlineStr"/>
-      <c r="N41" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N41" s="5" t="inlineStr"/>
       <c r="O41" s="5" t="inlineStr"/>
       <c r="P41" s="5" t="inlineStr"/>
-      <c r="Q41" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q41" s="5" t="inlineStr"/>
       <c r="R41" s="5" t="inlineStr"/>
-      <c r="S41" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S41" s="5" t="inlineStr"/>
       <c r="T41" s="5" t="inlineStr"/>
-      <c r="U41" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U41" s="5" t="inlineStr"/>
       <c r="V41" s="5" t="inlineStr"/>
     </row>
     <row r="42">
@@ -6539,42 +5875,18 @@
       <c r="G42" s="5" t="inlineStr"/>
       <c r="H42" s="5" t="inlineStr"/>
       <c r="I42" s="5" t="inlineStr"/>
-      <c r="J42" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J42" s="5" t="inlineStr"/>
       <c r="K42" s="5" t="inlineStr"/>
-      <c r="L42" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L42" s="5" t="inlineStr"/>
       <c r="M42" s="5" t="inlineStr"/>
-      <c r="N42" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N42" s="5" t="inlineStr"/>
       <c r="O42" s="5" t="inlineStr"/>
       <c r="P42" s="5" t="inlineStr"/>
-      <c r="Q42" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q42" s="5" t="inlineStr"/>
       <c r="R42" s="5" t="inlineStr"/>
-      <c r="S42" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S42" s="5" t="inlineStr"/>
       <c r="T42" s="5" t="inlineStr"/>
-      <c r="U42" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U42" s="5" t="inlineStr"/>
       <c r="V42" s="5" t="inlineStr"/>
     </row>
     <row r="43">
@@ -6603,42 +5915,18 @@
       <c r="G43" s="5" t="inlineStr"/>
       <c r="H43" s="5" t="inlineStr"/>
       <c r="I43" s="5" t="inlineStr"/>
-      <c r="J43" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J43" s="5" t="inlineStr"/>
       <c r="K43" s="5" t="inlineStr"/>
-      <c r="L43" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L43" s="5" t="inlineStr"/>
       <c r="M43" s="5" t="inlineStr"/>
-      <c r="N43" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N43" s="5" t="inlineStr"/>
       <c r="O43" s="5" t="inlineStr"/>
       <c r="P43" s="5" t="inlineStr"/>
-      <c r="Q43" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q43" s="5" t="inlineStr"/>
       <c r="R43" s="5" t="inlineStr"/>
-      <c r="S43" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S43" s="5" t="inlineStr"/>
       <c r="T43" s="5" t="inlineStr"/>
-      <c r="U43" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U43" s="5" t="inlineStr"/>
       <c r="V43" s="5" t="inlineStr"/>
     </row>
     <row r="44">
@@ -6667,42 +5955,18 @@
       <c r="G44" s="5" t="inlineStr"/>
       <c r="H44" s="5" t="inlineStr"/>
       <c r="I44" s="5" t="inlineStr"/>
-      <c r="J44" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J44" s="5" t="inlineStr"/>
       <c r="K44" s="5" t="inlineStr"/>
-      <c r="L44" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L44" s="5" t="inlineStr"/>
       <c r="M44" s="5" t="inlineStr"/>
-      <c r="N44" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N44" s="5" t="inlineStr"/>
       <c r="O44" s="5" t="inlineStr"/>
       <c r="P44" s="5" t="inlineStr"/>
-      <c r="Q44" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q44" s="5" t="inlineStr"/>
       <c r="R44" s="5" t="inlineStr"/>
-      <c r="S44" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S44" s="5" t="inlineStr"/>
       <c r="T44" s="5" t="inlineStr"/>
-      <c r="U44" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U44" s="5" t="inlineStr"/>
       <c r="V44" s="5" t="inlineStr"/>
     </row>
     <row r="45">
@@ -6731,42 +5995,18 @@
       <c r="G45" s="5" t="inlineStr"/>
       <c r="H45" s="5" t="inlineStr"/>
       <c r="I45" s="5" t="inlineStr"/>
-      <c r="J45" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J45" s="5" t="inlineStr"/>
       <c r="K45" s="5" t="inlineStr"/>
-      <c r="L45" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L45" s="5" t="inlineStr"/>
       <c r="M45" s="5" t="inlineStr"/>
-      <c r="N45" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N45" s="5" t="inlineStr"/>
       <c r="O45" s="5" t="inlineStr"/>
       <c r="P45" s="5" t="inlineStr"/>
-      <c r="Q45" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q45" s="5" t="inlineStr"/>
       <c r="R45" s="5" t="inlineStr"/>
-      <c r="S45" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S45" s="5" t="inlineStr"/>
       <c r="T45" s="5" t="inlineStr"/>
-      <c r="U45" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U45" s="5" t="inlineStr"/>
       <c r="V45" s="5" t="inlineStr"/>
     </row>
     <row r="46">
@@ -6795,42 +6035,18 @@
       <c r="G46" s="5" t="inlineStr"/>
       <c r="H46" s="5" t="inlineStr"/>
       <c r="I46" s="5" t="inlineStr"/>
-      <c r="J46" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J46" s="5" t="inlineStr"/>
       <c r="K46" s="5" t="inlineStr"/>
-      <c r="L46" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L46" s="5" t="inlineStr"/>
       <c r="M46" s="5" t="inlineStr"/>
-      <c r="N46" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N46" s="5" t="inlineStr"/>
       <c r="O46" s="5" t="inlineStr"/>
       <c r="P46" s="5" t="inlineStr"/>
-      <c r="Q46" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q46" s="5" t="inlineStr"/>
       <c r="R46" s="5" t="inlineStr"/>
-      <c r="S46" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S46" s="5" t="inlineStr"/>
       <c r="T46" s="5" t="inlineStr"/>
-      <c r="U46" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U46" s="5" t="inlineStr"/>
       <c r="V46" s="5" t="inlineStr"/>
     </row>
     <row r="47">
@@ -6859,42 +6075,18 @@
       <c r="G47" s="5" t="inlineStr"/>
       <c r="H47" s="5" t="inlineStr"/>
       <c r="I47" s="5" t="inlineStr"/>
-      <c r="J47" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J47" s="5" t="inlineStr"/>
       <c r="K47" s="5" t="inlineStr"/>
-      <c r="L47" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L47" s="5" t="inlineStr"/>
       <c r="M47" s="5" t="inlineStr"/>
-      <c r="N47" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N47" s="5" t="inlineStr"/>
       <c r="O47" s="5" t="inlineStr"/>
       <c r="P47" s="5" t="inlineStr"/>
-      <c r="Q47" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q47" s="5" t="inlineStr"/>
       <c r="R47" s="5" t="inlineStr"/>
-      <c r="S47" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S47" s="5" t="inlineStr"/>
       <c r="T47" s="5" t="inlineStr"/>
-      <c r="U47" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U47" s="5" t="inlineStr"/>
       <c r="V47" s="5" t="inlineStr"/>
     </row>
   </sheetData>

--- a/outputs/SA_curtailment.xlsx
+++ b/outputs/SA_curtailment.xlsx
@@ -549,12 +549,12 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>ELI Near Term</t>
+          <t>ELI Near Term (2026-28)</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>ELI Med Term</t>
+          <t>ELI Med Term (2030-35)</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
@@ -630,9 +630,21 @@
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr"/>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="3" t="inlineStr"/>
-      <c r="G2" s="2" t="inlineStr"/>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>Non-REZ</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>eli</t>
+        </is>
+      </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
           <t>SA</t>
@@ -681,9 +693,21 @@
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr"/>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Non-REZ</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>eli-station</t>
+        </is>
+      </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
           <t>SA</t>
@@ -730,9 +754,21 @@
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr"/>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="3" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Non-REZ</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>eli-station</t>
+        </is>
+      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
           <t>SA</t>
@@ -779,9 +815,21 @@
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr"/>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Non-REZ</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>eli</t>
+        </is>
+      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
           <t>SA</t>
@@ -795,7 +843,7 @@
         <v>0.1844</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>0.2168</v>
+        <v>0.2169</v>
       </c>
       <c r="M5" s="5" t="inlineStr"/>
       <c r="N5" s="5" t="inlineStr"/>
@@ -848,7 +896,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>eli</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -941,7 +989,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>eli</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1134,7 +1182,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>eli</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1149,10 +1197,10 @@
         <v>66</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>0.2554</v>
+        <v>0.2553</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>0.3269</v>
+        <v>0.3271</v>
       </c>
       <c r="M10" s="5" t="n">
         <v>0.511388342191138</v>
@@ -1213,7 +1261,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>eli</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1261,16 +1309,16 @@
         <v>0</v>
       </c>
       <c r="V11" s="6" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W11" s="6" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="X11" s="6" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="Y11" s="6" t="n">
-        <v>0</v>
+        <v>0.09333333333333334</v>
       </c>
     </row>
     <row r="12">
@@ -1306,7 +1354,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>eli</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1352,16 +1400,16 @@
         <v>0</v>
       </c>
       <c r="V12" s="6" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W12" s="6" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="X12" s="6" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="Y12" s="6" t="n">
-        <v>0</v>
+        <v>0.09333333333333334</v>
       </c>
     </row>
     <row r="13">
@@ -1397,7 +1445,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>eli</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1412,10 +1460,10 @@
         <v>33</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>0.3249</v>
+        <v>0.3248</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>0.2807</v>
+        <v>0.2805</v>
       </c>
       <c r="M13" s="5" t="n">
         <v>0.510590381447813</v>
@@ -1492,7 +1540,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>eli</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1507,10 +1555,10 @@
         <v>3.3</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>0.2753</v>
+        <v>0.2754</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>0.3888</v>
+        <v>0.3889</v>
       </c>
       <c r="M14" s="5" t="n">
         <v>0.65425629128861</v>
@@ -1587,7 +1635,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>eli</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1602,10 +1650,10 @@
         <v>3.3</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>0.2707</v>
+        <v>0.2706</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>0.3988</v>
+        <v>0.3995</v>
       </c>
       <c r="M15" s="5" t="n">
         <v>0.65425629128861</v>
@@ -1682,7 +1730,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>eli</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1697,10 +1745,10 @@
         <v>3.3</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>0.148</v>
+        <v>0.1479</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>0.286</v>
+        <v>0.2859</v>
       </c>
       <c r="M16" s="5" t="n">
         <v>0.65425629128861</v>
@@ -1777,7 +1825,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>eli</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1795,7 +1843,7 @@
         <v>0.2332</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>0.3481</v>
+        <v>0.3486</v>
       </c>
       <c r="M17" s="5" t="n">
         <v>0.65425629128861</v>
@@ -1872,7 +1920,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>eli</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1920,16 +1968,16 @@
         <v>0</v>
       </c>
       <c r="V18" s="6" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W18" s="6" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="X18" s="6" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="Y18" s="6" t="n">
-        <v>0</v>
+        <v>0.09333333333333334</v>
       </c>
     </row>
     <row r="19">
@@ -1965,7 +2013,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>eli</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1983,7 +2031,7 @@
         <v>0.4012</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>0.4797</v>
+        <v>0.4795</v>
       </c>
       <c r="M19" s="5" t="n">
         <v>0.501077617843089</v>
@@ -2060,7 +2108,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>eli</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -2078,7 +2126,7 @@
         <v>0.3167</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>0.4573</v>
+        <v>0.4574</v>
       </c>
       <c r="M20" s="5" t="n">
         <v>0.511370986967519</v>
@@ -2139,7 +2187,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>eli</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2157,7 +2205,7 @@
         <v>0.384</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>0.5138</v>
+        <v>0.5139</v>
       </c>
       <c r="M21" s="5" t="n">
         <v>0.511370986967519</v>
@@ -2202,9 +2250,21 @@
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr"/>
-      <c r="E22" s="2" t="inlineStr"/>
-      <c r="F22" s="3" t="inlineStr"/>
-      <c r="G22" s="2" t="inlineStr"/>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>South East South Australia</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>eli</t>
+        </is>
+      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
           <t>SA</t>
@@ -2229,14 +2289,30 @@
       <c r="Q22" s="5" t="n">
         <v>0.9527</v>
       </c>
-      <c r="R22" s="6" t="inlineStr"/>
-      <c r="S22" s="6" t="inlineStr"/>
-      <c r="T22" s="6" t="inlineStr"/>
-      <c r="U22" s="6" t="inlineStr"/>
-      <c r="V22" s="6" t="inlineStr"/>
-      <c r="W22" s="6" t="inlineStr"/>
-      <c r="X22" s="6" t="inlineStr"/>
-      <c r="Y22" s="6" t="inlineStr"/>
+      <c r="R22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W22" s="6" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="X22" s="6" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="Y22" s="6" t="n">
+        <v>0.09333333333333334</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -2255,9 +2331,21 @@
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr"/>
-      <c r="E23" s="2" t="inlineStr"/>
-      <c r="F23" s="3" t="inlineStr"/>
-      <c r="G23" s="2" t="inlineStr"/>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Eastern Eyre Peninsula</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>eli</t>
+        </is>
+      </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
           <t>SA</t>
@@ -2271,7 +2359,7 @@
         <v>0.0518</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>0.0381</v>
+        <v>0.0382</v>
       </c>
       <c r="M23" s="5" t="inlineStr"/>
       <c r="N23" s="5" t="inlineStr"/>
@@ -2282,14 +2370,30 @@
       <c r="Q23" s="5" t="n">
         <v>0.9417</v>
       </c>
-      <c r="R23" s="6" t="inlineStr"/>
-      <c r="S23" s="6" t="inlineStr"/>
-      <c r="T23" s="6" t="inlineStr"/>
-      <c r="U23" s="6" t="inlineStr"/>
-      <c r="V23" s="6" t="inlineStr"/>
-      <c r="W23" s="6" t="inlineStr"/>
-      <c r="X23" s="6" t="inlineStr"/>
-      <c r="Y23" s="6" t="inlineStr"/>
+      <c r="R23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" s="6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="W23" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="X23" s="6" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="Y23" s="6" t="n">
+        <v>0.05</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -2308,9 +2412,21 @@
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr"/>
-      <c r="E24" s="2" t="inlineStr"/>
-      <c r="F24" s="3" t="inlineStr"/>
-      <c r="G24" s="2" t="inlineStr"/>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Mid-North South Australia</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>eli</t>
+        </is>
+      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
           <t>SA</t>
@@ -2321,10 +2437,10 @@
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="5" t="n">
-        <v>0.0062</v>
+        <v>0.005</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>0.0178</v>
+        <v>0.0162</v>
       </c>
       <c r="M24" s="5" t="inlineStr"/>
       <c r="N24" s="5" t="inlineStr"/>
@@ -2335,14 +2451,30 @@
       <c r="Q24" s="5" t="n">
         <v>0.9614</v>
       </c>
-      <c r="R24" s="6" t="inlineStr"/>
-      <c r="S24" s="6" t="inlineStr"/>
-      <c r="T24" s="6" t="inlineStr"/>
-      <c r="U24" s="6" t="inlineStr"/>
-      <c r="V24" s="6" t="inlineStr"/>
-      <c r="W24" s="6" t="inlineStr"/>
-      <c r="X24" s="6" t="inlineStr"/>
-      <c r="Y24" s="6" t="inlineStr"/>
+      <c r="R24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" s="6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="W24" s="6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="X24" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="Y24" s="6" t="n">
+        <v>0.05333333333333334</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -2361,9 +2493,21 @@
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr"/>
-      <c r="E25" s="2" t="inlineStr"/>
-      <c r="F25" s="3" t="inlineStr"/>
-      <c r="G25" s="2" t="inlineStr"/>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Mid-North South Australia</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>eli</t>
+        </is>
+      </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
           <t>SA</t>
@@ -2377,7 +2521,7 @@
         <v>0.1796</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>0.094</v>
+        <v>0.0939</v>
       </c>
       <c r="M25" s="5" t="inlineStr"/>
       <c r="N25" s="5" t="inlineStr"/>
@@ -2388,14 +2532,30 @@
       <c r="Q25" s="5" t="n">
         <v>0.9687</v>
       </c>
-      <c r="R25" s="6" t="inlineStr"/>
-      <c r="S25" s="6" t="inlineStr"/>
-      <c r="T25" s="6" t="inlineStr"/>
-      <c r="U25" s="6" t="inlineStr"/>
-      <c r="V25" s="6" t="inlineStr"/>
-      <c r="W25" s="6" t="inlineStr"/>
-      <c r="X25" s="6" t="inlineStr"/>
-      <c r="Y25" s="6" t="inlineStr"/>
+      <c r="R25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" s="6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="W25" s="6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="X25" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="Y25" s="6" t="n">
+        <v>0.05333333333333334</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -2414,9 +2574,21 @@
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr"/>
-      <c r="E26" s="2" t="inlineStr"/>
-      <c r="F26" s="3" t="inlineStr"/>
-      <c r="G26" s="2" t="inlineStr"/>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Mid-North South Australia</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>eli</t>
+        </is>
+      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
           <t>SA</t>
@@ -2428,7 +2600,7 @@
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="5" t="inlineStr"/>
       <c r="L26" s="5" t="n">
-        <v>0.2785</v>
+        <v>0.2788</v>
       </c>
       <c r="M26" s="5" t="inlineStr"/>
       <c r="N26" s="5" t="inlineStr"/>
@@ -2439,14 +2611,30 @@
       <c r="Q26" s="5" t="n">
         <v>0.9687</v>
       </c>
-      <c r="R26" s="6" t="inlineStr"/>
-      <c r="S26" s="6" t="inlineStr"/>
-      <c r="T26" s="6" t="inlineStr"/>
-      <c r="U26" s="6" t="inlineStr"/>
-      <c r="V26" s="6" t="inlineStr"/>
-      <c r="W26" s="6" t="inlineStr"/>
-      <c r="X26" s="6" t="inlineStr"/>
-      <c r="Y26" s="6" t="inlineStr"/>
+      <c r="R26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" s="6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="W26" s="6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="X26" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="Y26" s="6" t="n">
+        <v>0.05333333333333334</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -2465,9 +2653,21 @@
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr"/>
-      <c r="E27" s="2" t="inlineStr"/>
-      <c r="F27" s="3" t="inlineStr"/>
-      <c r="G27" s="2" t="inlineStr"/>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Mid-North South Australia</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>eli</t>
+        </is>
+      </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
           <t>SA</t>
@@ -2478,10 +2678,10 @@
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="5" t="n">
-        <v>0.1209</v>
+        <v>0.1208</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>0.1935</v>
+        <v>0.1932</v>
       </c>
       <c r="M27" s="5" t="inlineStr"/>
       <c r="N27" s="5" t="inlineStr"/>
@@ -2492,14 +2692,30 @@
       <c r="Q27" s="5" t="n">
         <v>0.9628</v>
       </c>
-      <c r="R27" s="6" t="inlineStr"/>
-      <c r="S27" s="6" t="inlineStr"/>
-      <c r="T27" s="6" t="inlineStr"/>
-      <c r="U27" s="6" t="inlineStr"/>
-      <c r="V27" s="6" t="inlineStr"/>
-      <c r="W27" s="6" t="inlineStr"/>
-      <c r="X27" s="6" t="inlineStr"/>
-      <c r="Y27" s="6" t="inlineStr"/>
+      <c r="R27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" s="6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="W27" s="6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="X27" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="Y27" s="6" t="n">
+        <v>0.05333333333333334</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2518,9 +2734,21 @@
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr"/>
-      <c r="E28" s="2" t="inlineStr"/>
-      <c r="F28" s="3" t="inlineStr"/>
-      <c r="G28" s="2" t="inlineStr"/>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Mid-North South Australia</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>eli</t>
+        </is>
+      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
           <t>SA</t>
@@ -2531,10 +2759,10 @@
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="5" t="n">
-        <v>0.1083</v>
+        <v>0.1084</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>0.1916</v>
+        <v>0.1913</v>
       </c>
       <c r="M28" s="5" t="inlineStr"/>
       <c r="N28" s="5" t="inlineStr"/>
@@ -2545,14 +2773,30 @@
       <c r="Q28" s="5" t="n">
         <v>0.9606</v>
       </c>
-      <c r="R28" s="6" t="inlineStr"/>
-      <c r="S28" s="6" t="inlineStr"/>
-      <c r="T28" s="6" t="inlineStr"/>
-      <c r="U28" s="6" t="inlineStr"/>
-      <c r="V28" s="6" t="inlineStr"/>
-      <c r="W28" s="6" t="inlineStr"/>
-      <c r="X28" s="6" t="inlineStr"/>
-      <c r="Y28" s="6" t="inlineStr"/>
+      <c r="R28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" s="6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="W28" s="6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="X28" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="Y28" s="6" t="n">
+        <v>0.05333333333333334</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -2571,9 +2815,21 @@
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr"/>
-      <c r="E29" s="2" t="inlineStr"/>
-      <c r="F29" s="3" t="inlineStr"/>
-      <c r="G29" s="2" t="inlineStr"/>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>Mid-North South Australia</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>eli</t>
+        </is>
+      </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
           <t>SA</t>
@@ -2584,10 +2840,10 @@
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="5" t="n">
-        <v>0.0034</v>
+        <v>0.001</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>0.0016</v>
+        <v>0</v>
       </c>
       <c r="M29" s="5" t="inlineStr"/>
       <c r="N29" s="5" t="inlineStr"/>
@@ -2598,14 +2854,30 @@
       <c r="Q29" s="5" t="n">
         <v>0.9533</v>
       </c>
-      <c r="R29" s="6" t="inlineStr"/>
-      <c r="S29" s="6" t="inlineStr"/>
-      <c r="T29" s="6" t="inlineStr"/>
-      <c r="U29" s="6" t="inlineStr"/>
-      <c r="V29" s="6" t="inlineStr"/>
-      <c r="W29" s="6" t="inlineStr"/>
-      <c r="X29" s="6" t="inlineStr"/>
-      <c r="Y29" s="6" t="inlineStr"/>
+      <c r="R29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" s="6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="W29" s="6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="X29" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="Y29" s="6" t="n">
+        <v>0.05333333333333334</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2624,9 +2896,21 @@
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr"/>
-      <c r="E30" s="2" t="inlineStr"/>
-      <c r="F30" s="3" t="inlineStr"/>
-      <c r="G30" s="2" t="inlineStr"/>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Mid-North South Australia</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>eli</t>
+        </is>
+      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
           <t>SA</t>
@@ -2637,10 +2921,10 @@
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="5" t="n">
-        <v>0.0038</v>
+        <v>0</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>0.0011</v>
+        <v>0</v>
       </c>
       <c r="M30" s="5" t="inlineStr"/>
       <c r="N30" s="5" t="inlineStr"/>
@@ -2651,14 +2935,30 @@
       <c r="Q30" s="5" t="n">
         <v>0.9533</v>
       </c>
-      <c r="R30" s="6" t="inlineStr"/>
-      <c r="S30" s="6" t="inlineStr"/>
-      <c r="T30" s="6" t="inlineStr"/>
-      <c r="U30" s="6" t="inlineStr"/>
-      <c r="V30" s="6" t="inlineStr"/>
-      <c r="W30" s="6" t="inlineStr"/>
-      <c r="X30" s="6" t="inlineStr"/>
-      <c r="Y30" s="6" t="inlineStr"/>
+      <c r="R30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" s="6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="W30" s="6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="X30" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="Y30" s="6" t="n">
+        <v>0.05333333333333334</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -2677,9 +2977,21 @@
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr"/>
-      <c r="E31" s="2" t="inlineStr"/>
-      <c r="F31" s="3" t="inlineStr"/>
-      <c r="G31" s="2" t="inlineStr"/>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>Mid-North South Australia</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>eli</t>
+        </is>
+      </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
           <t>SA</t>
@@ -2690,10 +3002,10 @@
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="5" t="n">
-        <v>0.0028</v>
+        <v>0</v>
       </c>
       <c r="L31" s="5" t="n">
-        <v>0.0015</v>
+        <v>0</v>
       </c>
       <c r="M31" s="5" t="inlineStr"/>
       <c r="N31" s="5" t="inlineStr"/>
@@ -2704,14 +3016,30 @@
       <c r="Q31" s="5" t="n">
         <v>0.9533</v>
       </c>
-      <c r="R31" s="6" t="inlineStr"/>
-      <c r="S31" s="6" t="inlineStr"/>
-      <c r="T31" s="6" t="inlineStr"/>
-      <c r="U31" s="6" t="inlineStr"/>
-      <c r="V31" s="6" t="inlineStr"/>
-      <c r="W31" s="6" t="inlineStr"/>
-      <c r="X31" s="6" t="inlineStr"/>
-      <c r="Y31" s="6" t="inlineStr"/>
+      <c r="R31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" s="6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="W31" s="6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="X31" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="Y31" s="6" t="n">
+        <v>0.05333333333333334</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2730,9 +3058,21 @@
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr"/>
-      <c r="E32" s="2" t="inlineStr"/>
-      <c r="F32" s="3" t="inlineStr"/>
-      <c r="G32" s="2" t="inlineStr"/>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>South East South Australia</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>eli</t>
+        </is>
+      </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
           <t>SA</t>
@@ -2746,7 +3086,7 @@
         <v>0.2</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>0.2497</v>
+        <v>0.2496</v>
       </c>
       <c r="M32" s="5" t="inlineStr"/>
       <c r="N32" s="5" t="inlineStr"/>
@@ -2757,14 +3097,30 @@
       <c r="Q32" s="5" t="n">
         <v>0.9468</v>
       </c>
-      <c r="R32" s="6" t="inlineStr"/>
-      <c r="S32" s="6" t="inlineStr"/>
-      <c r="T32" s="6" t="inlineStr"/>
-      <c r="U32" s="6" t="inlineStr"/>
-      <c r="V32" s="6" t="inlineStr"/>
-      <c r="W32" s="6" t="inlineStr"/>
-      <c r="X32" s="6" t="inlineStr"/>
-      <c r="Y32" s="6" t="inlineStr"/>
+      <c r="R32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W32" s="6" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="X32" s="6" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="Y32" s="6" t="n">
+        <v>0.09333333333333334</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -2783,9 +3139,21 @@
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr"/>
-      <c r="E33" s="2" t="inlineStr"/>
-      <c r="F33" s="3" t="inlineStr"/>
-      <c r="G33" s="2" t="inlineStr"/>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>South East South Australia</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>eli</t>
+        </is>
+      </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
           <t>SA</t>
@@ -2810,14 +3178,30 @@
       <c r="Q33" s="5" t="n">
         <v>0.9468</v>
       </c>
-      <c r="R33" s="6" t="inlineStr"/>
-      <c r="S33" s="6" t="inlineStr"/>
-      <c r="T33" s="6" t="inlineStr"/>
-      <c r="U33" s="6" t="inlineStr"/>
-      <c r="V33" s="6" t="inlineStr"/>
-      <c r="W33" s="6" t="inlineStr"/>
-      <c r="X33" s="6" t="inlineStr"/>
-      <c r="Y33" s="6" t="inlineStr"/>
+      <c r="R33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W33" s="6" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="X33" s="6" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="Y33" s="6" t="n">
+        <v>0.09333333333333334</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -2836,9 +3220,21 @@
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr"/>
-      <c r="E34" s="2" t="inlineStr"/>
-      <c r="F34" s="3" t="inlineStr"/>
-      <c r="G34" s="2" t="inlineStr"/>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>South East South Australia</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>eli</t>
+        </is>
+      </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
           <t>SA</t>
@@ -2852,7 +3248,7 @@
         <v>0.2637</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>0.3006</v>
+        <v>0.3005</v>
       </c>
       <c r="M34" s="5" t="inlineStr"/>
       <c r="N34" s="5" t="inlineStr"/>
@@ -2863,14 +3259,30 @@
       <c r="Q34" s="5" t="n">
         <v>0.9468</v>
       </c>
-      <c r="R34" s="6" t="inlineStr"/>
-      <c r="S34" s="6" t="inlineStr"/>
-      <c r="T34" s="6" t="inlineStr"/>
-      <c r="U34" s="6" t="inlineStr"/>
-      <c r="V34" s="6" t="inlineStr"/>
-      <c r="W34" s="6" t="inlineStr"/>
-      <c r="X34" s="6" t="inlineStr"/>
-      <c r="Y34" s="6" t="inlineStr"/>
+      <c r="R34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W34" s="6" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="X34" s="6" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="Y34" s="6" t="n">
+        <v>0.09333333333333334</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -2889,9 +3301,21 @@
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr"/>
-      <c r="E35" s="2" t="inlineStr"/>
-      <c r="F35" s="3" t="inlineStr"/>
-      <c r="G35" s="2" t="inlineStr"/>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>Northern South Australia</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>eli</t>
+        </is>
+      </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
           <t>SA</t>
@@ -2905,7 +3329,7 @@
         <v>0.1458</v>
       </c>
       <c r="L35" s="5" t="n">
-        <v>0.1783</v>
+        <v>0.1782</v>
       </c>
       <c r="M35" s="5" t="inlineStr"/>
       <c r="N35" s="5" t="inlineStr"/>
@@ -2916,14 +3340,30 @@
       <c r="Q35" s="5" t="n">
         <v>0.9661</v>
       </c>
-      <c r="R35" s="6" t="inlineStr"/>
-      <c r="S35" s="6" t="inlineStr"/>
-      <c r="T35" s="6" t="inlineStr"/>
-      <c r="U35" s="6" t="inlineStr"/>
-      <c r="V35" s="6" t="inlineStr"/>
-      <c r="W35" s="6" t="inlineStr"/>
-      <c r="X35" s="6" t="inlineStr"/>
-      <c r="Y35" s="6" t="inlineStr"/>
+      <c r="R35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" s="6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="W35" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="X35" s="6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="Y35" s="6" t="n">
+        <v>0.07333333333333335</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -2942,9 +3382,21 @@
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr"/>
-      <c r="E36" s="2" t="inlineStr"/>
-      <c r="F36" s="3" t="inlineStr"/>
-      <c r="G36" s="2" t="inlineStr"/>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Northern South Australia</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>eli</t>
+        </is>
+      </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
           <t>SA</t>
@@ -2958,7 +3410,7 @@
         <v>0.1653</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>0.1995</v>
+        <v>0.1994</v>
       </c>
       <c r="M36" s="5" t="inlineStr"/>
       <c r="N36" s="5" t="inlineStr"/>
@@ -2969,14 +3421,30 @@
       <c r="Q36" s="5" t="n">
         <v>0.9661</v>
       </c>
-      <c r="R36" s="6" t="inlineStr"/>
-      <c r="S36" s="6" t="inlineStr"/>
-      <c r="T36" s="6" t="inlineStr"/>
-      <c r="U36" s="6" t="inlineStr"/>
-      <c r="V36" s="6" t="inlineStr"/>
-      <c r="W36" s="6" t="inlineStr"/>
-      <c r="X36" s="6" t="inlineStr"/>
-      <c r="Y36" s="6" t="inlineStr"/>
+      <c r="R36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" s="6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="W36" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="X36" s="6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="Y36" s="6" t="n">
+        <v>0.07333333333333335</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -2995,9 +3463,21 @@
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr"/>
-      <c r="E37" s="2" t="inlineStr"/>
-      <c r="F37" s="3" t="inlineStr"/>
-      <c r="G37" s="2" t="inlineStr"/>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>Eastern Eyre Peninsula</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>eli</t>
+        </is>
+      </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
           <t>SA</t>
@@ -3011,7 +3491,7 @@
         <v>0.3052</v>
       </c>
       <c r="L37" s="5" t="n">
-        <v>0.1511</v>
+        <v>0.151</v>
       </c>
       <c r="M37" s="5" t="inlineStr"/>
       <c r="N37" s="5" t="inlineStr"/>
@@ -3022,14 +3502,30 @@
       <c r="Q37" s="5" t="n">
         <v>0.9387</v>
       </c>
-      <c r="R37" s="6" t="inlineStr"/>
-      <c r="S37" s="6" t="inlineStr"/>
-      <c r="T37" s="6" t="inlineStr"/>
-      <c r="U37" s="6" t="inlineStr"/>
-      <c r="V37" s="6" t="inlineStr"/>
-      <c r="W37" s="6" t="inlineStr"/>
-      <c r="X37" s="6" t="inlineStr"/>
-      <c r="Y37" s="6" t="inlineStr"/>
+      <c r="R37" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" s="6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="W37" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="X37" s="6" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="Y37" s="6" t="n">
+        <v>0.05</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -3048,9 +3544,21 @@
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr"/>
-      <c r="E38" s="2" t="inlineStr"/>
-      <c r="F38" s="3" t="inlineStr"/>
-      <c r="G38" s="2" t="inlineStr"/>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>Mid-North South Australia</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>eli</t>
+        </is>
+      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
           <t>SA</t>
@@ -3064,7 +3572,7 @@
         <v>0.1223</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>0.1729</v>
+        <v>0.1727</v>
       </c>
       <c r="M38" s="5" t="inlineStr"/>
       <c r="N38" s="5" t="inlineStr"/>
@@ -3075,14 +3583,30 @@
       <c r="Q38" s="5" t="n">
         <v>0.9572000000000001</v>
       </c>
-      <c r="R38" s="6" t="inlineStr"/>
-      <c r="S38" s="6" t="inlineStr"/>
-      <c r="T38" s="6" t="inlineStr"/>
-      <c r="U38" s="6" t="inlineStr"/>
-      <c r="V38" s="6" t="inlineStr"/>
-      <c r="W38" s="6" t="inlineStr"/>
-      <c r="X38" s="6" t="inlineStr"/>
-      <c r="Y38" s="6" t="inlineStr"/>
+      <c r="R38" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" s="6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="W38" s="6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="X38" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="Y38" s="6" t="n">
+        <v>0.05333333333333334</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -3101,9 +3625,21 @@
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr"/>
-      <c r="E39" s="2" t="inlineStr"/>
-      <c r="F39" s="3" t="inlineStr"/>
-      <c r="G39" s="2" t="inlineStr"/>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>Northern South Australia</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>eli</t>
+        </is>
+      </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
           <t>SA</t>
@@ -3117,7 +3653,7 @@
         <v>0.1999</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>0.2153</v>
+        <v>0.2151</v>
       </c>
       <c r="M39" s="5" t="inlineStr"/>
       <c r="N39" s="5" t="inlineStr"/>
@@ -3128,14 +3664,30 @@
       <c r="Q39" s="5" t="n">
         <v>0.9709</v>
       </c>
-      <c r="R39" s="6" t="inlineStr"/>
-      <c r="S39" s="6" t="inlineStr"/>
-      <c r="T39" s="6" t="inlineStr"/>
-      <c r="U39" s="6" t="inlineStr"/>
-      <c r="V39" s="6" t="inlineStr"/>
-      <c r="W39" s="6" t="inlineStr"/>
-      <c r="X39" s="6" t="inlineStr"/>
-      <c r="Y39" s="6" t="inlineStr"/>
+      <c r="R39" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" s="6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="W39" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="X39" s="6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="Y39" s="6" t="n">
+        <v>0.07333333333333335</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -3154,9 +3706,21 @@
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr"/>
-      <c r="E40" s="2" t="inlineStr"/>
-      <c r="F40" s="3" t="inlineStr"/>
-      <c r="G40" s="2" t="inlineStr"/>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>Mid-North South Australia</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>eli</t>
+        </is>
+      </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
           <t>SA</t>
@@ -3167,10 +3731,10 @@
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="5" t="n">
-        <v>0.0037</v>
+        <v>0.0035</v>
       </c>
       <c r="L40" s="5" t="n">
-        <v>0.0022</v>
+        <v>0</v>
       </c>
       <c r="M40" s="5" t="inlineStr"/>
       <c r="N40" s="5" t="inlineStr"/>
@@ -3181,14 +3745,30 @@
       <c r="Q40" s="5" t="n">
         <v>0.9699</v>
       </c>
-      <c r="R40" s="6" t="inlineStr"/>
-      <c r="S40" s="6" t="inlineStr"/>
-      <c r="T40" s="6" t="inlineStr"/>
-      <c r="U40" s="6" t="inlineStr"/>
-      <c r="V40" s="6" t="inlineStr"/>
-      <c r="W40" s="6" t="inlineStr"/>
-      <c r="X40" s="6" t="inlineStr"/>
-      <c r="Y40" s="6" t="inlineStr"/>
+      <c r="R40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" s="6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="W40" s="6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="X40" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="Y40" s="6" t="n">
+        <v>0.05333333333333334</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -3207,9 +3787,21 @@
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr"/>
-      <c r="E41" s="2" t="inlineStr"/>
-      <c r="F41" s="3" t="inlineStr"/>
-      <c r="G41" s="2" t="inlineStr"/>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>Mid-North South Australia</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>eli</t>
+        </is>
+      </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
           <t>SA</t>
@@ -3220,10 +3812,10 @@
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="5" t="n">
-        <v>0.0027</v>
+        <v>0</v>
       </c>
       <c r="L41" s="5" t="n">
-        <v>0.0027</v>
+        <v>0.0011</v>
       </c>
       <c r="M41" s="5" t="inlineStr"/>
       <c r="N41" s="5" t="inlineStr"/>
@@ -3234,14 +3826,30 @@
       <c r="Q41" s="5" t="n">
         <v>0.9699</v>
       </c>
-      <c r="R41" s="6" t="inlineStr"/>
-      <c r="S41" s="6" t="inlineStr"/>
-      <c r="T41" s="6" t="inlineStr"/>
-      <c r="U41" s="6" t="inlineStr"/>
-      <c r="V41" s="6" t="inlineStr"/>
-      <c r="W41" s="6" t="inlineStr"/>
-      <c r="X41" s="6" t="inlineStr"/>
-      <c r="Y41" s="6" t="inlineStr"/>
+      <c r="R41" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" s="6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="W41" s="6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="X41" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="Y41" s="6" t="n">
+        <v>0.05333333333333334</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -3260,9 +3868,21 @@
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr"/>
-      <c r="E42" s="2" t="inlineStr"/>
-      <c r="F42" s="3" t="inlineStr"/>
-      <c r="G42" s="2" t="inlineStr"/>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>Mid-North South Australia</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>eli</t>
+        </is>
+      </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
           <t>SA</t>
@@ -3276,7 +3896,7 @@
         <v>0.1863</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>0.2696</v>
+        <v>0.2693</v>
       </c>
       <c r="M42" s="5" t="inlineStr"/>
       <c r="N42" s="5" t="inlineStr"/>
@@ -3287,14 +3907,30 @@
       <c r="Q42" s="5" t="n">
         <v>0.9132</v>
       </c>
-      <c r="R42" s="6" t="inlineStr"/>
-      <c r="S42" s="6" t="inlineStr"/>
-      <c r="T42" s="6" t="inlineStr"/>
-      <c r="U42" s="6" t="inlineStr"/>
-      <c r="V42" s="6" t="inlineStr"/>
-      <c r="W42" s="6" t="inlineStr"/>
-      <c r="X42" s="6" t="inlineStr"/>
-      <c r="Y42" s="6" t="inlineStr"/>
+      <c r="R42" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" s="6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="W42" s="6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="X42" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="Y42" s="6" t="n">
+        <v>0.05333333333333334</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -3313,9 +3949,21 @@
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr"/>
-      <c r="E43" s="2" t="inlineStr"/>
-      <c r="F43" s="3" t="inlineStr"/>
-      <c r="G43" s="2" t="inlineStr"/>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>Non-REZ</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>eli</t>
+        </is>
+      </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
           <t>SA</t>
@@ -3366,9 +4014,21 @@
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr"/>
-      <c r="E44" s="2" t="inlineStr"/>
-      <c r="F44" s="3" t="inlineStr"/>
-      <c r="G44" s="2" t="inlineStr"/>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>Mid-North South Australia</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>eli</t>
+        </is>
+      </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
           <t>SA</t>
@@ -3379,10 +4039,10 @@
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="5" t="n">
-        <v>0.0906</v>
+        <v>0.0886</v>
       </c>
       <c r="L44" s="5" t="n">
-        <v>0.1905</v>
+        <v>0.1901</v>
       </c>
       <c r="M44" s="5" t="inlineStr"/>
       <c r="N44" s="5" t="inlineStr"/>
@@ -3393,14 +4053,30 @@
       <c r="Q44" s="5" t="n">
         <v>0.9572000000000001</v>
       </c>
-      <c r="R44" s="6" t="inlineStr"/>
-      <c r="S44" s="6" t="inlineStr"/>
-      <c r="T44" s="6" t="inlineStr"/>
-      <c r="U44" s="6" t="inlineStr"/>
-      <c r="V44" s="6" t="inlineStr"/>
-      <c r="W44" s="6" t="inlineStr"/>
-      <c r="X44" s="6" t="inlineStr"/>
-      <c r="Y44" s="6" t="inlineStr"/>
+      <c r="R44" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" s="6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="W44" s="6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="X44" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="Y44" s="6" t="n">
+        <v>0.05333333333333334</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -3419,9 +4095,21 @@
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr"/>
-      <c r="E45" s="2" t="inlineStr"/>
-      <c r="F45" s="3" t="inlineStr"/>
-      <c r="G45" s="2" t="inlineStr"/>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>Mid-North South Australia</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>eli</t>
+        </is>
+      </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
           <t>SA</t>
@@ -3432,28 +4120,52 @@
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="5" t="n">
-        <v>0.0206</v>
+        <v>0.0205</v>
       </c>
       <c r="L45" s="5" t="n">
-        <v>0.0121</v>
-      </c>
-      <c r="M45" s="5" t="inlineStr"/>
-      <c r="N45" s="5" t="inlineStr"/>
-      <c r="O45" s="2" t="inlineStr"/>
+        <v>0.0109</v>
+      </c>
+      <c r="M45" s="5" t="n">
+        <v>0.691487736497032</v>
+      </c>
+      <c r="N45" s="5" t="n">
+        <v>0.402744462066548</v>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>location-name</t>
+        </is>
+      </c>
       <c r="P45" s="5" t="n">
         <v>0.9624</v>
       </c>
       <c r="Q45" s="5" t="n">
         <v>0.9611</v>
       </c>
-      <c r="R45" s="6" t="inlineStr"/>
-      <c r="S45" s="6" t="inlineStr"/>
-      <c r="T45" s="6" t="inlineStr"/>
-      <c r="U45" s="6" t="inlineStr"/>
-      <c r="V45" s="6" t="inlineStr"/>
-      <c r="W45" s="6" t="inlineStr"/>
-      <c r="X45" s="6" t="inlineStr"/>
-      <c r="Y45" s="6" t="inlineStr"/>
+      <c r="R45" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V45" s="6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="W45" s="6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="X45" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="Y45" s="6" t="n">
+        <v>0.05333333333333334</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -3472,9 +4184,21 @@
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr"/>
-      <c r="E46" s="2" t="inlineStr"/>
-      <c r="F46" s="3" t="inlineStr"/>
-      <c r="G46" s="2" t="inlineStr"/>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>Yorke Peninsula</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>eli</t>
+        </is>
+      </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
           <t>SA</t>
@@ -3488,7 +4212,7 @@
         <v>0.1686</v>
       </c>
       <c r="L46" s="5" t="n">
-        <v>0.2013</v>
+        <v>0.2012</v>
       </c>
       <c r="M46" s="5" t="inlineStr"/>
       <c r="N46" s="5" t="inlineStr"/>
@@ -3499,14 +4223,30 @@
       <c r="Q46" s="5" t="n">
         <v>0.8476</v>
       </c>
-      <c r="R46" s="6" t="inlineStr"/>
-      <c r="S46" s="6" t="inlineStr"/>
-      <c r="T46" s="6" t="inlineStr"/>
-      <c r="U46" s="6" t="inlineStr"/>
-      <c r="V46" s="6" t="inlineStr"/>
-      <c r="W46" s="6" t="inlineStr"/>
-      <c r="X46" s="6" t="inlineStr"/>
-      <c r="Y46" s="6" t="inlineStr"/>
+      <c r="R46" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W46" s="6" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="X46" s="6" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="Y46" s="6" t="n">
+        <v>0.09333333333333334</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -3525,9 +4265,21 @@
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr"/>
-      <c r="E47" s="2" t="inlineStr"/>
-      <c r="F47" s="3" t="inlineStr"/>
-      <c r="G47" s="2" t="inlineStr"/>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>Mid-North South Australia</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>eli</t>
+        </is>
+      </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
           <t>SA</t>
@@ -3541,7 +4293,7 @@
         <v>0.0432</v>
       </c>
       <c r="L47" s="5" t="n">
-        <v>0.0341</v>
+        <v>0.0337</v>
       </c>
       <c r="M47" s="5" t="inlineStr"/>
       <c r="N47" s="5" t="inlineStr"/>
@@ -3552,14 +4304,30 @@
       <c r="Q47" s="5" t="n">
         <v>0.9592000000000001</v>
       </c>
-      <c r="R47" s="6" t="inlineStr"/>
-      <c r="S47" s="6" t="inlineStr"/>
-      <c r="T47" s="6" t="inlineStr"/>
-      <c r="U47" s="6" t="inlineStr"/>
-      <c r="V47" s="6" t="inlineStr"/>
-      <c r="W47" s="6" t="inlineStr"/>
-      <c r="X47" s="6" t="inlineStr"/>
-      <c r="Y47" s="6" t="inlineStr"/>
+      <c r="R47" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U47" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V47" s="6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="W47" s="6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="X47" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="Y47" s="6" t="n">
+        <v>0.05333333333333334</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3842,7 +4610,7 @@
         <v>0.1844</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.2168</v>
+        <v>0.2169</v>
       </c>
       <c r="G5" s="5" t="inlineStr"/>
       <c r="H5" s="5" t="inlineStr"/>
@@ -4117,10 +4885,10 @@
         <v>1.0022</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>0.2554</v>
+        <v>0.2553</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>0.3269</v>
+        <v>0.3271</v>
       </c>
       <c r="G10" s="5" t="n">
         <v>0.511388342191138</v>
@@ -4129,42 +4897,18 @@
         <v>0.22265637813532</v>
       </c>
       <c r="I10" s="5" t="inlineStr"/>
-      <c r="J10" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J10" s="5" t="inlineStr"/>
       <c r="K10" s="5" t="inlineStr"/>
-      <c r="L10" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L10" s="5" t="inlineStr"/>
       <c r="M10" s="5" t="inlineStr"/>
-      <c r="N10" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N10" s="5" t="inlineStr"/>
       <c r="O10" s="5" t="inlineStr"/>
       <c r="P10" s="5" t="inlineStr"/>
-      <c r="Q10" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q10" s="5" t="inlineStr"/>
       <c r="R10" s="5" t="inlineStr"/>
-      <c r="S10" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S10" s="5" t="inlineStr"/>
       <c r="T10" s="5" t="inlineStr"/>
-      <c r="U10" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U10" s="5" t="inlineStr"/>
       <c r="V10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
@@ -4222,7 +4966,7 @@
         <v>0</v>
       </c>
       <c r="P11" s="5" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="Q11" s="5" t="inlineStr">
         <is>
@@ -4230,7 +4974,7 @@
         </is>
       </c>
       <c r="R11" s="5" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="S11" s="5" t="inlineStr">
         <is>
@@ -4238,7 +4982,7 @@
         </is>
       </c>
       <c r="T11" s="5" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="U11" s="5" t="inlineStr">
         <is>
@@ -4246,7 +4990,7 @@
         </is>
       </c>
       <c r="V11" s="5" t="n">
-        <v>0</v>
+        <v>0.09333333333333334</v>
       </c>
     </row>
     <row r="12">
@@ -4302,7 +5046,7 @@
         <v>0</v>
       </c>
       <c r="P12" s="5" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="Q12" s="5" t="inlineStr">
         <is>
@@ -4310,7 +5054,7 @@
         </is>
       </c>
       <c r="R12" s="5" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="S12" s="5" t="inlineStr">
         <is>
@@ -4318,7 +5062,7 @@
         </is>
       </c>
       <c r="T12" s="5" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="U12" s="5" t="inlineStr">
         <is>
@@ -4326,7 +5070,7 @@
         </is>
       </c>
       <c r="V12" s="5" t="n">
-        <v>0</v>
+        <v>0.09333333333333334</v>
       </c>
     </row>
     <row r="13">
@@ -4347,10 +5091,10 @@
         <v>0.9959</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>0.3249</v>
+        <v>0.3248</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.2807</v>
+        <v>0.2805</v>
       </c>
       <c r="G13" s="5" t="n">
         <v>0.510590381447813</v>
@@ -4431,10 +5175,10 @@
         <v>0.9540999999999999</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>0.2753</v>
+        <v>0.2754</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>0.3888</v>
+        <v>0.3889</v>
       </c>
       <c r="G14" s="5" t="n">
         <v>0.65425629128861</v>
@@ -4515,10 +5259,10 @@
         <v>0.9664</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>0.2707</v>
+        <v>0.2706</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>0.3988</v>
+        <v>0.3995</v>
       </c>
       <c r="G15" s="5" t="n">
         <v>0.65425629128861</v>
@@ -4599,10 +5343,10 @@
         <v>0.9741</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>0.148</v>
+        <v>0.1479</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>0.286</v>
+        <v>0.2859</v>
       </c>
       <c r="G16" s="5" t="n">
         <v>0.65425629128861</v>
@@ -4686,7 +5430,7 @@
         <v>0.2332</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>0.3481</v>
+        <v>0.3486</v>
       </c>
       <c r="G17" s="5" t="n">
         <v>0.65425629128861</v>
@@ -4804,7 +5548,7 @@
         <v>0</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="Q18" s="5" t="inlineStr">
         <is>
@@ -4812,7 +5556,7 @@
         </is>
       </c>
       <c r="R18" s="5" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="S18" s="5" t="inlineStr">
         <is>
@@ -4820,7 +5564,7 @@
         </is>
       </c>
       <c r="T18" s="5" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="U18" s="5" t="inlineStr">
         <is>
@@ -4828,7 +5572,7 @@
         </is>
       </c>
       <c r="V18" s="5" t="n">
-        <v>0</v>
+        <v>0.09333333333333334</v>
       </c>
     </row>
     <row r="19">
@@ -4852,7 +5596,7 @@
         <v>0.4012</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>0.4797</v>
+        <v>0.4795</v>
       </c>
       <c r="G19" s="5" t="n">
         <v>0.501077617843089</v>
@@ -4936,7 +5680,7 @@
         <v>0.3167</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>0.4573</v>
+        <v>0.4574</v>
       </c>
       <c r="G20" s="5" t="n">
         <v>0.511370986967519</v>
@@ -4945,42 +5689,18 @@
         <v>0.22945882760626</v>
       </c>
       <c r="I20" s="5" t="inlineStr"/>
-      <c r="J20" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J20" s="5" t="inlineStr"/>
       <c r="K20" s="5" t="inlineStr"/>
-      <c r="L20" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L20" s="5" t="inlineStr"/>
       <c r="M20" s="5" t="inlineStr"/>
-      <c r="N20" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N20" s="5" t="inlineStr"/>
       <c r="O20" s="5" t="inlineStr"/>
       <c r="P20" s="5" t="inlineStr"/>
-      <c r="Q20" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q20" s="5" t="inlineStr"/>
       <c r="R20" s="5" t="inlineStr"/>
-      <c r="S20" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S20" s="5" t="inlineStr"/>
       <c r="T20" s="5" t="inlineStr"/>
-      <c r="U20" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U20" s="5" t="inlineStr"/>
       <c r="V20" s="5" t="inlineStr"/>
     </row>
     <row r="21">
@@ -5004,7 +5724,7 @@
         <v>0.384</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>0.5138</v>
+        <v>0.5139</v>
       </c>
       <c r="G21" s="5" t="n">
         <v>0.511370986967519</v>
@@ -5013,42 +5733,18 @@
         <v>0.22945882760626</v>
       </c>
       <c r="I21" s="5" t="inlineStr"/>
-      <c r="J21" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J21" s="5" t="inlineStr"/>
       <c r="K21" s="5" t="inlineStr"/>
-      <c r="L21" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L21" s="5" t="inlineStr"/>
       <c r="M21" s="5" t="inlineStr"/>
-      <c r="N21" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N21" s="5" t="inlineStr"/>
       <c r="O21" s="5" t="inlineStr"/>
       <c r="P21" s="5" t="inlineStr"/>
-      <c r="Q21" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q21" s="5" t="inlineStr"/>
       <c r="R21" s="5" t="inlineStr"/>
-      <c r="S21" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S21" s="5" t="inlineStr"/>
       <c r="T21" s="5" t="inlineStr"/>
-      <c r="U21" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U21" s="5" t="inlineStr"/>
       <c r="V21" s="5" t="inlineStr"/>
     </row>
     <row r="22">
@@ -5076,20 +5772,60 @@
       </c>
       <c r="G22" s="5" t="inlineStr"/>
       <c r="H22" s="5" t="inlineStr"/>
-      <c r="I22" s="5" t="inlineStr"/>
-      <c r="J22" s="5" t="inlineStr"/>
-      <c r="K22" s="5" t="inlineStr"/>
-      <c r="L22" s="5" t="inlineStr"/>
-      <c r="M22" s="5" t="inlineStr"/>
-      <c r="N22" s="5" t="inlineStr"/>
-      <c r="O22" s="5" t="inlineStr"/>
-      <c r="P22" s="5" t="inlineStr"/>
-      <c r="Q22" s="5" t="inlineStr"/>
-      <c r="R22" s="5" t="inlineStr"/>
-      <c r="S22" s="5" t="inlineStr"/>
-      <c r="T22" s="5" t="inlineStr"/>
-      <c r="U22" s="5" t="inlineStr"/>
-      <c r="V22" s="5" t="inlineStr"/>
+      <c r="I22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q22" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R22" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="S22" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T22" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="U22" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V22" s="5" t="n">
+        <v>0.09333333333333334</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
@@ -5112,24 +5848,64 @@
         <v>0.0518</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>0.0381</v>
+        <v>0.0382</v>
       </c>
       <c r="G23" s="5" t="inlineStr"/>
       <c r="H23" s="5" t="inlineStr"/>
-      <c r="I23" s="5" t="inlineStr"/>
-      <c r="J23" s="5" t="inlineStr"/>
-      <c r="K23" s="5" t="inlineStr"/>
-      <c r="L23" s="5" t="inlineStr"/>
-      <c r="M23" s="5" t="inlineStr"/>
-      <c r="N23" s="5" t="inlineStr"/>
-      <c r="O23" s="5" t="inlineStr"/>
-      <c r="P23" s="5" t="inlineStr"/>
-      <c r="Q23" s="5" t="inlineStr"/>
-      <c r="R23" s="5" t="inlineStr"/>
-      <c r="S23" s="5" t="inlineStr"/>
-      <c r="T23" s="5" t="inlineStr"/>
-      <c r="U23" s="5" t="inlineStr"/>
-      <c r="V23" s="5" t="inlineStr"/>
+      <c r="I23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q23" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R23" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="S23" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T23" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="U23" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V23" s="5" t="n">
+        <v>0.05</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
@@ -5149,27 +5925,67 @@
         <v>0.9614</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>0.0062</v>
+        <v>0.005</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>0.0178</v>
+        <v>0.0162</v>
       </c>
       <c r="G24" s="5" t="inlineStr"/>
       <c r="H24" s="5" t="inlineStr"/>
-      <c r="I24" s="5" t="inlineStr"/>
-      <c r="J24" s="5" t="inlineStr"/>
-      <c r="K24" s="5" t="inlineStr"/>
-      <c r="L24" s="5" t="inlineStr"/>
-      <c r="M24" s="5" t="inlineStr"/>
-      <c r="N24" s="5" t="inlineStr"/>
-      <c r="O24" s="5" t="inlineStr"/>
-      <c r="P24" s="5" t="inlineStr"/>
-      <c r="Q24" s="5" t="inlineStr"/>
-      <c r="R24" s="5" t="inlineStr"/>
-      <c r="S24" s="5" t="inlineStr"/>
-      <c r="T24" s="5" t="inlineStr"/>
-      <c r="U24" s="5" t="inlineStr"/>
-      <c r="V24" s="5" t="inlineStr"/>
+      <c r="I24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="Q24" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R24" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="S24" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T24" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="U24" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V24" s="5" t="n">
+        <v>0.05333333333333334</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
@@ -5192,24 +6008,64 @@
         <v>0.1796</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>0.094</v>
+        <v>0.0939</v>
       </c>
       <c r="G25" s="5" t="inlineStr"/>
       <c r="H25" s="5" t="inlineStr"/>
-      <c r="I25" s="5" t="inlineStr"/>
-      <c r="J25" s="5" t="inlineStr"/>
-      <c r="K25" s="5" t="inlineStr"/>
-      <c r="L25" s="5" t="inlineStr"/>
-      <c r="M25" s="5" t="inlineStr"/>
-      <c r="N25" s="5" t="inlineStr"/>
-      <c r="O25" s="5" t="inlineStr"/>
-      <c r="P25" s="5" t="inlineStr"/>
-      <c r="Q25" s="5" t="inlineStr"/>
-      <c r="R25" s="5" t="inlineStr"/>
-      <c r="S25" s="5" t="inlineStr"/>
-      <c r="T25" s="5" t="inlineStr"/>
-      <c r="U25" s="5" t="inlineStr"/>
-      <c r="V25" s="5" t="inlineStr"/>
+      <c r="I25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="Q25" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R25" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="S25" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T25" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="U25" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V25" s="5" t="n">
+        <v>0.05333333333333334</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
@@ -5230,24 +6086,64 @@
       </c>
       <c r="E26" s="5" t="inlineStr"/>
       <c r="F26" s="5" t="n">
-        <v>0.2785</v>
+        <v>0.2788</v>
       </c>
       <c r="G26" s="5" t="inlineStr"/>
       <c r="H26" s="5" t="inlineStr"/>
-      <c r="I26" s="5" t="inlineStr"/>
-      <c r="J26" s="5" t="inlineStr"/>
-      <c r="K26" s="5" t="inlineStr"/>
-      <c r="L26" s="5" t="inlineStr"/>
-      <c r="M26" s="5" t="inlineStr"/>
-      <c r="N26" s="5" t="inlineStr"/>
-      <c r="O26" s="5" t="inlineStr"/>
-      <c r="P26" s="5" t="inlineStr"/>
-      <c r="Q26" s="5" t="inlineStr"/>
-      <c r="R26" s="5" t="inlineStr"/>
-      <c r="S26" s="5" t="inlineStr"/>
-      <c r="T26" s="5" t="inlineStr"/>
-      <c r="U26" s="5" t="inlineStr"/>
-      <c r="V26" s="5" t="inlineStr"/>
+      <c r="I26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="Q26" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R26" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="S26" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T26" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="U26" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V26" s="5" t="n">
+        <v>0.05333333333333334</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
@@ -5267,27 +6163,67 @@
         <v>0.9628</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>0.1209</v>
+        <v>0.1208</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>0.1935</v>
+        <v>0.1932</v>
       </c>
       <c r="G27" s="5" t="inlineStr"/>
       <c r="H27" s="5" t="inlineStr"/>
-      <c r="I27" s="5" t="inlineStr"/>
-      <c r="J27" s="5" t="inlineStr"/>
-      <c r="K27" s="5" t="inlineStr"/>
-      <c r="L27" s="5" t="inlineStr"/>
-      <c r="M27" s="5" t="inlineStr"/>
-      <c r="N27" s="5" t="inlineStr"/>
-      <c r="O27" s="5" t="inlineStr"/>
-      <c r="P27" s="5" t="inlineStr"/>
-      <c r="Q27" s="5" t="inlineStr"/>
-      <c r="R27" s="5" t="inlineStr"/>
-      <c r="S27" s="5" t="inlineStr"/>
-      <c r="T27" s="5" t="inlineStr"/>
-      <c r="U27" s="5" t="inlineStr"/>
-      <c r="V27" s="5" t="inlineStr"/>
+      <c r="I27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="Q27" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R27" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="S27" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T27" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="U27" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V27" s="5" t="n">
+        <v>0.05333333333333334</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
@@ -5307,27 +6243,67 @@
         <v>0.9606</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>0.1083</v>
+        <v>0.1084</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>0.1916</v>
+        <v>0.1913</v>
       </c>
       <c r="G28" s="5" t="inlineStr"/>
       <c r="H28" s="5" t="inlineStr"/>
-      <c r="I28" s="5" t="inlineStr"/>
-      <c r="J28" s="5" t="inlineStr"/>
-      <c r="K28" s="5" t="inlineStr"/>
-      <c r="L28" s="5" t="inlineStr"/>
-      <c r="M28" s="5" t="inlineStr"/>
-      <c r="N28" s="5" t="inlineStr"/>
-      <c r="O28" s="5" t="inlineStr"/>
-      <c r="P28" s="5" t="inlineStr"/>
-      <c r="Q28" s="5" t="inlineStr"/>
-      <c r="R28" s="5" t="inlineStr"/>
-      <c r="S28" s="5" t="inlineStr"/>
-      <c r="T28" s="5" t="inlineStr"/>
-      <c r="U28" s="5" t="inlineStr"/>
-      <c r="V28" s="5" t="inlineStr"/>
+      <c r="I28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="Q28" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R28" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="S28" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T28" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="U28" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V28" s="5" t="n">
+        <v>0.05333333333333334</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
@@ -5347,27 +6323,67 @@
         <v>0.9533</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>0.0034</v>
+        <v>0.001</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>0.0016</v>
+        <v>0</v>
       </c>
       <c r="G29" s="5" t="inlineStr"/>
       <c r="H29" s="5" t="inlineStr"/>
-      <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="5" t="inlineStr"/>
-      <c r="K29" s="5" t="inlineStr"/>
-      <c r="L29" s="5" t="inlineStr"/>
-      <c r="M29" s="5" t="inlineStr"/>
-      <c r="N29" s="5" t="inlineStr"/>
-      <c r="O29" s="5" t="inlineStr"/>
-      <c r="P29" s="5" t="inlineStr"/>
-      <c r="Q29" s="5" t="inlineStr"/>
-      <c r="R29" s="5" t="inlineStr"/>
-      <c r="S29" s="5" t="inlineStr"/>
-      <c r="T29" s="5" t="inlineStr"/>
-      <c r="U29" s="5" t="inlineStr"/>
-      <c r="V29" s="5" t="inlineStr"/>
+      <c r="I29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="Q29" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R29" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="S29" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T29" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="U29" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V29" s="5" t="n">
+        <v>0.05333333333333334</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
@@ -5387,27 +6403,67 @@
         <v>0.9533</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>0.0038</v>
+        <v>0</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>0.0011</v>
+        <v>0</v>
       </c>
       <c r="G30" s="5" t="inlineStr"/>
       <c r="H30" s="5" t="inlineStr"/>
-      <c r="I30" s="5" t="inlineStr"/>
-      <c r="J30" s="5" t="inlineStr"/>
-      <c r="K30" s="5" t="inlineStr"/>
-      <c r="L30" s="5" t="inlineStr"/>
-      <c r="M30" s="5" t="inlineStr"/>
-      <c r="N30" s="5" t="inlineStr"/>
-      <c r="O30" s="5" t="inlineStr"/>
-      <c r="P30" s="5" t="inlineStr"/>
-      <c r="Q30" s="5" t="inlineStr"/>
-      <c r="R30" s="5" t="inlineStr"/>
-      <c r="S30" s="5" t="inlineStr"/>
-      <c r="T30" s="5" t="inlineStr"/>
-      <c r="U30" s="5" t="inlineStr"/>
-      <c r="V30" s="5" t="inlineStr"/>
+      <c r="I30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="Q30" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R30" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="S30" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T30" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="U30" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V30" s="5" t="n">
+        <v>0.05333333333333334</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
@@ -5427,27 +6483,67 @@
         <v>0.9533</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>0.0028</v>
+        <v>0</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>0.0015</v>
+        <v>0</v>
       </c>
       <c r="G31" s="5" t="inlineStr"/>
       <c r="H31" s="5" t="inlineStr"/>
-      <c r="I31" s="5" t="inlineStr"/>
-      <c r="J31" s="5" t="inlineStr"/>
-      <c r="K31" s="5" t="inlineStr"/>
-      <c r="L31" s="5" t="inlineStr"/>
-      <c r="M31" s="5" t="inlineStr"/>
-      <c r="N31" s="5" t="inlineStr"/>
-      <c r="O31" s="5" t="inlineStr"/>
-      <c r="P31" s="5" t="inlineStr"/>
-      <c r="Q31" s="5" t="inlineStr"/>
-      <c r="R31" s="5" t="inlineStr"/>
-      <c r="S31" s="5" t="inlineStr"/>
-      <c r="T31" s="5" t="inlineStr"/>
-      <c r="U31" s="5" t="inlineStr"/>
-      <c r="V31" s="5" t="inlineStr"/>
+      <c r="I31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="Q31" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R31" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="S31" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T31" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="U31" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V31" s="5" t="n">
+        <v>0.05333333333333334</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
@@ -5470,24 +6566,64 @@
         <v>0.2</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>0.2497</v>
+        <v>0.2496</v>
       </c>
       <c r="G32" s="5" t="inlineStr"/>
       <c r="H32" s="5" t="inlineStr"/>
-      <c r="I32" s="5" t="inlineStr"/>
-      <c r="J32" s="5" t="inlineStr"/>
-      <c r="K32" s="5" t="inlineStr"/>
-      <c r="L32" s="5" t="inlineStr"/>
-      <c r="M32" s="5" t="inlineStr"/>
-      <c r="N32" s="5" t="inlineStr"/>
-      <c r="O32" s="5" t="inlineStr"/>
-      <c r="P32" s="5" t="inlineStr"/>
-      <c r="Q32" s="5" t="inlineStr"/>
-      <c r="R32" s="5" t="inlineStr"/>
-      <c r="S32" s="5" t="inlineStr"/>
-      <c r="T32" s="5" t="inlineStr"/>
-      <c r="U32" s="5" t="inlineStr"/>
-      <c r="V32" s="5" t="inlineStr"/>
+      <c r="I32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q32" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R32" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="S32" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T32" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="U32" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V32" s="5" t="n">
+        <v>0.09333333333333334</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
@@ -5514,20 +6650,60 @@
       </c>
       <c r="G33" s="5" t="inlineStr"/>
       <c r="H33" s="5" t="inlineStr"/>
-      <c r="I33" s="5" t="inlineStr"/>
-      <c r="J33" s="5" t="inlineStr"/>
-      <c r="K33" s="5" t="inlineStr"/>
-      <c r="L33" s="5" t="inlineStr"/>
-      <c r="M33" s="5" t="inlineStr"/>
-      <c r="N33" s="5" t="inlineStr"/>
-      <c r="O33" s="5" t="inlineStr"/>
-      <c r="P33" s="5" t="inlineStr"/>
-      <c r="Q33" s="5" t="inlineStr"/>
-      <c r="R33" s="5" t="inlineStr"/>
-      <c r="S33" s="5" t="inlineStr"/>
-      <c r="T33" s="5" t="inlineStr"/>
-      <c r="U33" s="5" t="inlineStr"/>
-      <c r="V33" s="5" t="inlineStr"/>
+      <c r="I33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q33" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R33" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="S33" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T33" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="U33" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V33" s="5" t="n">
+        <v>0.09333333333333334</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
@@ -5550,24 +6726,64 @@
         <v>0.2637</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>0.3006</v>
+        <v>0.3005</v>
       </c>
       <c r="G34" s="5" t="inlineStr"/>
       <c r="H34" s="5" t="inlineStr"/>
-      <c r="I34" s="5" t="inlineStr"/>
-      <c r="J34" s="5" t="inlineStr"/>
-      <c r="K34" s="5" t="inlineStr"/>
-      <c r="L34" s="5" t="inlineStr"/>
-      <c r="M34" s="5" t="inlineStr"/>
-      <c r="N34" s="5" t="inlineStr"/>
-      <c r="O34" s="5" t="inlineStr"/>
-      <c r="P34" s="5" t="inlineStr"/>
-      <c r="Q34" s="5" t="inlineStr"/>
-      <c r="R34" s="5" t="inlineStr"/>
-      <c r="S34" s="5" t="inlineStr"/>
-      <c r="T34" s="5" t="inlineStr"/>
-      <c r="U34" s="5" t="inlineStr"/>
-      <c r="V34" s="5" t="inlineStr"/>
+      <c r="I34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q34" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R34" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="S34" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T34" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="U34" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V34" s="5" t="n">
+        <v>0.09333333333333334</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
@@ -5590,24 +6806,64 @@
         <v>0.1458</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>0.1783</v>
+        <v>0.1782</v>
       </c>
       <c r="G35" s="5" t="inlineStr"/>
       <c r="H35" s="5" t="inlineStr"/>
-      <c r="I35" s="5" t="inlineStr"/>
-      <c r="J35" s="5" t="inlineStr"/>
-      <c r="K35" s="5" t="inlineStr"/>
-      <c r="L35" s="5" t="inlineStr"/>
-      <c r="M35" s="5" t="inlineStr"/>
-      <c r="N35" s="5" t="inlineStr"/>
-      <c r="O35" s="5" t="inlineStr"/>
-      <c r="P35" s="5" t="inlineStr"/>
-      <c r="Q35" s="5" t="inlineStr"/>
-      <c r="R35" s="5" t="inlineStr"/>
-      <c r="S35" s="5" t="inlineStr"/>
-      <c r="T35" s="5" t="inlineStr"/>
-      <c r="U35" s="5" t="inlineStr"/>
-      <c r="V35" s="5" t="inlineStr"/>
+      <c r="I35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="Q35" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R35" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="S35" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T35" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="U35" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V35" s="5" t="n">
+        <v>0.07333333333333335</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
@@ -5630,24 +6886,64 @@
         <v>0.1653</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>0.1995</v>
+        <v>0.1994</v>
       </c>
       <c r="G36" s="5" t="inlineStr"/>
       <c r="H36" s="5" t="inlineStr"/>
-      <c r="I36" s="5" t="inlineStr"/>
-      <c r="J36" s="5" t="inlineStr"/>
-      <c r="K36" s="5" t="inlineStr"/>
-      <c r="L36" s="5" t="inlineStr"/>
-      <c r="M36" s="5" t="inlineStr"/>
-      <c r="N36" s="5" t="inlineStr"/>
-      <c r="O36" s="5" t="inlineStr"/>
-      <c r="P36" s="5" t="inlineStr"/>
-      <c r="Q36" s="5" t="inlineStr"/>
-      <c r="R36" s="5" t="inlineStr"/>
-      <c r="S36" s="5" t="inlineStr"/>
-      <c r="T36" s="5" t="inlineStr"/>
-      <c r="U36" s="5" t="inlineStr"/>
-      <c r="V36" s="5" t="inlineStr"/>
+      <c r="I36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="Q36" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R36" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="S36" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T36" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="U36" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V36" s="5" t="n">
+        <v>0.07333333333333335</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
@@ -5670,24 +6966,64 @@
         <v>0.3052</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>0.1511</v>
+        <v>0.151</v>
       </c>
       <c r="G37" s="5" t="inlineStr"/>
       <c r="H37" s="5" t="inlineStr"/>
-      <c r="I37" s="5" t="inlineStr"/>
-      <c r="J37" s="5" t="inlineStr"/>
-      <c r="K37" s="5" t="inlineStr"/>
-      <c r="L37" s="5" t="inlineStr"/>
-      <c r="M37" s="5" t="inlineStr"/>
-      <c r="N37" s="5" t="inlineStr"/>
-      <c r="O37" s="5" t="inlineStr"/>
-      <c r="P37" s="5" t="inlineStr"/>
-      <c r="Q37" s="5" t="inlineStr"/>
-      <c r="R37" s="5" t="inlineStr"/>
-      <c r="S37" s="5" t="inlineStr"/>
-      <c r="T37" s="5" t="inlineStr"/>
-      <c r="U37" s="5" t="inlineStr"/>
-      <c r="V37" s="5" t="inlineStr"/>
+      <c r="I37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q37" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R37" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="S37" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T37" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="U37" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V37" s="5" t="n">
+        <v>0.05</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
@@ -5710,24 +7046,64 @@
         <v>0.1223</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>0.1729</v>
+        <v>0.1727</v>
       </c>
       <c r="G38" s="5" t="inlineStr"/>
       <c r="H38" s="5" t="inlineStr"/>
-      <c r="I38" s="5" t="inlineStr"/>
-      <c r="J38" s="5" t="inlineStr"/>
-      <c r="K38" s="5" t="inlineStr"/>
-      <c r="L38" s="5" t="inlineStr"/>
-      <c r="M38" s="5" t="inlineStr"/>
-      <c r="N38" s="5" t="inlineStr"/>
-      <c r="O38" s="5" t="inlineStr"/>
-      <c r="P38" s="5" t="inlineStr"/>
-      <c r="Q38" s="5" t="inlineStr"/>
-      <c r="R38" s="5" t="inlineStr"/>
-      <c r="S38" s="5" t="inlineStr"/>
-      <c r="T38" s="5" t="inlineStr"/>
-      <c r="U38" s="5" t="inlineStr"/>
-      <c r="V38" s="5" t="inlineStr"/>
+      <c r="I38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="Q38" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R38" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="S38" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T38" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="U38" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V38" s="5" t="n">
+        <v>0.05333333333333334</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
@@ -5750,24 +7126,64 @@
         <v>0.1999</v>
       </c>
       <c r="F39" s="5" t="n">
-        <v>0.2153</v>
+        <v>0.2151</v>
       </c>
       <c r="G39" s="5" t="inlineStr"/>
       <c r="H39" s="5" t="inlineStr"/>
-      <c r="I39" s="5" t="inlineStr"/>
-      <c r="J39" s="5" t="inlineStr"/>
-      <c r="K39" s="5" t="inlineStr"/>
-      <c r="L39" s="5" t="inlineStr"/>
-      <c r="M39" s="5" t="inlineStr"/>
-      <c r="N39" s="5" t="inlineStr"/>
-      <c r="O39" s="5" t="inlineStr"/>
-      <c r="P39" s="5" t="inlineStr"/>
-      <c r="Q39" s="5" t="inlineStr"/>
-      <c r="R39" s="5" t="inlineStr"/>
-      <c r="S39" s="5" t="inlineStr"/>
-      <c r="T39" s="5" t="inlineStr"/>
-      <c r="U39" s="5" t="inlineStr"/>
-      <c r="V39" s="5" t="inlineStr"/>
+      <c r="I39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="Q39" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R39" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="S39" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T39" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="U39" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V39" s="5" t="n">
+        <v>0.07333333333333335</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
@@ -5787,27 +7203,67 @@
         <v>0.9699</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>0.0037</v>
+        <v>0.0035</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>0.0022</v>
+        <v>0</v>
       </c>
       <c r="G40" s="5" t="inlineStr"/>
       <c r="H40" s="5" t="inlineStr"/>
-      <c r="I40" s="5" t="inlineStr"/>
-      <c r="J40" s="5" t="inlineStr"/>
-      <c r="K40" s="5" t="inlineStr"/>
-      <c r="L40" s="5" t="inlineStr"/>
-      <c r="M40" s="5" t="inlineStr"/>
-      <c r="N40" s="5" t="inlineStr"/>
-      <c r="O40" s="5" t="inlineStr"/>
-      <c r="P40" s="5" t="inlineStr"/>
-      <c r="Q40" s="5" t="inlineStr"/>
-      <c r="R40" s="5" t="inlineStr"/>
-      <c r="S40" s="5" t="inlineStr"/>
-      <c r="T40" s="5" t="inlineStr"/>
-      <c r="U40" s="5" t="inlineStr"/>
-      <c r="V40" s="5" t="inlineStr"/>
+      <c r="I40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="Q40" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R40" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="S40" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T40" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="U40" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V40" s="5" t="n">
+        <v>0.05333333333333334</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
@@ -5827,27 +7283,67 @@
         <v>0.9699</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>0.0027</v>
+        <v>0</v>
       </c>
       <c r="F41" s="5" t="n">
-        <v>0.0027</v>
+        <v>0.0011</v>
       </c>
       <c r="G41" s="5" t="inlineStr"/>
       <c r="H41" s="5" t="inlineStr"/>
-      <c r="I41" s="5" t="inlineStr"/>
-      <c r="J41" s="5" t="inlineStr"/>
-      <c r="K41" s="5" t="inlineStr"/>
-      <c r="L41" s="5" t="inlineStr"/>
-      <c r="M41" s="5" t="inlineStr"/>
-      <c r="N41" s="5" t="inlineStr"/>
-      <c r="O41" s="5" t="inlineStr"/>
-      <c r="P41" s="5" t="inlineStr"/>
-      <c r="Q41" s="5" t="inlineStr"/>
-      <c r="R41" s="5" t="inlineStr"/>
-      <c r="S41" s="5" t="inlineStr"/>
-      <c r="T41" s="5" t="inlineStr"/>
-      <c r="U41" s="5" t="inlineStr"/>
-      <c r="V41" s="5" t="inlineStr"/>
+      <c r="I41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="Q41" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R41" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="S41" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T41" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="U41" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V41" s="5" t="n">
+        <v>0.05333333333333334</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="8" t="inlineStr">
@@ -5870,24 +7366,64 @@
         <v>0.1863</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>0.2696</v>
+        <v>0.2693</v>
       </c>
       <c r="G42" s="5" t="inlineStr"/>
       <c r="H42" s="5" t="inlineStr"/>
-      <c r="I42" s="5" t="inlineStr"/>
-      <c r="J42" s="5" t="inlineStr"/>
-      <c r="K42" s="5" t="inlineStr"/>
-      <c r="L42" s="5" t="inlineStr"/>
-      <c r="M42" s="5" t="inlineStr"/>
-      <c r="N42" s="5" t="inlineStr"/>
-      <c r="O42" s="5" t="inlineStr"/>
-      <c r="P42" s="5" t="inlineStr"/>
-      <c r="Q42" s="5" t="inlineStr"/>
-      <c r="R42" s="5" t="inlineStr"/>
-      <c r="S42" s="5" t="inlineStr"/>
-      <c r="T42" s="5" t="inlineStr"/>
-      <c r="U42" s="5" t="inlineStr"/>
-      <c r="V42" s="5" t="inlineStr"/>
+      <c r="I42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="Q42" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R42" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="S42" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T42" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="U42" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V42" s="5" t="n">
+        <v>0.05333333333333334</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
@@ -5947,27 +7483,67 @@
         <v>0.9572000000000001</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>0.0906</v>
+        <v>0.0886</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>0.1905</v>
+        <v>0.1901</v>
       </c>
       <c r="G44" s="5" t="inlineStr"/>
       <c r="H44" s="5" t="inlineStr"/>
-      <c r="I44" s="5" t="inlineStr"/>
-      <c r="J44" s="5" t="inlineStr"/>
-      <c r="K44" s="5" t="inlineStr"/>
-      <c r="L44" s="5" t="inlineStr"/>
-      <c r="M44" s="5" t="inlineStr"/>
-      <c r="N44" s="5" t="inlineStr"/>
-      <c r="O44" s="5" t="inlineStr"/>
-      <c r="P44" s="5" t="inlineStr"/>
-      <c r="Q44" s="5" t="inlineStr"/>
-      <c r="R44" s="5" t="inlineStr"/>
-      <c r="S44" s="5" t="inlineStr"/>
-      <c r="T44" s="5" t="inlineStr"/>
-      <c r="U44" s="5" t="inlineStr"/>
-      <c r="V44" s="5" t="inlineStr"/>
+      <c r="I44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="Q44" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R44" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="S44" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T44" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="U44" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V44" s="5" t="n">
+        <v>0.05333333333333334</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
@@ -5987,27 +7563,71 @@
         <v>0.9611</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>0.0206</v>
+        <v>0.0205</v>
       </c>
       <c r="F45" s="5" t="n">
-        <v>0.0121</v>
-      </c>
-      <c r="G45" s="5" t="inlineStr"/>
-      <c r="H45" s="5" t="inlineStr"/>
-      <c r="I45" s="5" t="inlineStr"/>
-      <c r="J45" s="5" t="inlineStr"/>
-      <c r="K45" s="5" t="inlineStr"/>
-      <c r="L45" s="5" t="inlineStr"/>
-      <c r="M45" s="5" t="inlineStr"/>
-      <c r="N45" s="5" t="inlineStr"/>
-      <c r="O45" s="5" t="inlineStr"/>
-      <c r="P45" s="5" t="inlineStr"/>
-      <c r="Q45" s="5" t="inlineStr"/>
-      <c r="R45" s="5" t="inlineStr"/>
-      <c r="S45" s="5" t="inlineStr"/>
-      <c r="T45" s="5" t="inlineStr"/>
-      <c r="U45" s="5" t="inlineStr"/>
-      <c r="V45" s="5" t="inlineStr"/>
+        <v>0.0109</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>0.691487736497032</v>
+      </c>
+      <c r="H45" s="5" t="n">
+        <v>0.402744462066548</v>
+      </c>
+      <c r="I45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="Q45" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R45" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="S45" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T45" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="U45" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V45" s="5" t="n">
+        <v>0.05333333333333334</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
@@ -6030,24 +7650,64 @@
         <v>0.1686</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>0.2013</v>
+        <v>0.2012</v>
       </c>
       <c r="G46" s="5" t="inlineStr"/>
       <c r="H46" s="5" t="inlineStr"/>
-      <c r="I46" s="5" t="inlineStr"/>
-      <c r="J46" s="5" t="inlineStr"/>
-      <c r="K46" s="5" t="inlineStr"/>
-      <c r="L46" s="5" t="inlineStr"/>
-      <c r="M46" s="5" t="inlineStr"/>
-      <c r="N46" s="5" t="inlineStr"/>
-      <c r="O46" s="5" t="inlineStr"/>
-      <c r="P46" s="5" t="inlineStr"/>
-      <c r="Q46" s="5" t="inlineStr"/>
-      <c r="R46" s="5" t="inlineStr"/>
-      <c r="S46" s="5" t="inlineStr"/>
-      <c r="T46" s="5" t="inlineStr"/>
-      <c r="U46" s="5" t="inlineStr"/>
-      <c r="V46" s="5" t="inlineStr"/>
+      <c r="I46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q46" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R46" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="S46" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T46" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="U46" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V46" s="5" t="n">
+        <v>0.09333333333333334</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
@@ -6070,24 +7730,64 @@
         <v>0.0432</v>
       </c>
       <c r="F47" s="5" t="n">
-        <v>0.0341</v>
+        <v>0.0337</v>
       </c>
       <c r="G47" s="5" t="inlineStr"/>
       <c r="H47" s="5" t="inlineStr"/>
-      <c r="I47" s="5" t="inlineStr"/>
-      <c r="J47" s="5" t="inlineStr"/>
-      <c r="K47" s="5" t="inlineStr"/>
-      <c r="L47" s="5" t="inlineStr"/>
-      <c r="M47" s="5" t="inlineStr"/>
-      <c r="N47" s="5" t="inlineStr"/>
-      <c r="O47" s="5" t="inlineStr"/>
-      <c r="P47" s="5" t="inlineStr"/>
-      <c r="Q47" s="5" t="inlineStr"/>
-      <c r="R47" s="5" t="inlineStr"/>
-      <c r="S47" s="5" t="inlineStr"/>
-      <c r="T47" s="5" t="inlineStr"/>
-      <c r="U47" s="5" t="inlineStr"/>
-      <c r="V47" s="5" t="inlineStr"/>
+      <c r="I47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="Q47" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R47" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="S47" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T47" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="U47" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V47" s="5" t="n">
+        <v>0.05333333333333334</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="C2:C47">

--- a/outputs/SA_curtailment.xlsx
+++ b/outputs/SA_curtailment.xlsx
@@ -922,7 +922,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>per-DUID</t>
+          <t>location</t>
         </is>
       </c>
       <c r="P6" s="5" t="n">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>per-DUID</t>
+          <t>location</t>
         </is>
       </c>
       <c r="P7" s="5" t="n">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>per-DUID</t>
+          <t>location</t>
         </is>
       </c>
       <c r="P10" s="5" t="n">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>per-DUID</t>
+          <t>location</t>
         </is>
       </c>
       <c r="P11" s="5" t="n">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>per-DUID</t>
+          <t>location</t>
         </is>
       </c>
       <c r="P12" s="5" t="n">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>per-DUID</t>
+          <t>location</t>
         </is>
       </c>
       <c r="P13" s="5" t="n">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>per-DUID</t>
+          <t>location</t>
         </is>
       </c>
       <c r="P14" s="5" t="n">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>per-DUID</t>
+          <t>location</t>
         </is>
       </c>
       <c r="P15" s="5" t="n">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>per-DUID</t>
+          <t>location</t>
         </is>
       </c>
       <c r="P16" s="5" t="n">
@@ -1853,7 +1853,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>per-DUID</t>
+          <t>location</t>
         </is>
       </c>
       <c r="P17" s="5" t="n">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>per-DUID</t>
+          <t>location</t>
         </is>
       </c>
       <c r="P18" s="5" t="n">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>per-DUID</t>
+          <t>location</t>
         </is>
       </c>
       <c r="P19" s="5" t="n">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>per-DUID</t>
+          <t>location</t>
         </is>
       </c>
       <c r="P20" s="5" t="n">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>per-DUID</t>
+          <t>location</t>
         </is>
       </c>
       <c r="P21" s="5" t="n">

--- a/outputs/SA_curtailment.xlsx
+++ b/outputs/SA_curtailment.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y47"/>
+  <dimension ref="A1:AG47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -484,6 +484,14 @@
     <col width="12" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="27" max="27"/>
+    <col width="12" customWidth="1" min="28" max="28"/>
+    <col width="12" customWidth="1" min="29" max="29"/>
+    <col width="12" customWidth="1" min="30" max="30"/>
+    <col width="12" customWidth="1" min="31" max="31"/>
+    <col width="12" customWidth="1" min="32" max="32"/>
+    <col width="12" customWidth="1" min="33" max="33"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -610,6 +618,46 @@
       <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Offl Avg</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>2026 ISP REZ</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>2026 ISP REZ match</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>2026 ISP Step Change Transm Curt 2029-30</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>2026 ISP Step Change Transm Curt 2039-40</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>2026 ISP Step Change Transm Curt 2049-50</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>2026 ISP Step Change Econ Spill 2029-30</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>2026 ISP Step Change Econ Spill 2039-40</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>2026 ISP Step Change Econ Spill 2049-50</t>
         </is>
       </c>
     </row>
@@ -675,6 +723,14 @@
       <c r="W2" s="6" t="inlineStr"/>
       <c r="X2" s="6" t="inlineStr"/>
       <c r="Y2" s="6" t="inlineStr"/>
+      <c r="Z2" s="2" t="inlineStr"/>
+      <c r="AA2" s="2" t="inlineStr"/>
+      <c r="AB2" s="6" t="inlineStr"/>
+      <c r="AC2" s="6" t="inlineStr"/>
+      <c r="AD2" s="6" t="inlineStr"/>
+      <c r="AE2" s="6" t="inlineStr"/>
+      <c r="AF2" s="6" t="inlineStr"/>
+      <c r="AG2" s="6" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -736,6 +792,14 @@
       <c r="W3" s="6" t="inlineStr"/>
       <c r="X3" s="6" t="inlineStr"/>
       <c r="Y3" s="6" t="inlineStr"/>
+      <c r="Z3" s="2" t="inlineStr"/>
+      <c r="AA3" s="2" t="inlineStr"/>
+      <c r="AB3" s="6" t="inlineStr"/>
+      <c r="AC3" s="6" t="inlineStr"/>
+      <c r="AD3" s="6" t="inlineStr"/>
+      <c r="AE3" s="6" t="inlineStr"/>
+      <c r="AF3" s="6" t="inlineStr"/>
+      <c r="AG3" s="6" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -797,6 +861,14 @@
       <c r="W4" s="6" t="inlineStr"/>
       <c r="X4" s="6" t="inlineStr"/>
       <c r="Y4" s="6" t="inlineStr"/>
+      <c r="Z4" s="2" t="inlineStr"/>
+      <c r="AA4" s="2" t="inlineStr"/>
+      <c r="AB4" s="6" t="inlineStr"/>
+      <c r="AC4" s="6" t="inlineStr"/>
+      <c r="AD4" s="6" t="inlineStr"/>
+      <c r="AE4" s="6" t="inlineStr"/>
+      <c r="AF4" s="6" t="inlineStr"/>
+      <c r="AG4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -862,6 +934,14 @@
       <c r="W5" s="6" t="inlineStr"/>
       <c r="X5" s="6" t="inlineStr"/>
       <c r="Y5" s="6" t="inlineStr"/>
+      <c r="Z5" s="2" t="inlineStr"/>
+      <c r="AA5" s="2" t="inlineStr"/>
+      <c r="AB5" s="6" t="inlineStr"/>
+      <c r="AC5" s="6" t="inlineStr"/>
+      <c r="AD5" s="6" t="inlineStr"/>
+      <c r="AE5" s="6" t="inlineStr"/>
+      <c r="AF5" s="6" t="inlineStr"/>
+      <c r="AG5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -955,6 +1035,34 @@
       <c r="Y6" s="6" t="n">
         <v>0.07333333333333335</v>
       </c>
+      <c r="Z6" s="2" t="inlineStr">
+        <is>
+          <t>Northern South Australia</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AB6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AG6" s="6" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1049,6 +1157,34 @@
       </c>
       <c r="Y7" s="6" t="n">
         <v>0.07333333333333335</v>
+      </c>
+      <c r="Z7" s="2" t="inlineStr">
+        <is>
+          <t>Northern South Australia</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AB7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AG7" s="6" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="8">
@@ -1099,6 +1235,14 @@
       <c r="W8" s="6" t="inlineStr"/>
       <c r="X8" s="6" t="inlineStr"/>
       <c r="Y8" s="6" t="inlineStr"/>
+      <c r="Z8" s="2" t="inlineStr"/>
+      <c r="AA8" s="2" t="inlineStr"/>
+      <c r="AB8" s="6" t="inlineStr"/>
+      <c r="AC8" s="6" t="inlineStr"/>
+      <c r="AD8" s="6" t="inlineStr"/>
+      <c r="AE8" s="6" t="inlineStr"/>
+      <c r="AF8" s="6" t="inlineStr"/>
+      <c r="AG8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1148,6 +1292,14 @@
       <c r="W9" s="6" t="inlineStr"/>
       <c r="X9" s="6" t="inlineStr"/>
       <c r="Y9" s="6" t="inlineStr"/>
+      <c r="Z9" s="2" t="inlineStr"/>
+      <c r="AA9" s="2" t="inlineStr"/>
+      <c r="AB9" s="6" t="inlineStr"/>
+      <c r="AC9" s="6" t="inlineStr"/>
+      <c r="AD9" s="6" t="inlineStr"/>
+      <c r="AE9" s="6" t="inlineStr"/>
+      <c r="AF9" s="6" t="inlineStr"/>
+      <c r="AG9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1227,6 +1379,14 @@
       <c r="W10" s="6" t="inlineStr"/>
       <c r="X10" s="6" t="inlineStr"/>
       <c r="Y10" s="6" t="inlineStr"/>
+      <c r="Z10" s="2" t="inlineStr"/>
+      <c r="AA10" s="2" t="inlineStr"/>
+      <c r="AB10" s="6" t="inlineStr"/>
+      <c r="AC10" s="6" t="inlineStr"/>
+      <c r="AD10" s="6" t="inlineStr"/>
+      <c r="AE10" s="6" t="inlineStr"/>
+      <c r="AF10" s="6" t="inlineStr"/>
+      <c r="AG10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1319,6 +1479,34 @@
       </c>
       <c r="Y11" s="6" t="n">
         <v>0.09333333333333334</v>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>South East</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>renamed</t>
+        </is>
+      </c>
+      <c r="AB11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AG11" s="6" t="n">
+        <v>0.11</v>
       </c>
     </row>
     <row r="12">
@@ -1411,6 +1599,34 @@
       <c r="Y12" s="6" t="n">
         <v>0.09333333333333334</v>
       </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>South East</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>renamed</t>
+        </is>
+      </c>
+      <c r="AB12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AG12" s="6" t="n">
+        <v>0.11</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1506,6 +1722,34 @@
       <c r="Y13" s="6" t="n">
         <v>0.16</v>
       </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>Riverland</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AB13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AG13" s="6" t="n">
+        <v>0.26</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1601,6 +1845,34 @@
       <c r="Y14" s="6" t="n">
         <v>0.16</v>
       </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>Riverland</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AB14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AG14" s="6" t="n">
+        <v>0.26</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1696,6 +1968,34 @@
       <c r="Y15" s="6" t="n">
         <v>0.16</v>
       </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>Riverland</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AB15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AG15" s="6" t="n">
+        <v>0.26</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1791,6 +2091,34 @@
       <c r="Y16" s="6" t="n">
         <v>0.16</v>
       </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>Riverland</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AB16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AG16" s="6" t="n">
+        <v>0.26</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1886,6 +2214,34 @@
       <c r="Y17" s="6" t="n">
         <v>0.16</v>
       </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>Riverland</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AB17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AG17" s="6" t="n">
+        <v>0.26</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1979,6 +2335,34 @@
       <c r="Y18" s="6" t="n">
         <v>0.09333333333333334</v>
       </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>South East</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>renamed</t>
+        </is>
+      </c>
+      <c r="AB18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AG18" s="6" t="n">
+        <v>0.11</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -2073,6 +2457,34 @@
       </c>
       <c r="Y19" s="6" t="n">
         <v>0.07333333333333335</v>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>Northern South Australia</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AB19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AG19" s="6" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="20">
@@ -2153,6 +2565,14 @@
       <c r="W20" s="6" t="inlineStr"/>
       <c r="X20" s="6" t="inlineStr"/>
       <c r="Y20" s="6" t="inlineStr"/>
+      <c r="Z20" s="2" t="inlineStr"/>
+      <c r="AA20" s="2" t="inlineStr"/>
+      <c r="AB20" s="6" t="inlineStr"/>
+      <c r="AC20" s="6" t="inlineStr"/>
+      <c r="AD20" s="6" t="inlineStr"/>
+      <c r="AE20" s="6" t="inlineStr"/>
+      <c r="AF20" s="6" t="inlineStr"/>
+      <c r="AG20" s="6" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -2232,6 +2652,14 @@
       <c r="W21" s="6" t="inlineStr"/>
       <c r="X21" s="6" t="inlineStr"/>
       <c r="Y21" s="6" t="inlineStr"/>
+      <c r="Z21" s="2" t="inlineStr"/>
+      <c r="AA21" s="2" t="inlineStr"/>
+      <c r="AB21" s="6" t="inlineStr"/>
+      <c r="AC21" s="6" t="inlineStr"/>
+      <c r="AD21" s="6" t="inlineStr"/>
+      <c r="AE21" s="6" t="inlineStr"/>
+      <c r="AF21" s="6" t="inlineStr"/>
+      <c r="AG21" s="6" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -2313,6 +2741,34 @@
       <c r="Y22" s="6" t="n">
         <v>0.09333333333333334</v>
       </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>South East</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>renamed</t>
+        </is>
+      </c>
+      <c r="AB22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF22" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AG22" s="6" t="n">
+        <v>0.11</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -2394,6 +2850,34 @@
       <c r="Y23" s="6" t="n">
         <v>0.05</v>
       </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Eyre Peninsula</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>renamed</t>
+        </is>
+      </c>
+      <c r="AB23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF23" s="6" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="AG23" s="6" t="n">
+        <v>0.18</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -2475,6 +2959,34 @@
       <c r="Y24" s="6" t="n">
         <v>0.05333333333333334</v>
       </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>Mid-North</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>renamed</t>
+        </is>
+      </c>
+      <c r="AB24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG24" s="6" t="n">
+        <v>0.09</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -2556,6 +3068,34 @@
       <c r="Y25" s="6" t="n">
         <v>0.05333333333333334</v>
       </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>Mid-North</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>renamed</t>
+        </is>
+      </c>
+      <c r="AB25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG25" s="6" t="n">
+        <v>0.09</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -2635,6 +3175,34 @@
       <c r="Y26" s="6" t="n">
         <v>0.05333333333333334</v>
       </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>Mid-North</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>renamed</t>
+        </is>
+      </c>
+      <c r="AB26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG26" s="6" t="n">
+        <v>0.09</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -2716,6 +3284,34 @@
       <c r="Y27" s="6" t="n">
         <v>0.05333333333333334</v>
       </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>Mid-North</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>renamed</t>
+        </is>
+      </c>
+      <c r="AB27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG27" s="6" t="n">
+        <v>0.09</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2797,6 +3393,34 @@
       <c r="Y28" s="6" t="n">
         <v>0.05333333333333334</v>
       </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>Mid-North</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>renamed</t>
+        </is>
+      </c>
+      <c r="AB28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG28" s="6" t="n">
+        <v>0.09</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -2878,6 +3502,34 @@
       <c r="Y29" s="6" t="n">
         <v>0.05333333333333334</v>
       </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>Mid-North</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>renamed</t>
+        </is>
+      </c>
+      <c r="AB29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="6" t="n">
+        <v>0.09</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2959,6 +3611,34 @@
       <c r="Y30" s="6" t="n">
         <v>0.05333333333333334</v>
       </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>Mid-North</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>renamed</t>
+        </is>
+      </c>
+      <c r="AB30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG30" s="6" t="n">
+        <v>0.09</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -3040,6 +3720,34 @@
       <c r="Y31" s="6" t="n">
         <v>0.05333333333333334</v>
       </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>Mid-North</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>renamed</t>
+        </is>
+      </c>
+      <c r="AB31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG31" s="6" t="n">
+        <v>0.09</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -3121,6 +3829,34 @@
       <c r="Y32" s="6" t="n">
         <v>0.09333333333333334</v>
       </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>South East</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>renamed</t>
+        </is>
+      </c>
+      <c r="AB32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF32" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AG32" s="6" t="n">
+        <v>0.11</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -3202,6 +3938,34 @@
       <c r="Y33" s="6" t="n">
         <v>0.09333333333333334</v>
       </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>South East</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>renamed</t>
+        </is>
+      </c>
+      <c r="AB33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF33" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AG33" s="6" t="n">
+        <v>0.11</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -3283,6 +4047,34 @@
       <c r="Y34" s="6" t="n">
         <v>0.09333333333333334</v>
       </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>South East</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>renamed</t>
+        </is>
+      </c>
+      <c r="AB34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF34" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AG34" s="6" t="n">
+        <v>0.11</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -3364,6 +4156,34 @@
       <c r="Y35" s="6" t="n">
         <v>0.07333333333333335</v>
       </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>Northern South Australia</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AB35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AG35" s="6" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -3445,6 +4265,34 @@
       <c r="Y36" s="6" t="n">
         <v>0.07333333333333335</v>
       </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>Northern South Australia</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AB36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF36" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AG36" s="6" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -3526,6 +4374,34 @@
       <c r="Y37" s="6" t="n">
         <v>0.05</v>
       </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Eyre Peninsula</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>renamed</t>
+        </is>
+      </c>
+      <c r="AB37" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC37" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD37" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE37" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF37" s="6" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="AG37" s="6" t="n">
+        <v>0.18</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -3607,6 +4483,34 @@
       <c r="Y38" s="6" t="n">
         <v>0.05333333333333334</v>
       </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>Mid-North</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>renamed</t>
+        </is>
+      </c>
+      <c r="AB38" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC38" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD38" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE38" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF38" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG38" s="6" t="n">
+        <v>0.09</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -3688,6 +4592,34 @@
       <c r="Y39" s="6" t="n">
         <v>0.07333333333333335</v>
       </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>Northern South Australia</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AB39" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC39" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD39" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE39" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF39" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AG39" s="6" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -3769,6 +4701,34 @@
       <c r="Y40" s="6" t="n">
         <v>0.05333333333333334</v>
       </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>Mid-North</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>renamed</t>
+        </is>
+      </c>
+      <c r="AB40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG40" s="6" t="n">
+        <v>0.09</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -3850,6 +4810,34 @@
       <c r="Y41" s="6" t="n">
         <v>0.05333333333333334</v>
       </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>Mid-North</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>renamed</t>
+        </is>
+      </c>
+      <c r="AB41" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC41" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD41" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE41" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF41" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG41" s="6" t="n">
+        <v>0.09</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -3930,6 +4918,34 @@
       </c>
       <c r="Y42" s="6" t="n">
         <v>0.05333333333333334</v>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>Mid-North</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>renamed</t>
+        </is>
+      </c>
+      <c r="AB42" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD42" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE42" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF42" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG42" s="6" t="n">
+        <v>0.09</v>
       </c>
     </row>
     <row r="43">
@@ -3996,6 +5012,14 @@
       <c r="W43" s="6" t="inlineStr"/>
       <c r="X43" s="6" t="inlineStr"/>
       <c r="Y43" s="6" t="inlineStr"/>
+      <c r="Z43" s="2" t="inlineStr"/>
+      <c r="AA43" s="2" t="inlineStr"/>
+      <c r="AB43" s="6" t="inlineStr"/>
+      <c r="AC43" s="6" t="inlineStr"/>
+      <c r="AD43" s="6" t="inlineStr"/>
+      <c r="AE43" s="6" t="inlineStr"/>
+      <c r="AF43" s="6" t="inlineStr"/>
+      <c r="AG43" s="6" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -4077,6 +5101,34 @@
       <c r="Y44" s="6" t="n">
         <v>0.05333333333333334</v>
       </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>Mid-North</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>renamed</t>
+        </is>
+      </c>
+      <c r="AB44" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC44" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD44" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE44" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF44" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG44" s="6" t="n">
+        <v>0.09</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -4165,6 +5217,34 @@
       </c>
       <c r="Y45" s="6" t="n">
         <v>0.05333333333333334</v>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>Mid-North</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>renamed</t>
+        </is>
+      </c>
+      <c r="AB45" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC45" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD45" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE45" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF45" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG45" s="6" t="n">
+        <v>0.09</v>
       </c>
     </row>
     <row r="46">
@@ -4247,6 +5327,30 @@
       <c r="Y46" s="6" t="n">
         <v>0.09333333333333334</v>
       </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>Yorke Peninsula</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AB46" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC46" s="6" t="inlineStr"/>
+      <c r="AD46" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE46" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF46" s="6" t="inlineStr"/>
+      <c r="AG46" s="6" t="n">
+        <v>0.25</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -4327,6 +5431,34 @@
       </c>
       <c r="Y47" s="6" t="n">
         <v>0.05333333333333334</v>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>Mid-North</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>renamed</t>
+        </is>
+      </c>
+      <c r="AB47" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC47" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD47" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE47" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF47" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG47" s="6" t="n">
+        <v>0.09</v>
       </c>
     </row>
   </sheetData>
@@ -4340,7 +5472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V47"/>
+  <dimension ref="A1:AB47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4365,6 +5497,12 @@
     <col width="14" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="25" max="25"/>
+    <col width="14" customWidth="1" min="26" max="26"/>
+    <col width="14" customWidth="1" min="27" max="27"/>
+    <col width="14" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4476,6 +5614,36 @@
       <c r="V1" s="7" t="inlineStr">
         <is>
           <t>ISP_OFFLOADING_AVG</t>
+        </is>
+      </c>
+      <c r="W1" s="7" t="inlineStr">
+        <is>
+          <t>ISPA3_TRANSMISSION_Y1</t>
+        </is>
+      </c>
+      <c r="X1" s="7" t="inlineStr">
+        <is>
+          <t>ISPA3_TRANSMISSION_Y2</t>
+        </is>
+      </c>
+      <c r="Y1" s="7" t="inlineStr">
+        <is>
+          <t>ISPA3_TRANSMISSION_Y3</t>
+        </is>
+      </c>
+      <c r="Z1" s="7" t="inlineStr">
+        <is>
+          <t>ISPA3_SPILL_Y1</t>
+        </is>
+      </c>
+      <c r="AA1" s="7" t="inlineStr">
+        <is>
+          <t>ISPA3_SPILL_Y2</t>
+        </is>
+      </c>
+      <c r="AB1" s="7" t="inlineStr">
+        <is>
+          <t>ISPA3_SPILL_Y3</t>
         </is>
       </c>
     </row>
@@ -4516,6 +5684,12 @@
       <c r="T2" s="5" t="inlineStr"/>
       <c r="U2" s="5" t="inlineStr"/>
       <c r="V2" s="5" t="inlineStr"/>
+      <c r="W2" s="5" t="inlineStr"/>
+      <c r="X2" s="5" t="inlineStr"/>
+      <c r="Y2" s="5" t="inlineStr"/>
+      <c r="Z2" s="5" t="inlineStr"/>
+      <c r="AA2" s="5" t="inlineStr"/>
+      <c r="AB2" s="5" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
@@ -4552,6 +5726,12 @@
       <c r="T3" s="5" t="inlineStr"/>
       <c r="U3" s="5" t="inlineStr"/>
       <c r="V3" s="5" t="inlineStr"/>
+      <c r="W3" s="5" t="inlineStr"/>
+      <c r="X3" s="5" t="inlineStr"/>
+      <c r="Y3" s="5" t="inlineStr"/>
+      <c r="Z3" s="5" t="inlineStr"/>
+      <c r="AA3" s="5" t="inlineStr"/>
+      <c r="AB3" s="5" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
@@ -4588,6 +5768,12 @@
       <c r="T4" s="5" t="inlineStr"/>
       <c r="U4" s="5" t="inlineStr"/>
       <c r="V4" s="5" t="inlineStr"/>
+      <c r="W4" s="5" t="inlineStr"/>
+      <c r="X4" s="5" t="inlineStr"/>
+      <c r="Y4" s="5" t="inlineStr"/>
+      <c r="Z4" s="5" t="inlineStr"/>
+      <c r="AA4" s="5" t="inlineStr"/>
+      <c r="AB4" s="5" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
@@ -4628,6 +5814,12 @@
       <c r="T5" s="5" t="inlineStr"/>
       <c r="U5" s="5" t="inlineStr"/>
       <c r="V5" s="5" t="inlineStr"/>
+      <c r="W5" s="5" t="inlineStr"/>
+      <c r="X5" s="5" t="inlineStr"/>
+      <c r="Y5" s="5" t="inlineStr"/>
+      <c r="Z5" s="5" t="inlineStr"/>
+      <c r="AA5" s="5" t="inlineStr"/>
+      <c r="AB5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
@@ -4710,6 +5902,24 @@
       <c r="V6" s="5" t="n">
         <v>0.07333333333333335</v>
       </c>
+      <c r="W6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AB6" s="5" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
@@ -4793,6 +6003,24 @@
       </c>
       <c r="V7" s="5" t="n">
         <v>0.07333333333333335</v>
+      </c>
+      <c r="W7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AB7" s="5" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="8">
@@ -4830,6 +6058,12 @@
       <c r="T8" s="5" t="inlineStr"/>
       <c r="U8" s="5" t="inlineStr"/>
       <c r="V8" s="5" t="inlineStr"/>
+      <c r="W8" s="5" t="inlineStr"/>
+      <c r="X8" s="5" t="inlineStr"/>
+      <c r="Y8" s="5" t="inlineStr"/>
+      <c r="Z8" s="5" t="inlineStr"/>
+      <c r="AA8" s="5" t="inlineStr"/>
+      <c r="AB8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
@@ -4866,6 +6100,12 @@
       <c r="T9" s="5" t="inlineStr"/>
       <c r="U9" s="5" t="inlineStr"/>
       <c r="V9" s="5" t="inlineStr"/>
+      <c r="W9" s="5" t="inlineStr"/>
+      <c r="X9" s="5" t="inlineStr"/>
+      <c r="Y9" s="5" t="inlineStr"/>
+      <c r="Z9" s="5" t="inlineStr"/>
+      <c r="AA9" s="5" t="inlineStr"/>
+      <c r="AB9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
@@ -4910,6 +6150,12 @@
       <c r="T10" s="5" t="inlineStr"/>
       <c r="U10" s="5" t="inlineStr"/>
       <c r="V10" s="5" t="inlineStr"/>
+      <c r="W10" s="5" t="inlineStr"/>
+      <c r="X10" s="5" t="inlineStr"/>
+      <c r="Y10" s="5" t="inlineStr"/>
+      <c r="Z10" s="5" t="inlineStr"/>
+      <c r="AA10" s="5" t="inlineStr"/>
+      <c r="AB10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
@@ -4991,6 +6237,24 @@
       </c>
       <c r="V11" s="5" t="n">
         <v>0.09333333333333334</v>
+      </c>
+      <c r="W11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AB11" s="5" t="n">
+        <v>0.11</v>
       </c>
     </row>
     <row r="12">
@@ -5072,6 +6336,24 @@
       <c r="V12" s="5" t="n">
         <v>0.09333333333333334</v>
       </c>
+      <c r="W12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AB12" s="5" t="n">
+        <v>0.11</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
@@ -5156,6 +6438,24 @@
       <c r="V13" s="5" t="n">
         <v>0.16</v>
       </c>
+      <c r="W13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AB13" s="5" t="n">
+        <v>0.26</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
@@ -5240,6 +6540,24 @@
       <c r="V14" s="5" t="n">
         <v>0.16</v>
       </c>
+      <c r="W14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AB14" s="5" t="n">
+        <v>0.26</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
@@ -5324,6 +6642,24 @@
       <c r="V15" s="5" t="n">
         <v>0.16</v>
       </c>
+      <c r="W15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AB15" s="5" t="n">
+        <v>0.26</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
@@ -5408,6 +6744,24 @@
       <c r="V16" s="5" t="n">
         <v>0.16</v>
       </c>
+      <c r="W16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AB16" s="5" t="n">
+        <v>0.26</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
@@ -5492,6 +6846,24 @@
       <c r="V17" s="5" t="n">
         <v>0.16</v>
       </c>
+      <c r="W17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AB17" s="5" t="n">
+        <v>0.26</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
@@ -5574,6 +6946,24 @@
       <c r="V18" s="5" t="n">
         <v>0.09333333333333334</v>
       </c>
+      <c r="W18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AB18" s="5" t="n">
+        <v>0.11</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
@@ -5657,6 +7047,24 @@
       </c>
       <c r="V19" s="5" t="n">
         <v>0.07333333333333335</v>
+      </c>
+      <c r="W19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AB19" s="5" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="20">
@@ -5702,6 +7110,12 @@
       <c r="T20" s="5" t="inlineStr"/>
       <c r="U20" s="5" t="inlineStr"/>
       <c r="V20" s="5" t="inlineStr"/>
+      <c r="W20" s="5" t="inlineStr"/>
+      <c r="X20" s="5" t="inlineStr"/>
+      <c r="Y20" s="5" t="inlineStr"/>
+      <c r="Z20" s="5" t="inlineStr"/>
+      <c r="AA20" s="5" t="inlineStr"/>
+      <c r="AB20" s="5" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
@@ -5746,6 +7160,12 @@
       <c r="T21" s="5" t="inlineStr"/>
       <c r="U21" s="5" t="inlineStr"/>
       <c r="V21" s="5" t="inlineStr"/>
+      <c r="W21" s="5" t="inlineStr"/>
+      <c r="X21" s="5" t="inlineStr"/>
+      <c r="Y21" s="5" t="inlineStr"/>
+      <c r="Z21" s="5" t="inlineStr"/>
+      <c r="AA21" s="5" t="inlineStr"/>
+      <c r="AB21" s="5" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
@@ -5826,6 +7246,24 @@
       <c r="V22" s="5" t="n">
         <v>0.09333333333333334</v>
       </c>
+      <c r="W22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AB22" s="5" t="n">
+        <v>0.11</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
@@ -5906,6 +7344,24 @@
       <c r="V23" s="5" t="n">
         <v>0.05</v>
       </c>
+      <c r="W23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="AB23" s="5" t="n">
+        <v>0.18</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
@@ -5986,6 +7442,24 @@
       <c r="V24" s="5" t="n">
         <v>0.05333333333333334</v>
       </c>
+      <c r="W24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" s="5" t="n">
+        <v>0.09</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
@@ -6066,6 +7540,24 @@
       <c r="V25" s="5" t="n">
         <v>0.05333333333333334</v>
       </c>
+      <c r="W25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB25" s="5" t="n">
+        <v>0.09</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
@@ -6144,6 +7636,24 @@
       <c r="V26" s="5" t="n">
         <v>0.05333333333333334</v>
       </c>
+      <c r="W26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB26" s="5" t="n">
+        <v>0.09</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
@@ -6224,6 +7734,24 @@
       <c r="V27" s="5" t="n">
         <v>0.05333333333333334</v>
       </c>
+      <c r="W27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB27" s="5" t="n">
+        <v>0.09</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
@@ -6304,6 +7832,24 @@
       <c r="V28" s="5" t="n">
         <v>0.05333333333333334</v>
       </c>
+      <c r="W28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB28" s="5" t="n">
+        <v>0.09</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
@@ -6384,6 +7930,24 @@
       <c r="V29" s="5" t="n">
         <v>0.05333333333333334</v>
       </c>
+      <c r="W29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="5" t="n">
+        <v>0.09</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
@@ -6464,6 +8028,24 @@
       <c r="V30" s="5" t="n">
         <v>0.05333333333333334</v>
       </c>
+      <c r="W30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB30" s="5" t="n">
+        <v>0.09</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
@@ -6544,6 +8126,24 @@
       <c r="V31" s="5" t="n">
         <v>0.05333333333333334</v>
       </c>
+      <c r="W31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB31" s="5" t="n">
+        <v>0.09</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
@@ -6624,6 +8224,24 @@
       <c r="V32" s="5" t="n">
         <v>0.09333333333333334</v>
       </c>
+      <c r="W32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AB32" s="5" t="n">
+        <v>0.11</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
@@ -6704,6 +8322,24 @@
       <c r="V33" s="5" t="n">
         <v>0.09333333333333334</v>
       </c>
+      <c r="W33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA33" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AB33" s="5" t="n">
+        <v>0.11</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
@@ -6784,6 +8420,24 @@
       <c r="V34" s="5" t="n">
         <v>0.09333333333333334</v>
       </c>
+      <c r="W34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA34" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AB34" s="5" t="n">
+        <v>0.11</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
@@ -6864,6 +8518,24 @@
       <c r="V35" s="5" t="n">
         <v>0.07333333333333335</v>
       </c>
+      <c r="W35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA35" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AB35" s="5" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
@@ -6944,6 +8616,24 @@
       <c r="V36" s="5" t="n">
         <v>0.07333333333333335</v>
       </c>
+      <c r="W36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA36" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AB36" s="5" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
@@ -7024,6 +8714,24 @@
       <c r="V37" s="5" t="n">
         <v>0.05</v>
       </c>
+      <c r="W37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA37" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="AB37" s="5" t="n">
+        <v>0.18</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
@@ -7104,6 +8812,24 @@
       <c r="V38" s="5" t="n">
         <v>0.05333333333333334</v>
       </c>
+      <c r="W38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB38" s="5" t="n">
+        <v>0.09</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
@@ -7184,6 +8910,24 @@
       <c r="V39" s="5" t="n">
         <v>0.07333333333333335</v>
       </c>
+      <c r="W39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA39" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AB39" s="5" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
@@ -7264,6 +9008,24 @@
       <c r="V40" s="5" t="n">
         <v>0.05333333333333334</v>
       </c>
+      <c r="W40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB40" s="5" t="n">
+        <v>0.09</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
@@ -7344,6 +9106,24 @@
       <c r="V41" s="5" t="n">
         <v>0.05333333333333334</v>
       </c>
+      <c r="W41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB41" s="5" t="n">
+        <v>0.09</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="8" t="inlineStr">
@@ -7423,6 +9203,24 @@
       </c>
       <c r="V42" s="5" t="n">
         <v>0.05333333333333334</v>
+      </c>
+      <c r="W42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB42" s="5" t="n">
+        <v>0.09</v>
       </c>
     </row>
     <row r="43">
@@ -7464,6 +9262,12 @@
       <c r="T43" s="5" t="inlineStr"/>
       <c r="U43" s="5" t="inlineStr"/>
       <c r="V43" s="5" t="inlineStr"/>
+      <c r="W43" s="5" t="inlineStr"/>
+      <c r="X43" s="5" t="inlineStr"/>
+      <c r="Y43" s="5" t="inlineStr"/>
+      <c r="Z43" s="5" t="inlineStr"/>
+      <c r="AA43" s="5" t="inlineStr"/>
+      <c r="AB43" s="5" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
@@ -7544,6 +9348,24 @@
       <c r="V44" s="5" t="n">
         <v>0.05333333333333334</v>
       </c>
+      <c r="W44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB44" s="5" t="n">
+        <v>0.09</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
@@ -7628,6 +9450,24 @@
       <c r="V45" s="5" t="n">
         <v>0.05333333333333334</v>
       </c>
+      <c r="W45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB45" s="5" t="n">
+        <v>0.09</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
@@ -7708,6 +9548,20 @@
       <c r="V46" s="5" t="n">
         <v>0.09333333333333334</v>
       </c>
+      <c r="W46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X46" s="5" t="inlineStr"/>
+      <c r="Y46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA46" s="5" t="inlineStr"/>
+      <c r="AB46" s="5" t="n">
+        <v>0.25</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
@@ -7787,6 +9641,24 @@
       </c>
       <c r="V47" s="5" t="n">
         <v>0.05333333333333334</v>
+      </c>
+      <c r="W47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB47" s="5" t="n">
+        <v>0.09</v>
       </c>
     </row>
   </sheetData>
@@ -8030,6 +9902,78 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="W2:W47">
+    <cfRule type="colorScale" priority="21">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X2:X47">
+    <cfRule type="colorScale" priority="22">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Y2:Y47">
+    <cfRule type="colorScale" priority="23">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z2:Z47">
+    <cfRule type="colorScale" priority="24">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA2:AA47">
+    <cfRule type="colorScale" priority="25">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AB2:AB47">
+    <cfRule type="colorScale" priority="26">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/outputs/SA_curtailment.xlsx
+++ b/outputs/SA_curtailment.xlsx
@@ -915,7 +915,7 @@
         <v>0.1844</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>0.2169</v>
+        <v>0.2166</v>
       </c>
       <c r="M5" s="5" t="inlineStr"/>
       <c r="N5" s="5" t="inlineStr"/>
@@ -1115,7 +1115,7 @@
         <v>0.2949</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>0.3494</v>
+        <v>0.3505</v>
       </c>
       <c r="M7" s="5" t="n">
         <v>0.501077617843089</v>
@@ -1352,7 +1352,7 @@
         <v>0.2553</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>0.3271</v>
+        <v>0.3267</v>
       </c>
       <c r="M10" s="5" t="n">
         <v>0.511388342191138</v>
@@ -1679,7 +1679,7 @@
         <v>0.3248</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>0.2805</v>
+        <v>0.2803</v>
       </c>
       <c r="M13" s="5" t="n">
         <v>0.510590381447813</v>
@@ -1802,7 +1802,7 @@
         <v>0.2754</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>0.3889</v>
+        <v>0.3887</v>
       </c>
       <c r="M14" s="5" t="n">
         <v>0.65425629128861</v>
@@ -1925,7 +1925,7 @@
         <v>0.2706</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>0.3995</v>
+        <v>0.3983</v>
       </c>
       <c r="M15" s="5" t="n">
         <v>0.65425629128861</v>
@@ -2171,7 +2171,7 @@
         <v>0.2332</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>0.3486</v>
+        <v>0.3477</v>
       </c>
       <c r="M17" s="5" t="n">
         <v>0.65425629128861</v>
@@ -2415,7 +2415,7 @@
         <v>0.4012</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>0.4795</v>
+        <v>0.4793</v>
       </c>
       <c r="M19" s="5" t="n">
         <v>0.501077617843089</v>
@@ -2538,7 +2538,7 @@
         <v>0.3167</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>0.4574</v>
+        <v>0.4571</v>
       </c>
       <c r="M20" s="5" t="n">
         <v>0.511370986967519</v>
@@ -2625,7 +2625,7 @@
         <v>0.384</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>0.5139</v>
+        <v>0.5138</v>
       </c>
       <c r="M21" s="5" t="n">
         <v>0.511370986967519</v>
@@ -2706,7 +2706,7 @@
         <v>0.2612</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>0.2954</v>
+        <v>0.2957</v>
       </c>
       <c r="M22" s="5" t="inlineStr"/>
       <c r="N22" s="5" t="inlineStr"/>
@@ -3033,7 +3033,7 @@
         <v>0.1796</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>0.0939</v>
+        <v>0.09370000000000001</v>
       </c>
       <c r="M25" s="5" t="inlineStr"/>
       <c r="N25" s="5" t="inlineStr"/>
@@ -3140,7 +3140,7 @@
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="5" t="inlineStr"/>
       <c r="L26" s="5" t="n">
-        <v>0.2788</v>
+        <v>0.2786</v>
       </c>
       <c r="M26" s="5" t="inlineStr"/>
       <c r="N26" s="5" t="inlineStr"/>
@@ -3249,7 +3249,7 @@
         <v>0.1208</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>0.1932</v>
+        <v>0.194</v>
       </c>
       <c r="M27" s="5" t="inlineStr"/>
       <c r="N27" s="5" t="inlineStr"/>
@@ -3358,7 +3358,7 @@
         <v>0.1084</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>0.1913</v>
+        <v>0.1921</v>
       </c>
       <c r="M28" s="5" t="inlineStr"/>
       <c r="N28" s="5" t="inlineStr"/>
@@ -3903,7 +3903,7 @@
         <v>0.2652</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>0.2733</v>
+        <v>0.2735</v>
       </c>
       <c r="M33" s="5" t="inlineStr"/>
       <c r="N33" s="5" t="inlineStr"/>
@@ -4121,7 +4121,7 @@
         <v>0.1458</v>
       </c>
       <c r="L35" s="5" t="n">
-        <v>0.1782</v>
+        <v>0.1786</v>
       </c>
       <c r="M35" s="5" t="inlineStr"/>
       <c r="N35" s="5" t="inlineStr"/>
@@ -4230,7 +4230,7 @@
         <v>0.1653</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>0.1994</v>
+        <v>0.1997</v>
       </c>
       <c r="M36" s="5" t="inlineStr"/>
       <c r="N36" s="5" t="inlineStr"/>
@@ -4339,7 +4339,7 @@
         <v>0.3052</v>
       </c>
       <c r="L37" s="5" t="n">
-        <v>0.151</v>
+        <v>0.1508</v>
       </c>
       <c r="M37" s="5" t="inlineStr"/>
       <c r="N37" s="5" t="inlineStr"/>
@@ -4448,7 +4448,7 @@
         <v>0.1223</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>0.1727</v>
+        <v>0.1735</v>
       </c>
       <c r="M38" s="5" t="inlineStr"/>
       <c r="N38" s="5" t="inlineStr"/>
@@ -4557,7 +4557,7 @@
         <v>0.1999</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>0.2151</v>
+        <v>0.2152</v>
       </c>
       <c r="M39" s="5" t="inlineStr"/>
       <c r="N39" s="5" t="inlineStr"/>
@@ -4775,7 +4775,7 @@
         <v>0</v>
       </c>
       <c r="L41" s="5" t="n">
-        <v>0.0011</v>
+        <v>0.0012</v>
       </c>
       <c r="M41" s="5" t="inlineStr"/>
       <c r="N41" s="5" t="inlineStr"/>
@@ -4884,7 +4884,7 @@
         <v>0.1863</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>0.2693</v>
+        <v>0.2691</v>
       </c>
       <c r="M42" s="5" t="inlineStr"/>
       <c r="N42" s="5" t="inlineStr"/>
@@ -5066,7 +5066,7 @@
         <v>0.0886</v>
       </c>
       <c r="L44" s="5" t="n">
-        <v>0.1901</v>
+        <v>0.1909</v>
       </c>
       <c r="M44" s="5" t="inlineStr"/>
       <c r="N44" s="5" t="inlineStr"/>
@@ -5175,7 +5175,7 @@
         <v>0.0205</v>
       </c>
       <c r="L45" s="5" t="n">
-        <v>0.0109</v>
+        <v>0.0108</v>
       </c>
       <c r="M45" s="5" t="n">
         <v>0.691487736497032</v>
@@ -5292,7 +5292,7 @@
         <v>0.1686</v>
       </c>
       <c r="L46" s="5" t="n">
-        <v>0.2012</v>
+        <v>0.2022</v>
       </c>
       <c r="M46" s="5" t="inlineStr"/>
       <c r="N46" s="5" t="inlineStr"/>
@@ -5397,7 +5397,7 @@
         <v>0.0432</v>
       </c>
       <c r="L47" s="5" t="n">
-        <v>0.0337</v>
+        <v>0.0335</v>
       </c>
       <c r="M47" s="5" t="inlineStr"/>
       <c r="N47" s="5" t="inlineStr"/>
@@ -5796,7 +5796,7 @@
         <v>0.1844</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.2169</v>
+        <v>0.2166</v>
       </c>
       <c r="G5" s="5" t="inlineStr"/>
       <c r="H5" s="5" t="inlineStr"/>
@@ -5942,7 +5942,7 @@
         <v>0.2949</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.3494</v>
+        <v>0.3505</v>
       </c>
       <c r="G7" s="5" t="n">
         <v>0.501077617843089</v>
@@ -6128,7 +6128,7 @@
         <v>0.2553</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>0.3271</v>
+        <v>0.3267</v>
       </c>
       <c r="G10" s="5" t="n">
         <v>0.511388342191138</v>
@@ -6376,7 +6376,7 @@
         <v>0.3248</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.2805</v>
+        <v>0.2803</v>
       </c>
       <c r="G13" s="5" t="n">
         <v>0.510590381447813</v>
@@ -6478,7 +6478,7 @@
         <v>0.2754</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>0.3889</v>
+        <v>0.3887</v>
       </c>
       <c r="G14" s="5" t="n">
         <v>0.65425629128861</v>
@@ -6580,7 +6580,7 @@
         <v>0.2706</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>0.3995</v>
+        <v>0.3983</v>
       </c>
       <c r="G15" s="5" t="n">
         <v>0.65425629128861</v>
@@ -6784,7 +6784,7 @@
         <v>0.2332</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>0.3486</v>
+        <v>0.3477</v>
       </c>
       <c r="G17" s="5" t="n">
         <v>0.65425629128861</v>
@@ -6986,7 +6986,7 @@
         <v>0.4012</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>0.4795</v>
+        <v>0.4793</v>
       </c>
       <c r="G19" s="5" t="n">
         <v>0.501077617843089</v>
@@ -7088,7 +7088,7 @@
         <v>0.3167</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>0.4574</v>
+        <v>0.4571</v>
       </c>
       <c r="G20" s="5" t="n">
         <v>0.511370986967519</v>
@@ -7138,7 +7138,7 @@
         <v>0.384</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>0.5139</v>
+        <v>0.5138</v>
       </c>
       <c r="G21" s="5" t="n">
         <v>0.511370986967519</v>
@@ -7188,7 +7188,7 @@
         <v>0.2612</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>0.2954</v>
+        <v>0.2957</v>
       </c>
       <c r="G22" s="5" t="inlineStr"/>
       <c r="H22" s="5" t="inlineStr"/>
@@ -7482,7 +7482,7 @@
         <v>0.1796</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>0.0939</v>
+        <v>0.09370000000000001</v>
       </c>
       <c r="G25" s="5" t="inlineStr"/>
       <c r="H25" s="5" t="inlineStr"/>
@@ -7578,7 +7578,7 @@
       </c>
       <c r="E26" s="5" t="inlineStr"/>
       <c r="F26" s="5" t="n">
-        <v>0.2788</v>
+        <v>0.2786</v>
       </c>
       <c r="G26" s="5" t="inlineStr"/>
       <c r="H26" s="5" t="inlineStr"/>
@@ -7676,7 +7676,7 @@
         <v>0.1208</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>0.1932</v>
+        <v>0.194</v>
       </c>
       <c r="G27" s="5" t="inlineStr"/>
       <c r="H27" s="5" t="inlineStr"/>
@@ -7774,7 +7774,7 @@
         <v>0.1084</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>0.1913</v>
+        <v>0.1921</v>
       </c>
       <c r="G28" s="5" t="inlineStr"/>
       <c r="H28" s="5" t="inlineStr"/>
@@ -8264,7 +8264,7 @@
         <v>0.2652</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>0.2733</v>
+        <v>0.2735</v>
       </c>
       <c r="G33" s="5" t="inlineStr"/>
       <c r="H33" s="5" t="inlineStr"/>
@@ -8460,7 +8460,7 @@
         <v>0.1458</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>0.1782</v>
+        <v>0.1786</v>
       </c>
       <c r="G35" s="5" t="inlineStr"/>
       <c r="H35" s="5" t="inlineStr"/>
@@ -8558,7 +8558,7 @@
         <v>0.1653</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>0.1994</v>
+        <v>0.1997</v>
       </c>
       <c r="G36" s="5" t="inlineStr"/>
       <c r="H36" s="5" t="inlineStr"/>
@@ -8656,7 +8656,7 @@
         <v>0.3052</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>0.151</v>
+        <v>0.1508</v>
       </c>
       <c r="G37" s="5" t="inlineStr"/>
       <c r="H37" s="5" t="inlineStr"/>
@@ -8754,7 +8754,7 @@
         <v>0.1223</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>0.1727</v>
+        <v>0.1735</v>
       </c>
       <c r="G38" s="5" t="inlineStr"/>
       <c r="H38" s="5" t="inlineStr"/>
@@ -8852,7 +8852,7 @@
         <v>0.1999</v>
       </c>
       <c r="F39" s="5" t="n">
-        <v>0.2151</v>
+        <v>0.2152</v>
       </c>
       <c r="G39" s="5" t="inlineStr"/>
       <c r="H39" s="5" t="inlineStr"/>
@@ -9048,7 +9048,7 @@
         <v>0</v>
       </c>
       <c r="F41" s="5" t="n">
-        <v>0.0011</v>
+        <v>0.0012</v>
       </c>
       <c r="G41" s="5" t="inlineStr"/>
       <c r="H41" s="5" t="inlineStr"/>
@@ -9146,7 +9146,7 @@
         <v>0.1863</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>0.2693</v>
+        <v>0.2691</v>
       </c>
       <c r="G42" s="5" t="inlineStr"/>
       <c r="H42" s="5" t="inlineStr"/>
@@ -9290,7 +9290,7 @@
         <v>0.0886</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>0.1901</v>
+        <v>0.1909</v>
       </c>
       <c r="G44" s="5" t="inlineStr"/>
       <c r="H44" s="5" t="inlineStr"/>
@@ -9388,7 +9388,7 @@
         <v>0.0205</v>
       </c>
       <c r="F45" s="5" t="n">
-        <v>0.0109</v>
+        <v>0.0108</v>
       </c>
       <c r="G45" s="5" t="n">
         <v>0.691487736497032</v>
@@ -9490,7 +9490,7 @@
         <v>0.1686</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>0.2012</v>
+        <v>0.2022</v>
       </c>
       <c r="G46" s="5" t="inlineStr"/>
       <c r="H46" s="5" t="inlineStr"/>
@@ -9584,7 +9584,7 @@
         <v>0.0432</v>
       </c>
       <c r="F47" s="5" t="n">
-        <v>0.0337</v>
+        <v>0.0335</v>
       </c>
       <c r="G47" s="5" t="inlineStr"/>
       <c r="H47" s="5" t="inlineStr"/>
